--- a/data/data.xlsx
+++ b/data/data.xlsx
@@ -5,51 +5,52 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Cecilia\Documents\Modellering\SASM\Modulation\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\git\SASM\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B97A8B43-C7E4-4AB4-B861-60B225759A47}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0CC54695-508B-4F07-92D5-159E6E9E2C38}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="757" firstSheet="9" activeTab="12" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1905" yWindow="1905" windowWidth="38700" windowHeight="15345" tabRatio="878" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="README" sheetId="43" r:id="rId1"/>
-    <sheet name="BIN(IN,SDP)" sheetId="20" r:id="rId2"/>
-    <sheet name="BIR(R,IR,SDP)" sheetId="21" r:id="rId3"/>
-    <sheet name="BIRF(IR,R)" sheetId="22" r:id="rId4"/>
-    <sheet name="BIRI(IR,R)" sheetId="23" r:id="rId5"/>
-    <sheet name="BISFA(SR,IS)" sheetId="24" r:id="rId6"/>
-    <sheet name="BMR(R,PR,TRD)" sheetId="25" r:id="rId7"/>
-    <sheet name="BPN(PN,SDP)" sheetId="26" r:id="rId8"/>
-    <sheet name="BPRN(PR,SDP)" sheetId="27" r:id="rId9"/>
-    <sheet name="BPSI_SA(SA,PS)" sheetId="29" r:id="rId10"/>
-    <sheet name="BXR(R,PR,TRD)" sheetId="30" r:id="rId11"/>
-    <sheet name="CONST(IP,AS)" sheetId="39" r:id="rId12"/>
-    <sheet name="DT(RS,RD)" sheetId="31" r:id="rId13"/>
-    <sheet name="ECR(R,CR,IP)" sheetId="32" r:id="rId14"/>
-    <sheet name="ECR2(R,CR,IP)" sheetId="37" r:id="rId15"/>
-    <sheet name="ECR3(R,CR,IP)" sheetId="38" r:id="rId16"/>
-    <sheet name="MANURE(AS,IP)" sheetId="34" r:id="rId17"/>
-    <sheet name="NSUB(AS,SR)" sheetId="35" r:id="rId18"/>
-    <sheet name="NUTRIENT(P,NUTX)" sheetId="36" r:id="rId19"/>
-    <sheet name="POP(R)" sheetId="40" r:id="rId20"/>
-    <sheet name="PRODCOEFC_SA" sheetId="1" r:id="rId21"/>
-    <sheet name="PRODCOEFC2_PO" sheetId="42" r:id="rId22"/>
-    <sheet name="PRODCOEFL_SA" sheetId="5" r:id="rId23"/>
-    <sheet name="UT(IP)" sheetId="41" r:id="rId24"/>
+    <sheet name="index" sheetId="44" r:id="rId2"/>
+    <sheet name="BIN(IN,SDP)" sheetId="20" r:id="rId3"/>
+    <sheet name="BIR(R,IR,SDP)" sheetId="21" r:id="rId4"/>
+    <sheet name="BIRF(IR,R)" sheetId="22" r:id="rId5"/>
+    <sheet name="BIRI(IR,R)" sheetId="23" r:id="rId6"/>
+    <sheet name="BISFA(SR,IS)" sheetId="24" r:id="rId7"/>
+    <sheet name="BMR(R,PR,TRD)" sheetId="25" r:id="rId8"/>
+    <sheet name="BPN(PN,SDP)" sheetId="26" r:id="rId9"/>
+    <sheet name="BPRN(PR,SDP)" sheetId="27" r:id="rId10"/>
+    <sheet name="BPSI_SA(SA,PS)" sheetId="29" r:id="rId11"/>
+    <sheet name="BXR(R,PR,TRD)" sheetId="30" r:id="rId12"/>
+    <sheet name="CONST(IP,AS)" sheetId="39" r:id="rId13"/>
+    <sheet name="DT(RS,RD)" sheetId="31" r:id="rId14"/>
+    <sheet name="ECR(R,CR,IP)" sheetId="32" r:id="rId15"/>
+    <sheet name="ECR2(R,CR,IP)" sheetId="37" r:id="rId16"/>
+    <sheet name="ECR3(R,CR,IP)" sheetId="38" r:id="rId17"/>
+    <sheet name="MANURE(AS,IP)" sheetId="34" r:id="rId18"/>
+    <sheet name="NSUB(AS,SR)" sheetId="35" r:id="rId19"/>
+    <sheet name="NUTRIENT(P,NUTX)" sheetId="36" r:id="rId20"/>
+    <sheet name="POP(R)" sheetId="40" r:id="rId21"/>
+    <sheet name="PRODCOEFC_SA" sheetId="1" r:id="rId22"/>
+    <sheet name="PRODCOEFC2_PO" sheetId="42" r:id="rId23"/>
+    <sheet name="PRODCOEFL_SA" sheetId="5" r:id="rId24"/>
+    <sheet name="UT(IP)" sheetId="41" r:id="rId25"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'BIN(IN,SDP)'!$A$1:$C$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'BIR(R,IR,SDP)'!$A$1:$D$131</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'BIRF(IR,R)'!$A$1:$C$93</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'BMR(R,PR,TRD)'!$A$1:$D$346</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'BPRN(PR,SDP)'!$A$1:$C$196</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'BPSI_SA(SA,PS)'!$A$1:$C$49</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'CONST(IP,AS)'!$A$1:$C$178</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="13" hidden="1">'ECR(R,CR,IP)'!$A$1:$D$98</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="20" hidden="1">PRODCOEFC_SA!$A$1:$D$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="21" hidden="1">PRODCOEFC2_PO!$A$1:$K$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="22" hidden="1">PRODCOEFL_SA!$A$1:$D$2155</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'BIN(IN,SDP)'!$A$1:$C$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'BIR(R,IR,SDP)'!$A$1:$D$131</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'BIRF(IR,R)'!$A$1:$C$93</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'BMR(R,PR,TRD)'!$A$1:$D$346</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'BPRN(PR,SDP)'!$A$1:$C$196</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'BPSI_SA(SA,PS)'!$A$1:$C$49</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'CONST(IP,AS)'!$A$1:$C$178</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="14" hidden="1">'ECR(R,CR,IP)'!$A$1:$D$98</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="21" hidden="1">PRODCOEFC_SA!$A$1:$D$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="22" hidden="1">PRODCOEFC2_PO!$A$1:$K$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="23" hidden="1">PRODCOEFL_SA!$A$1:$D$2155</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -69,7 +70,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16670" uniqueCount="636">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16745" uniqueCount="689">
   <si>
     <t>AS</t>
   </si>
@@ -1978,12 +1979,171 @@
   <si>
     <t>RD</t>
   </si>
+  <si>
+    <t xml:space="preserve">PRODCOEFC_SA   </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> PRODCOEFC_SA!A2     </t>
+  </si>
+  <si>
+    <t xml:space="preserve">PRODCOEFC2_PO  </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> PRODCOEFC2_PO!A2    </t>
+  </si>
+  <si>
+    <t xml:space="preserve">PRODCOEFL_SA   </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> PRODCOEFL_SA!A2     </t>
+  </si>
+  <si>
+    <t xml:space="preserve">BIN            </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> BIN(IN,SDP)!A2      </t>
+  </si>
+  <si>
+    <t xml:space="preserve">BIR            </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> BIR(R,IR,SDP)!A2    </t>
+  </si>
+  <si>
+    <t xml:space="preserve">BIRF           </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> BIRF(IR,R)!A2       </t>
+  </si>
+  <si>
+    <t xml:space="preserve">BIRI           </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> BIRI(IR,R)!A2       </t>
+  </si>
+  <si>
+    <t xml:space="preserve">BISFA          </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> BISFA(SR,IS)!A1     </t>
+  </si>
+  <si>
+    <t xml:space="preserve">BMR            </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> BMR(R,PR,TRD)!A2    </t>
+  </si>
+  <si>
+    <t xml:space="preserve">BPN            </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> BPN(PN,SDP)!A2      </t>
+  </si>
+  <si>
+    <t xml:space="preserve">BPRN           </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> BPRN(PR,SDP)!A2     </t>
+  </si>
+  <si>
+    <t xml:space="preserve">BPSI_SA        </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> BPSI_SA(SA,PS)!A2   </t>
+  </si>
+  <si>
+    <t xml:space="preserve">BXR            </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> BXR(R,PR,TRD)!A2    </t>
+  </si>
+  <si>
+    <t xml:space="preserve">DT             </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> DT(RS,RD)!A2        </t>
+  </si>
+  <si>
+    <t xml:space="preserve">CONST          </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> CONST(IP,AS)!A2     </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ECR            </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> ECR(R,CR,IP)!A2     </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ECR2           </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> ECR2(R,CR,IP)!A2    </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ECR3           </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> ECR3(R,CR,IP)!A2    </t>
+  </si>
+  <si>
+    <t xml:space="preserve">MANURE         </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> MANURE(AS,IP)!A2    </t>
+  </si>
+  <si>
+    <t xml:space="preserve">NSUB           </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> NSUB(AS,SR)!A2      </t>
+  </si>
+  <si>
+    <t xml:space="preserve">NUTRIENT       </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> NUTRIENT(P,NUTX)!A2 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">POP            </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> POP(R)!A2           </t>
+  </si>
+  <si>
+    <t xml:space="preserve">UT             </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> UT(IP)!A2           </t>
+  </si>
+  <si>
+    <t>range</t>
+  </si>
+  <si>
+    <t>rdim</t>
+  </si>
+  <si>
+    <t>cdim</t>
+  </si>
+  <si>
+    <t>symbol name</t>
+  </si>
+  <si>
+    <t>Define which symbols to read from this workbook</t>
+  </si>
+  <si>
+    <t>Symbol type</t>
+  </si>
+  <si>
+    <t>par</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2025,6 +2185,14 @@
       <name val="Consolas"/>
       <family val="3"/>
     </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color theme="0" tint="-0.499984740745262"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="6">
     <fill>
@@ -2058,7 +2226,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -2090,12 +2258,21 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -2111,10 +2288,12 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="Heading 3" xfId="1" builtinId="18"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Rubrik 3" xfId="1" builtinId="18"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
@@ -3101,6 +3280,2029 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F02DEA1A-0627-4FA3-8C95-326A86063434}">
+  <dimension ref="A1:C196"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="12.28515625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>263</v>
+      </c>
+      <c r="B1" t="s">
+        <v>344</v>
+      </c>
+      <c r="C1" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>307</v>
+      </c>
+      <c r="B2" t="s">
+        <v>129</v>
+      </c>
+      <c r="C2">
+        <v>1.89</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>307</v>
+      </c>
+      <c r="B3" t="s">
+        <v>130</v>
+      </c>
+      <c r="C3">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>307</v>
+      </c>
+      <c r="B4" t="s">
+        <v>131</v>
+      </c>
+      <c r="C4">
+        <v>-0.9</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>307</v>
+      </c>
+      <c r="B5" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>307</v>
+      </c>
+      <c r="B6" t="s">
+        <v>132</v>
+      </c>
+      <c r="C6">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>308</v>
+      </c>
+      <c r="B7" t="s">
+        <v>129</v>
+      </c>
+      <c r="C7">
+        <v>1.79</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>308</v>
+      </c>
+      <c r="B8" t="s">
+        <v>130</v>
+      </c>
+      <c r="C8">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>308</v>
+      </c>
+      <c r="B9" t="s">
+        <v>131</v>
+      </c>
+      <c r="C9">
+        <v>-0.9</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>308</v>
+      </c>
+      <c r="B10" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>308</v>
+      </c>
+      <c r="B11" t="s">
+        <v>132</v>
+      </c>
+      <c r="C11">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>309</v>
+      </c>
+      <c r="B12" t="s">
+        <v>129</v>
+      </c>
+      <c r="C12">
+        <v>5.0199999999999996</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>309</v>
+      </c>
+      <c r="B13" t="s">
+        <v>130</v>
+      </c>
+      <c r="C13">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>309</v>
+      </c>
+      <c r="B14" t="s">
+        <v>131</v>
+      </c>
+      <c r="C14">
+        <v>-0.9</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>309</v>
+      </c>
+      <c r="B15" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>309</v>
+      </c>
+      <c r="B16" t="s">
+        <v>132</v>
+      </c>
+      <c r="C16">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>84</v>
+      </c>
+      <c r="B17" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>84</v>
+      </c>
+      <c r="B18" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>84</v>
+      </c>
+      <c r="B19" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>84</v>
+      </c>
+      <c r="B20" t="s">
+        <v>145</v>
+      </c>
+      <c r="C20">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>84</v>
+      </c>
+      <c r="B21" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>310</v>
+      </c>
+      <c r="B22" t="s">
+        <v>129</v>
+      </c>
+      <c r="C22">
+        <v>14.6</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>310</v>
+      </c>
+      <c r="B23" t="s">
+        <v>130</v>
+      </c>
+      <c r="C23">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>310</v>
+      </c>
+      <c r="B24" t="s">
+        <v>131</v>
+      </c>
+      <c r="C24">
+        <v>-0.9</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>310</v>
+      </c>
+      <c r="B25" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>310</v>
+      </c>
+      <c r="B26" t="s">
+        <v>132</v>
+      </c>
+      <c r="C26">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>311</v>
+      </c>
+      <c r="B27" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>311</v>
+      </c>
+      <c r="B28" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>311</v>
+      </c>
+      <c r="B29" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>311</v>
+      </c>
+      <c r="B30" t="s">
+        <v>145</v>
+      </c>
+      <c r="C30">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>311</v>
+      </c>
+      <c r="B31" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>312</v>
+      </c>
+      <c r="B32" t="s">
+        <v>129</v>
+      </c>
+      <c r="C32">
+        <v>1.35</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>312</v>
+      </c>
+      <c r="B33" t="s">
+        <v>130</v>
+      </c>
+      <c r="C33">
+        <v>850</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>312</v>
+      </c>
+      <c r="B34" t="s">
+        <v>131</v>
+      </c>
+      <c r="C34">
+        <v>-0.9</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>312</v>
+      </c>
+      <c r="B35" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>312</v>
+      </c>
+      <c r="B36" t="s">
+        <v>132</v>
+      </c>
+      <c r="C36">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>313</v>
+      </c>
+      <c r="B37" t="s">
+        <v>129</v>
+      </c>
+      <c r="C37">
+        <v>5.45</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>313</v>
+      </c>
+      <c r="B38" t="s">
+        <v>130</v>
+      </c>
+      <c r="C38">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>313</v>
+      </c>
+      <c r="B39" t="s">
+        <v>131</v>
+      </c>
+      <c r="C39">
+        <v>-0.9</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>313</v>
+      </c>
+      <c r="B40" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>313</v>
+      </c>
+      <c r="B41" t="s">
+        <v>132</v>
+      </c>
+      <c r="C41">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>314</v>
+      </c>
+      <c r="B42" t="s">
+        <v>129</v>
+      </c>
+      <c r="C42">
+        <v>16.13</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>314</v>
+      </c>
+      <c r="B43" t="s">
+        <v>130</v>
+      </c>
+      <c r="C43">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>314</v>
+      </c>
+      <c r="B44" t="s">
+        <v>131</v>
+      </c>
+      <c r="C44">
+        <v>-0.9</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>314</v>
+      </c>
+      <c r="B45" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>314</v>
+      </c>
+      <c r="B46" t="s">
+        <v>132</v>
+      </c>
+      <c r="C46">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>315</v>
+      </c>
+      <c r="B47" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>315</v>
+      </c>
+      <c r="B48" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>315</v>
+      </c>
+      <c r="B49" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>315</v>
+      </c>
+      <c r="B50" t="s">
+        <v>145</v>
+      </c>
+      <c r="C50">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>315</v>
+      </c>
+      <c r="B51" t="s">
+        <v>132</v>
+      </c>
+      <c r="C51">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>316</v>
+      </c>
+      <c r="B52" t="s">
+        <v>129</v>
+      </c>
+      <c r="C52">
+        <v>6.33</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>316</v>
+      </c>
+      <c r="B53" t="s">
+        <v>130</v>
+      </c>
+      <c r="C53">
+        <v>923</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>316</v>
+      </c>
+      <c r="B54" t="s">
+        <v>131</v>
+      </c>
+      <c r="C54">
+        <v>-0.9</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>316</v>
+      </c>
+      <c r="B55" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>316</v>
+      </c>
+      <c r="B56" t="s">
+        <v>132</v>
+      </c>
+      <c r="C56">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>317</v>
+      </c>
+      <c r="B57" t="s">
+        <v>129</v>
+      </c>
+      <c r="C57">
+        <v>46.07</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>317</v>
+      </c>
+      <c r="B58" t="s">
+        <v>130</v>
+      </c>
+      <c r="C58">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>317</v>
+      </c>
+      <c r="B59" t="s">
+        <v>131</v>
+      </c>
+      <c r="C59">
+        <v>-0.9</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>317</v>
+      </c>
+      <c r="B60" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>317</v>
+      </c>
+      <c r="B61" t="s">
+        <v>132</v>
+      </c>
+      <c r="C61">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>318</v>
+      </c>
+      <c r="B62" t="s">
+        <v>129</v>
+      </c>
+      <c r="C62">
+        <v>49.47</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>318</v>
+      </c>
+      <c r="B63" t="s">
+        <v>130</v>
+      </c>
+      <c r="C63">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>318</v>
+      </c>
+      <c r="B64" t="s">
+        <v>131</v>
+      </c>
+      <c r="C64">
+        <v>-0.9</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>318</v>
+      </c>
+      <c r="B65" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>318</v>
+      </c>
+      <c r="B66" t="s">
+        <v>132</v>
+      </c>
+      <c r="C66">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>319</v>
+      </c>
+      <c r="B67" t="s">
+        <v>129</v>
+      </c>
+      <c r="C67">
+        <v>36.020000000000003</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>319</v>
+      </c>
+      <c r="B68" t="s">
+        <v>130</v>
+      </c>
+      <c r="C68">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>319</v>
+      </c>
+      <c r="B69" t="s">
+        <v>131</v>
+      </c>
+      <c r="C69">
+        <v>-0.9</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>319</v>
+      </c>
+      <c r="B70" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
+        <v>319</v>
+      </c>
+      <c r="B71" t="s">
+        <v>132</v>
+      </c>
+      <c r="C71">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
+        <v>320</v>
+      </c>
+      <c r="B72" t="s">
+        <v>129</v>
+      </c>
+      <c r="C72">
+        <v>36.47</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
+        <v>320</v>
+      </c>
+      <c r="B73" t="s">
+        <v>130</v>
+      </c>
+      <c r="C73">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
+        <v>320</v>
+      </c>
+      <c r="B74" t="s">
+        <v>131</v>
+      </c>
+      <c r="C74">
+        <v>-0.9</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
+        <v>320</v>
+      </c>
+      <c r="B75" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
+        <v>320</v>
+      </c>
+      <c r="B76" t="s">
+        <v>132</v>
+      </c>
+      <c r="C76">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
+        <v>321</v>
+      </c>
+      <c r="B77" t="s">
+        <v>129</v>
+      </c>
+      <c r="C77">
+        <v>54.81</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
+        <v>321</v>
+      </c>
+      <c r="B78" t="s">
+        <v>130</v>
+      </c>
+      <c r="C78">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
+        <v>321</v>
+      </c>
+      <c r="B79" t="s">
+        <v>131</v>
+      </c>
+      <c r="C79">
+        <v>-0.9</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A80" t="s">
+        <v>321</v>
+      </c>
+      <c r="B80" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
+        <v>321</v>
+      </c>
+      <c r="B81" t="s">
+        <v>132</v>
+      </c>
+      <c r="C81">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="82" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A82" t="s">
+        <v>322</v>
+      </c>
+      <c r="B82" t="s">
+        <v>129</v>
+      </c>
+      <c r="C82">
+        <v>25.98</v>
+      </c>
+    </row>
+    <row r="83" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A83" t="s">
+        <v>322</v>
+      </c>
+      <c r="B83" t="s">
+        <v>130</v>
+      </c>
+      <c r="C83">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="84" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A84" t="s">
+        <v>322</v>
+      </c>
+      <c r="B84" t="s">
+        <v>131</v>
+      </c>
+      <c r="C84">
+        <v>-0.9</v>
+      </c>
+    </row>
+    <row r="85" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A85" t="s">
+        <v>322</v>
+      </c>
+      <c r="B85" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="86" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A86" t="s">
+        <v>322</v>
+      </c>
+      <c r="B86" t="s">
+        <v>132</v>
+      </c>
+      <c r="C86">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="87" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A87" t="s">
+        <v>323</v>
+      </c>
+      <c r="B87" t="s">
+        <v>129</v>
+      </c>
+      <c r="C87">
+        <v>33.619999999999997</v>
+      </c>
+    </row>
+    <row r="88" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A88" t="s">
+        <v>323</v>
+      </c>
+      <c r="B88" t="s">
+        <v>130</v>
+      </c>
+      <c r="C88">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="89" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A89" t="s">
+        <v>323</v>
+      </c>
+      <c r="B89" t="s">
+        <v>131</v>
+      </c>
+      <c r="C89">
+        <v>-0.9</v>
+      </c>
+    </row>
+    <row r="90" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A90" t="s">
+        <v>323</v>
+      </c>
+      <c r="B90" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="91" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A91" t="s">
+        <v>323</v>
+      </c>
+      <c r="B91" t="s">
+        <v>132</v>
+      </c>
+      <c r="C91">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="92" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A92" t="s">
+        <v>324</v>
+      </c>
+      <c r="B92" t="s">
+        <v>129</v>
+      </c>
+      <c r="C92">
+        <v>64.87</v>
+      </c>
+    </row>
+    <row r="93" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A93" t="s">
+        <v>324</v>
+      </c>
+      <c r="B93" t="s">
+        <v>130</v>
+      </c>
+      <c r="C93">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="94" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A94" t="s">
+        <v>324</v>
+      </c>
+      <c r="B94" t="s">
+        <v>131</v>
+      </c>
+      <c r="C94">
+        <v>-0.9</v>
+      </c>
+    </row>
+    <row r="95" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A95" t="s">
+        <v>324</v>
+      </c>
+      <c r="B95" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="96" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A96" t="s">
+        <v>324</v>
+      </c>
+      <c r="B96" t="s">
+        <v>132</v>
+      </c>
+      <c r="C96">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="97" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A97" t="s">
+        <v>325</v>
+      </c>
+      <c r="B97" t="s">
+        <v>129</v>
+      </c>
+      <c r="C97">
+        <v>56.95</v>
+      </c>
+    </row>
+    <row r="98" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A98" t="s">
+        <v>325</v>
+      </c>
+      <c r="B98" t="s">
+        <v>130</v>
+      </c>
+      <c r="C98">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="99" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A99" t="s">
+        <v>325</v>
+      </c>
+      <c r="B99" t="s">
+        <v>131</v>
+      </c>
+      <c r="C99">
+        <v>-0.9</v>
+      </c>
+    </row>
+    <row r="100" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A100" t="s">
+        <v>325</v>
+      </c>
+      <c r="B100" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="101" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A101" t="s">
+        <v>325</v>
+      </c>
+      <c r="B101" t="s">
+        <v>132</v>
+      </c>
+      <c r="C101">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="102" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A102" t="s">
+        <v>326</v>
+      </c>
+      <c r="B102" t="s">
+        <v>129</v>
+      </c>
+      <c r="C102">
+        <v>37.479999999999997</v>
+      </c>
+    </row>
+    <row r="103" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A103" t="s">
+        <v>326</v>
+      </c>
+      <c r="B103" t="s">
+        <v>130</v>
+      </c>
+      <c r="C103">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="104" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A104" t="s">
+        <v>326</v>
+      </c>
+      <c r="B104" t="s">
+        <v>131</v>
+      </c>
+      <c r="C104">
+        <v>-0.9</v>
+      </c>
+    </row>
+    <row r="105" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A105" t="s">
+        <v>326</v>
+      </c>
+      <c r="B105" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="106" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A106" t="s">
+        <v>326</v>
+      </c>
+      <c r="B106" t="s">
+        <v>132</v>
+      </c>
+      <c r="C106">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="107" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A107" t="s">
+        <v>327</v>
+      </c>
+      <c r="B107" t="s">
+        <v>129</v>
+      </c>
+      <c r="C107">
+        <v>12.64</v>
+      </c>
+    </row>
+    <row r="108" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A108" t="s">
+        <v>327</v>
+      </c>
+      <c r="B108" t="s">
+        <v>130</v>
+      </c>
+      <c r="C108">
+        <v>940</v>
+      </c>
+    </row>
+    <row r="109" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A109" t="s">
+        <v>327</v>
+      </c>
+      <c r="B109" t="s">
+        <v>131</v>
+      </c>
+      <c r="C109">
+        <v>-0.9</v>
+      </c>
+    </row>
+    <row r="110" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A110" t="s">
+        <v>327</v>
+      </c>
+      <c r="B110" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="111" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A111" t="s">
+        <v>327</v>
+      </c>
+      <c r="B111" t="s">
+        <v>132</v>
+      </c>
+      <c r="C111">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="112" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A112" t="s">
+        <v>328</v>
+      </c>
+      <c r="B112" t="s">
+        <v>129</v>
+      </c>
+      <c r="C112">
+        <v>12.64</v>
+      </c>
+    </row>
+    <row r="113" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A113" t="s">
+        <v>328</v>
+      </c>
+      <c r="B113" t="s">
+        <v>130</v>
+      </c>
+      <c r="C113">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="114" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A114" t="s">
+        <v>328</v>
+      </c>
+      <c r="B114" t="s">
+        <v>131</v>
+      </c>
+      <c r="C114">
+        <v>-0.9</v>
+      </c>
+    </row>
+    <row r="115" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A115" t="s">
+        <v>328</v>
+      </c>
+      <c r="B115" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="116" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A116" t="s">
+        <v>328</v>
+      </c>
+      <c r="B116" t="s">
+        <v>132</v>
+      </c>
+      <c r="C116">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="117" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A117" t="s">
+        <v>329</v>
+      </c>
+      <c r="B117" t="s">
+        <v>129</v>
+      </c>
+      <c r="C117">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="118" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A118" t="s">
+        <v>329</v>
+      </c>
+      <c r="B118" t="s">
+        <v>130</v>
+      </c>
+      <c r="C118">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="119" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A119" t="s">
+        <v>329</v>
+      </c>
+      <c r="B119" t="s">
+        <v>131</v>
+      </c>
+      <c r="C119">
+        <v>-0.9</v>
+      </c>
+    </row>
+    <row r="120" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A120" t="s">
+        <v>329</v>
+      </c>
+      <c r="B120" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="121" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A121" t="s">
+        <v>329</v>
+      </c>
+      <c r="B121" t="s">
+        <v>132</v>
+      </c>
+      <c r="C121">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="122" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A122" t="s">
+        <v>268</v>
+      </c>
+      <c r="B122" t="s">
+        <v>129</v>
+      </c>
+      <c r="C122">
+        <v>1.75</v>
+      </c>
+    </row>
+    <row r="123" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A123" t="s">
+        <v>268</v>
+      </c>
+      <c r="B123" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="124" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A124" t="s">
+        <v>268</v>
+      </c>
+      <c r="B124" t="s">
+        <v>131</v>
+      </c>
+      <c r="C124">
+        <v>-999</v>
+      </c>
+    </row>
+    <row r="125" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A125" t="s">
+        <v>268</v>
+      </c>
+      <c r="B125" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="126" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A126" t="s">
+        <v>268</v>
+      </c>
+      <c r="B126" t="s">
+        <v>132</v>
+      </c>
+      <c r="C126">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="127" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A127" t="s">
+        <v>330</v>
+      </c>
+      <c r="B127" t="s">
+        <v>129</v>
+      </c>
+      <c r="C127">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="128" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A128" t="s">
+        <v>330</v>
+      </c>
+      <c r="B128" t="s">
+        <v>130</v>
+      </c>
+      <c r="C128">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="129" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A129" t="s">
+        <v>330</v>
+      </c>
+      <c r="B129" t="s">
+        <v>131</v>
+      </c>
+      <c r="C129">
+        <v>-999</v>
+      </c>
+    </row>
+    <row r="130" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A130" t="s">
+        <v>330</v>
+      </c>
+      <c r="B130" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="131" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A131" t="s">
+        <v>330</v>
+      </c>
+      <c r="B131" t="s">
+        <v>132</v>
+      </c>
+      <c r="C131">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="132" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A132" t="s">
+        <v>331</v>
+      </c>
+      <c r="B132" t="s">
+        <v>129</v>
+      </c>
+      <c r="C132">
+        <v>5.2</v>
+      </c>
+    </row>
+    <row r="133" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A133" t="s">
+        <v>331</v>
+      </c>
+      <c r="B133" t="s">
+        <v>130</v>
+      </c>
+      <c r="C133">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="134" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A134" t="s">
+        <v>331</v>
+      </c>
+      <c r="B134" t="s">
+        <v>131</v>
+      </c>
+      <c r="C134">
+        <v>-999</v>
+      </c>
+    </row>
+    <row r="135" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A135" t="s">
+        <v>331</v>
+      </c>
+      <c r="B135" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="136" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A136" t="s">
+        <v>331</v>
+      </c>
+      <c r="B136" t="s">
+        <v>132</v>
+      </c>
+      <c r="C136">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="137" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A137" t="s">
+        <v>332</v>
+      </c>
+      <c r="B137" t="s">
+        <v>129</v>
+      </c>
+      <c r="C137">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="138" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A138" t="s">
+        <v>332</v>
+      </c>
+      <c r="B138" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="139" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A139" t="s">
+        <v>332</v>
+      </c>
+      <c r="B139" t="s">
+        <v>131</v>
+      </c>
+      <c r="C139">
+        <v>-999</v>
+      </c>
+    </row>
+    <row r="140" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A140" t="s">
+        <v>332</v>
+      </c>
+      <c r="B140" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="141" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A141" t="s">
+        <v>332</v>
+      </c>
+      <c r="B141" t="s">
+        <v>132</v>
+      </c>
+      <c r="C141">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="142" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A142" t="s">
+        <v>333</v>
+      </c>
+      <c r="B142" t="s">
+        <v>129</v>
+      </c>
+      <c r="C142">
+        <v>2.2000000000000002</v>
+      </c>
+    </row>
+    <row r="143" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A143" t="s">
+        <v>333</v>
+      </c>
+      <c r="B143" t="s">
+        <v>130</v>
+      </c>
+      <c r="C143">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="144" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A144" t="s">
+        <v>333</v>
+      </c>
+      <c r="B144" t="s">
+        <v>131</v>
+      </c>
+      <c r="C144">
+        <v>-0.1</v>
+      </c>
+    </row>
+    <row r="145" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A145" t="s">
+        <v>333</v>
+      </c>
+      <c r="B145" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="146" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A146" t="s">
+        <v>333</v>
+      </c>
+      <c r="B146" t="s">
+        <v>132</v>
+      </c>
+      <c r="C146">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="147" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A147" t="s">
+        <v>334</v>
+      </c>
+      <c r="B147" t="s">
+        <v>129</v>
+      </c>
+      <c r="C147">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="148" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A148" t="s">
+        <v>334</v>
+      </c>
+      <c r="B148" t="s">
+        <v>130</v>
+      </c>
+      <c r="C148">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="149" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A149" t="s">
+        <v>334</v>
+      </c>
+      <c r="B149" t="s">
+        <v>131</v>
+      </c>
+      <c r="C149">
+        <v>-0.5</v>
+      </c>
+    </row>
+    <row r="150" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A150" t="s">
+        <v>334</v>
+      </c>
+      <c r="B150" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="151" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A151" t="s">
+        <v>334</v>
+      </c>
+      <c r="B151" t="s">
+        <v>132</v>
+      </c>
+      <c r="C151">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="152" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A152" t="s">
+        <v>335</v>
+      </c>
+      <c r="B152" t="s">
+        <v>129</v>
+      </c>
+      <c r="C152">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="153" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A153" t="s">
+        <v>335</v>
+      </c>
+      <c r="B153" t="s">
+        <v>130</v>
+      </c>
+      <c r="C153">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="154" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A154" t="s">
+        <v>335</v>
+      </c>
+      <c r="B154" t="s">
+        <v>131</v>
+      </c>
+      <c r="C154">
+        <v>-0.5</v>
+      </c>
+    </row>
+    <row r="155" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A155" t="s">
+        <v>335</v>
+      </c>
+      <c r="B155" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="156" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A156" t="s">
+        <v>335</v>
+      </c>
+      <c r="B156" t="s">
+        <v>132</v>
+      </c>
+      <c r="C156">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="157" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A157" t="s">
+        <v>336</v>
+      </c>
+      <c r="B157" t="s">
+        <v>129</v>
+      </c>
+      <c r="C157">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="158" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A158" t="s">
+        <v>336</v>
+      </c>
+      <c r="B158" t="s">
+        <v>130</v>
+      </c>
+      <c r="C158">
+        <v>4.3</v>
+      </c>
+    </row>
+    <row r="159" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A159" t="s">
+        <v>336</v>
+      </c>
+      <c r="B159" t="s">
+        <v>131</v>
+      </c>
+      <c r="C159">
+        <v>-0.5</v>
+      </c>
+    </row>
+    <row r="160" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A160" t="s">
+        <v>336</v>
+      </c>
+      <c r="B160" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="161" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A161" t="s">
+        <v>336</v>
+      </c>
+      <c r="B161" t="s">
+        <v>132</v>
+      </c>
+      <c r="C161">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="162" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A162" t="s">
+        <v>337</v>
+      </c>
+      <c r="B162" t="s">
+        <v>129</v>
+      </c>
+      <c r="C162">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="163" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A163" t="s">
+        <v>337</v>
+      </c>
+      <c r="B163" t="s">
+        <v>130</v>
+      </c>
+      <c r="C163">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="164" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A164" t="s">
+        <v>337</v>
+      </c>
+      <c r="B164" t="s">
+        <v>131</v>
+      </c>
+      <c r="C164">
+        <v>-0.5</v>
+      </c>
+    </row>
+    <row r="165" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A165" t="s">
+        <v>337</v>
+      </c>
+      <c r="B165" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="166" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A166" t="s">
+        <v>337</v>
+      </c>
+      <c r="B166" t="s">
+        <v>132</v>
+      </c>
+      <c r="C166">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="167" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A167" t="s">
+        <v>338</v>
+      </c>
+      <c r="B167" t="s">
+        <v>129</v>
+      </c>
+      <c r="C167">
+        <v>10.5</v>
+      </c>
+    </row>
+    <row r="168" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A168" t="s">
+        <v>338</v>
+      </c>
+      <c r="B168" t="s">
+        <v>130</v>
+      </c>
+      <c r="C168">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="169" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A169" t="s">
+        <v>338</v>
+      </c>
+      <c r="B169" t="s">
+        <v>131</v>
+      </c>
+      <c r="C169">
+        <v>-0.5</v>
+      </c>
+    </row>
+    <row r="170" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A170" t="s">
+        <v>338</v>
+      </c>
+      <c r="B170" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="171" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A171" t="s">
+        <v>338</v>
+      </c>
+      <c r="B171" t="s">
+        <v>132</v>
+      </c>
+      <c r="C171">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="172" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A172" t="s">
+        <v>339</v>
+      </c>
+      <c r="B172" t="s">
+        <v>129</v>
+      </c>
+      <c r="C172">
+        <v>1E-3</v>
+      </c>
+    </row>
+    <row r="173" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A173" t="s">
+        <v>339</v>
+      </c>
+      <c r="B173" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="174" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A174" t="s">
+        <v>339</v>
+      </c>
+      <c r="B174" t="s">
+        <v>131</v>
+      </c>
+      <c r="C174">
+        <v>-999</v>
+      </c>
+    </row>
+    <row r="175" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A175" t="s">
+        <v>339</v>
+      </c>
+      <c r="B175" t="s">
+        <v>145</v>
+      </c>
+      <c r="C175">
+        <v>38.83</v>
+      </c>
+    </row>
+    <row r="176" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A176" t="s">
+        <v>339</v>
+      </c>
+      <c r="B176" t="s">
+        <v>132</v>
+      </c>
+      <c r="C176">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="177" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A177" t="s">
+        <v>340</v>
+      </c>
+      <c r="B177" t="s">
+        <v>129</v>
+      </c>
+      <c r="C177">
+        <v>1E-3</v>
+      </c>
+    </row>
+    <row r="178" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A178" t="s">
+        <v>340</v>
+      </c>
+      <c r="B178" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="179" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A179" t="s">
+        <v>340</v>
+      </c>
+      <c r="B179" t="s">
+        <v>131</v>
+      </c>
+      <c r="C179">
+        <v>-999</v>
+      </c>
+    </row>
+    <row r="180" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A180" t="s">
+        <v>340</v>
+      </c>
+      <c r="B180" t="s">
+        <v>145</v>
+      </c>
+      <c r="C180">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="181" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A181" t="s">
+        <v>340</v>
+      </c>
+      <c r="B181" t="s">
+        <v>132</v>
+      </c>
+      <c r="C181">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="182" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A182" t="s">
+        <v>341</v>
+      </c>
+      <c r="B182" t="s">
+        <v>129</v>
+      </c>
+      <c r="C182">
+        <v>1E-3</v>
+      </c>
+    </row>
+    <row r="183" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A183" t="s">
+        <v>341</v>
+      </c>
+      <c r="B183" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="184" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A184" t="s">
+        <v>341</v>
+      </c>
+      <c r="B184" t="s">
+        <v>131</v>
+      </c>
+      <c r="C184">
+        <v>-999</v>
+      </c>
+    </row>
+    <row r="185" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A185" t="s">
+        <v>341</v>
+      </c>
+      <c r="B185" t="s">
+        <v>145</v>
+      </c>
+      <c r="C185">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="186" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A186" t="s">
+        <v>341</v>
+      </c>
+      <c r="B186" t="s">
+        <v>132</v>
+      </c>
+      <c r="C186">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="187" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A187" t="s">
+        <v>342</v>
+      </c>
+      <c r="B187" t="s">
+        <v>129</v>
+      </c>
+      <c r="C187">
+        <v>1E-3</v>
+      </c>
+    </row>
+    <row r="188" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A188" t="s">
+        <v>342</v>
+      </c>
+      <c r="B188" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="189" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A189" t="s">
+        <v>342</v>
+      </c>
+      <c r="B189" t="s">
+        <v>131</v>
+      </c>
+      <c r="C189">
+        <v>-999</v>
+      </c>
+    </row>
+    <row r="190" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A190" t="s">
+        <v>342</v>
+      </c>
+      <c r="B190" t="s">
+        <v>145</v>
+      </c>
+      <c r="C190">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="191" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A191" t="s">
+        <v>342</v>
+      </c>
+      <c r="B191" t="s">
+        <v>132</v>
+      </c>
+      <c r="C191">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="192" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A192" t="s">
+        <v>343</v>
+      </c>
+      <c r="B192" t="s">
+        <v>129</v>
+      </c>
+      <c r="C192">
+        <v>1E-3</v>
+      </c>
+    </row>
+    <row r="193" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A193" t="s">
+        <v>343</v>
+      </c>
+      <c r="B193" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="194" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A194" t="s">
+        <v>343</v>
+      </c>
+      <c r="B194" t="s">
+        <v>131</v>
+      </c>
+      <c r="C194">
+        <v>-999</v>
+      </c>
+    </row>
+    <row r="195" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A195" t="s">
+        <v>343</v>
+      </c>
+      <c r="B195" t="s">
+        <v>145</v>
+      </c>
+      <c r="C195">
+        <v>1028</v>
+      </c>
+    </row>
+    <row r="196" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A196" t="s">
+        <v>343</v>
+      </c>
+      <c r="B196" t="s">
+        <v>132</v>
+      </c>
+      <c r="C196">
+        <v>8000</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:C196" xr:uid="{F02DEA1A-0627-4FA3-8C95-326A86063434}"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{543294A7-8847-4059-B9C5-DCC8AF9576B7}">
   <dimension ref="A1:G53"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -3668,7 +5870,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E133A33D-E39B-4857-9733-11C96C659C3D}">
   <dimension ref="A1:D211"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -6257,7 +8459,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7376126D-3EA0-4AA6-924B-8CDB79470677}">
   <dimension ref="A1:C178"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -8234,7 +10436,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{60EE37BB-98DC-4ED4-A28C-74B3846A915F}">
   <dimension ref="A1:C31"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -8585,7 +10787,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{80DF8849-C01F-4A0B-9953-8F8DCF30C6A1}">
   <sheetPr filterMode="1"/>
   <dimension ref="A1:D98"/>
@@ -9983,7 +12185,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C093044C-CE87-48B9-9743-B9C8F946775A}">
   <dimension ref="A1:D44"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -10609,7 +12811,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{099EBCF6-02CF-4AE3-A766-589E08AF19F2}">
   <dimension ref="A1:D13"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -10801,7 +13003,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{118A6323-FA6A-47F1-8FD7-71097682A301}">
   <dimension ref="A1:C183"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -12594,7 +14796,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{61D05816-00FF-458D-8921-8D01423DCE8A}">
   <dimension ref="A1:C61"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -13275,7 +15477,436 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FC09F416-B83A-444C-8E2A-32773041705C}">
+  <dimension ref="A1:E28"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="13.7109375" customWidth="1"/>
+    <col min="2" max="2" width="34.5703125" customWidth="1"/>
+    <col min="3" max="3" width="22.140625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>686</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" s="11" t="s">
+        <v>687</v>
+      </c>
+      <c r="B5" s="11" t="s">
+        <v>685</v>
+      </c>
+      <c r="C5" s="11" t="s">
+        <v>682</v>
+      </c>
+      <c r="D5" s="12" t="s">
+        <v>683</v>
+      </c>
+      <c r="E5" s="12" t="s">
+        <v>684</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>688</v>
+      </c>
+      <c r="B6" t="s">
+        <v>636</v>
+      </c>
+      <c r="C6" t="s">
+        <v>637</v>
+      </c>
+      <c r="D6">
+        <v>3</v>
+      </c>
+      <c r="E6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>688</v>
+      </c>
+      <c r="B7" t="s">
+        <v>638</v>
+      </c>
+      <c r="C7" t="s">
+        <v>639</v>
+      </c>
+      <c r="D7">
+        <v>3</v>
+      </c>
+      <c r="E7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>688</v>
+      </c>
+      <c r="B8" t="s">
+        <v>640</v>
+      </c>
+      <c r="C8" t="s">
+        <v>641</v>
+      </c>
+      <c r="D8">
+        <v>3</v>
+      </c>
+      <c r="E8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>688</v>
+      </c>
+      <c r="B9" t="s">
+        <v>642</v>
+      </c>
+      <c r="C9" t="s">
+        <v>643</v>
+      </c>
+      <c r="D9">
+        <v>2</v>
+      </c>
+      <c r="E9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>688</v>
+      </c>
+      <c r="B10" t="s">
+        <v>644</v>
+      </c>
+      <c r="C10" t="s">
+        <v>645</v>
+      </c>
+      <c r="D10">
+        <v>3</v>
+      </c>
+      <c r="E10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>688</v>
+      </c>
+      <c r="B11" t="s">
+        <v>646</v>
+      </c>
+      <c r="C11" t="s">
+        <v>647</v>
+      </c>
+      <c r="D11">
+        <v>2</v>
+      </c>
+      <c r="E11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>688</v>
+      </c>
+      <c r="B12" t="s">
+        <v>648</v>
+      </c>
+      <c r="C12" t="s">
+        <v>649</v>
+      </c>
+      <c r="D12">
+        <v>2</v>
+      </c>
+      <c r="E12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>688</v>
+      </c>
+      <c r="B13" t="s">
+        <v>650</v>
+      </c>
+      <c r="C13" t="s">
+        <v>651</v>
+      </c>
+      <c r="D13">
+        <v>1</v>
+      </c>
+      <c r="E13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>688</v>
+      </c>
+      <c r="B14" t="s">
+        <v>652</v>
+      </c>
+      <c r="C14" t="s">
+        <v>653</v>
+      </c>
+      <c r="D14">
+        <v>3</v>
+      </c>
+      <c r="E14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>688</v>
+      </c>
+      <c r="B15" t="s">
+        <v>654</v>
+      </c>
+      <c r="C15" t="s">
+        <v>655</v>
+      </c>
+      <c r="D15">
+        <v>2</v>
+      </c>
+      <c r="E15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>688</v>
+      </c>
+      <c r="B16" t="s">
+        <v>656</v>
+      </c>
+      <c r="C16" t="s">
+        <v>657</v>
+      </c>
+      <c r="D16">
+        <v>2</v>
+      </c>
+      <c r="E16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>688</v>
+      </c>
+      <c r="B17" t="s">
+        <v>658</v>
+      </c>
+      <c r="C17" t="s">
+        <v>659</v>
+      </c>
+      <c r="D17">
+        <v>2</v>
+      </c>
+      <c r="E17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>688</v>
+      </c>
+      <c r="B18" t="s">
+        <v>660</v>
+      </c>
+      <c r="C18" t="s">
+        <v>661</v>
+      </c>
+      <c r="D18">
+        <v>3</v>
+      </c>
+      <c r="E18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>688</v>
+      </c>
+      <c r="B19" t="s">
+        <v>662</v>
+      </c>
+      <c r="C19" t="s">
+        <v>663</v>
+      </c>
+      <c r="D19">
+        <v>2</v>
+      </c>
+      <c r="E19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>688</v>
+      </c>
+      <c r="B20" t="s">
+        <v>664</v>
+      </c>
+      <c r="C20" t="s">
+        <v>665</v>
+      </c>
+      <c r="D20">
+        <v>2</v>
+      </c>
+      <c r="E20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>688</v>
+      </c>
+      <c r="B21" t="s">
+        <v>666</v>
+      </c>
+      <c r="C21" t="s">
+        <v>667</v>
+      </c>
+      <c r="D21">
+        <v>3</v>
+      </c>
+      <c r="E21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>688</v>
+      </c>
+      <c r="B22" t="s">
+        <v>668</v>
+      </c>
+      <c r="C22" t="s">
+        <v>669</v>
+      </c>
+      <c r="D22">
+        <v>3</v>
+      </c>
+      <c r="E22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>688</v>
+      </c>
+      <c r="B23" t="s">
+        <v>670</v>
+      </c>
+      <c r="C23" t="s">
+        <v>671</v>
+      </c>
+      <c r="D23">
+        <v>3</v>
+      </c>
+      <c r="E23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>688</v>
+      </c>
+      <c r="B24" t="s">
+        <v>672</v>
+      </c>
+      <c r="C24" t="s">
+        <v>673</v>
+      </c>
+      <c r="D24">
+        <v>2</v>
+      </c>
+      <c r="E24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>688</v>
+      </c>
+      <c r="B25" t="s">
+        <v>674</v>
+      </c>
+      <c r="C25" t="s">
+        <v>675</v>
+      </c>
+      <c r="D25">
+        <v>2</v>
+      </c>
+      <c r="E25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>688</v>
+      </c>
+      <c r="B26" t="s">
+        <v>676</v>
+      </c>
+      <c r="C26" t="s">
+        <v>677</v>
+      </c>
+      <c r="D26">
+        <v>2</v>
+      </c>
+      <c r="E26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>688</v>
+      </c>
+      <c r="B27" t="s">
+        <v>678</v>
+      </c>
+      <c r="C27" t="s">
+        <v>679</v>
+      </c>
+      <c r="D27">
+        <v>1</v>
+      </c>
+      <c r="E27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>688</v>
+      </c>
+      <c r="B28" t="s">
+        <v>680</v>
+      </c>
+      <c r="C28" t="s">
+        <v>681</v>
+      </c>
+      <c r="D28">
+        <v>1</v>
+      </c>
+      <c r="E28">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0206C416-5E99-4BF3-A01A-B219B8D6BE2C}">
   <dimension ref="A1:C106"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -14451,939 +17082,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F64D4604-6735-4BAB-A260-3ED112DA39AC}">
-  <dimension ref="A1:C89"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="12.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="9.85546875" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>128</v>
-      </c>
-      <c r="B1" t="s">
-        <v>344</v>
-      </c>
-      <c r="C1" t="s">
-        <v>345</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B2" t="s">
-        <v>129</v>
-      </c>
-      <c r="C2">
-        <v>0.05</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>5</v>
-      </c>
-      <c r="B3" t="s">
-        <v>131</v>
-      </c>
-      <c r="C3">
-        <v>999</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>5</v>
-      </c>
-      <c r="B4" t="s">
-        <v>132</v>
-      </c>
-      <c r="C4" s="5">
-        <v>1000000000</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>5</v>
-      </c>
-      <c r="B5" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>138</v>
-      </c>
-      <c r="B6" t="s">
-        <v>129</v>
-      </c>
-      <c r="C6">
-        <v>1E-4</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>138</v>
-      </c>
-      <c r="B7" t="s">
-        <v>131</v>
-      </c>
-      <c r="C7">
-        <v>999</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>138</v>
-      </c>
-      <c r="B8" t="s">
-        <v>132</v>
-      </c>
-      <c r="C8" s="5">
-        <v>1000000000</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>138</v>
-      </c>
-      <c r="B9" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>137</v>
-      </c>
-      <c r="B10" t="s">
-        <v>129</v>
-      </c>
-      <c r="C10">
-        <v>1E-4</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>137</v>
-      </c>
-      <c r="B11" t="s">
-        <v>131</v>
-      </c>
-      <c r="C11">
-        <v>999</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>137</v>
-      </c>
-      <c r="B12" t="s">
-        <v>132</v>
-      </c>
-      <c r="C12" s="5">
-        <v>1000000000</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>137</v>
-      </c>
-      <c r="B13" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>140</v>
-      </c>
-      <c r="B14" t="s">
-        <v>129</v>
-      </c>
-      <c r="C14">
-        <v>1E-4</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>140</v>
-      </c>
-      <c r="B15" t="s">
-        <v>131</v>
-      </c>
-      <c r="C15">
-        <v>999</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>140</v>
-      </c>
-      <c r="B16" t="s">
-        <v>132</v>
-      </c>
-      <c r="C16" s="5">
-        <v>1000000000</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>140</v>
-      </c>
-      <c r="B17" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>135</v>
-      </c>
-      <c r="B18" t="s">
-        <v>129</v>
-      </c>
-      <c r="C18">
-        <v>10.65</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>135</v>
-      </c>
-      <c r="B19" t="s">
-        <v>131</v>
-      </c>
-      <c r="C19">
-        <v>999</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>135</v>
-      </c>
-      <c r="B20" t="s">
-        <v>132</v>
-      </c>
-      <c r="C20" s="5">
-        <v>1000000000</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>135</v>
-      </c>
-      <c r="B21" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
-        <v>144</v>
-      </c>
-      <c r="B22" t="s">
-        <v>129</v>
-      </c>
-      <c r="C22">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
-        <v>144</v>
-      </c>
-      <c r="B23" t="s">
-        <v>131</v>
-      </c>
-      <c r="C23">
-        <v>999</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
-        <v>144</v>
-      </c>
-      <c r="B24" t="s">
-        <v>132</v>
-      </c>
-      <c r="C24" s="5">
-        <v>1000000000</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
-        <v>144</v>
-      </c>
-      <c r="B25" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
-        <v>57</v>
-      </c>
-      <c r="B26" t="s">
-        <v>129</v>
-      </c>
-      <c r="C26">
-        <v>1.83</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
-        <v>57</v>
-      </c>
-      <c r="B27" t="s">
-        <v>131</v>
-      </c>
-      <c r="C27">
-        <v>999</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
-        <v>57</v>
-      </c>
-      <c r="B28" t="s">
-        <v>132</v>
-      </c>
-      <c r="C28" s="5">
-        <v>1000000000</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
-        <v>57</v>
-      </c>
-      <c r="B29" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
-        <v>55</v>
-      </c>
-      <c r="B30" t="s">
-        <v>129</v>
-      </c>
-      <c r="C30">
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A31" t="s">
-        <v>55</v>
-      </c>
-      <c r="B31" t="s">
-        <v>131</v>
-      </c>
-      <c r="C31">
-        <v>999</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A32" t="s">
-        <v>55</v>
-      </c>
-      <c r="B32" t="s">
-        <v>132</v>
-      </c>
-      <c r="C32" s="5">
-        <v>1000000000</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A33" t="s">
-        <v>55</v>
-      </c>
-      <c r="B33" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A34" t="s">
-        <v>48</v>
-      </c>
-      <c r="B34" t="s">
-        <v>129</v>
-      </c>
-      <c r="C34">
-        <v>0.7</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A35" t="s">
-        <v>48</v>
-      </c>
-      <c r="B35" t="s">
-        <v>131</v>
-      </c>
-      <c r="C35">
-        <v>999</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A36" t="s">
-        <v>48</v>
-      </c>
-      <c r="B36" t="s">
-        <v>132</v>
-      </c>
-      <c r="C36" s="5">
-        <v>1000000000</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A37" t="s">
-        <v>48</v>
-      </c>
-      <c r="B37" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A38" t="s">
-        <v>58</v>
-      </c>
-      <c r="B38" t="s">
-        <v>129</v>
-      </c>
-      <c r="C38">
-        <v>2.6120000000000001</v>
-      </c>
-    </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A39" t="s">
-        <v>58</v>
-      </c>
-      <c r="B39" t="s">
-        <v>131</v>
-      </c>
-      <c r="C39">
-        <v>999</v>
-      </c>
-    </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A40" t="s">
-        <v>58</v>
-      </c>
-      <c r="B40" t="s">
-        <v>132</v>
-      </c>
-      <c r="C40" s="5">
-        <v>1000000000</v>
-      </c>
-    </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A41" t="s">
-        <v>58</v>
-      </c>
-      <c r="B41" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A42" t="s">
-        <v>133</v>
-      </c>
-      <c r="B42" t="s">
-        <v>129</v>
-      </c>
-      <c r="C42">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A43" t="s">
-        <v>133</v>
-      </c>
-      <c r="B43" t="s">
-        <v>131</v>
-      </c>
-      <c r="C43">
-        <v>999</v>
-      </c>
-    </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A44" t="s">
-        <v>133</v>
-      </c>
-      <c r="B44" t="s">
-        <v>132</v>
-      </c>
-      <c r="C44" s="5">
-        <v>1000000000</v>
-      </c>
-    </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A45" t="s">
-        <v>133</v>
-      </c>
-      <c r="B45" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A46" t="s">
-        <v>92</v>
-      </c>
-      <c r="B46" t="s">
-        <v>129</v>
-      </c>
-      <c r="C46">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A47" t="s">
-        <v>92</v>
-      </c>
-      <c r="B47" t="s">
-        <v>131</v>
-      </c>
-      <c r="C47">
-        <v>999</v>
-      </c>
-    </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A48" t="s">
-        <v>92</v>
-      </c>
-      <c r="B48" t="s">
-        <v>132</v>
-      </c>
-      <c r="C48" s="5">
-        <v>1000000000</v>
-      </c>
-    </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A49" t="s">
-        <v>92</v>
-      </c>
-      <c r="B49" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A50" t="s">
-        <v>139</v>
-      </c>
-      <c r="B50" t="s">
-        <v>129</v>
-      </c>
-      <c r="C50">
-        <v>1E-4</v>
-      </c>
-    </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A51" t="s">
-        <v>139</v>
-      </c>
-      <c r="B51" t="s">
-        <v>131</v>
-      </c>
-      <c r="C51">
-        <v>999</v>
-      </c>
-    </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A52" t="s">
-        <v>139</v>
-      </c>
-      <c r="B52" t="s">
-        <v>132</v>
-      </c>
-      <c r="C52" s="5">
-        <v>1000000000</v>
-      </c>
-    </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A53" t="s">
-        <v>139</v>
-      </c>
-      <c r="B53" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A54" t="s">
-        <v>141</v>
-      </c>
-      <c r="B54" t="s">
-        <v>129</v>
-      </c>
-      <c r="C54">
-        <v>1E-4</v>
-      </c>
-    </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A55" t="s">
-        <v>141</v>
-      </c>
-      <c r="B55" t="s">
-        <v>131</v>
-      </c>
-      <c r="C55">
-        <v>999</v>
-      </c>
-    </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A56" t="s">
-        <v>141</v>
-      </c>
-      <c r="B56" t="s">
-        <v>132</v>
-      </c>
-      <c r="C56" s="5">
-        <v>1000000000</v>
-      </c>
-    </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A57" t="s">
-        <v>141</v>
-      </c>
-      <c r="B57" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A58" t="s">
-        <v>64</v>
-      </c>
-      <c r="B58" t="s">
-        <v>129</v>
-      </c>
-      <c r="C58">
-        <v>1.3</v>
-      </c>
-    </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A59" t="s">
-        <v>64</v>
-      </c>
-      <c r="B59" t="s">
-        <v>131</v>
-      </c>
-      <c r="C59">
-        <v>999</v>
-      </c>
-    </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A60" t="s">
-        <v>64</v>
-      </c>
-      <c r="B60" t="s">
-        <v>132</v>
-      </c>
-      <c r="C60" s="5">
-        <v>1000000000</v>
-      </c>
-    </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A61" t="s">
-        <v>64</v>
-      </c>
-      <c r="B61" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A62" t="s">
-        <v>24</v>
-      </c>
-      <c r="B62" t="s">
-        <v>129</v>
-      </c>
-      <c r="C62">
-        <v>1.28</v>
-      </c>
-    </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A63" t="s">
-        <v>24</v>
-      </c>
-      <c r="B63" t="s">
-        <v>131</v>
-      </c>
-      <c r="C63">
-        <v>999</v>
-      </c>
-    </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A64" t="s">
-        <v>24</v>
-      </c>
-      <c r="B64" t="s">
-        <v>132</v>
-      </c>
-      <c r="C64" s="5">
-        <v>1000000000</v>
-      </c>
-    </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A65" t="s">
-        <v>24</v>
-      </c>
-      <c r="B65" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A66" t="s">
-        <v>613</v>
-      </c>
-      <c r="B66" t="s">
-        <v>129</v>
-      </c>
-      <c r="C66">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A67" t="s">
-        <v>613</v>
-      </c>
-      <c r="B67" t="s">
-        <v>131</v>
-      </c>
-      <c r="C67">
-        <v>999</v>
-      </c>
-    </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A68" t="s">
-        <v>613</v>
-      </c>
-      <c r="B68" t="s">
-        <v>132</v>
-      </c>
-      <c r="C68" s="5">
-        <v>1000000000</v>
-      </c>
-    </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A69" t="s">
-        <v>613</v>
-      </c>
-      <c r="B69" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A70" t="s">
-        <v>25</v>
-      </c>
-      <c r="B70" t="s">
-        <v>129</v>
-      </c>
-      <c r="C70">
-        <v>1E-4</v>
-      </c>
-    </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A71" t="s">
-        <v>25</v>
-      </c>
-      <c r="B71" t="s">
-        <v>131</v>
-      </c>
-      <c r="C71">
-        <v>999</v>
-      </c>
-    </row>
-    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A72" t="s">
-        <v>25</v>
-      </c>
-      <c r="B72" t="s">
-        <v>132</v>
-      </c>
-      <c r="C72" s="5">
-        <v>1000000000</v>
-      </c>
-    </row>
-    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A73" t="s">
-        <v>25</v>
-      </c>
-      <c r="B73" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A74" t="s">
-        <v>136</v>
-      </c>
-      <c r="B74" t="s">
-        <v>129</v>
-      </c>
-      <c r="C74">
-        <v>1E-4</v>
-      </c>
-    </row>
-    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A75" t="s">
-        <v>136</v>
-      </c>
-      <c r="B75" t="s">
-        <v>131</v>
-      </c>
-      <c r="C75">
-        <v>999</v>
-      </c>
-    </row>
-    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A76" t="s">
-        <v>136</v>
-      </c>
-      <c r="B76" t="s">
-        <v>132</v>
-      </c>
-      <c r="C76" s="5">
-        <v>1000000000</v>
-      </c>
-    </row>
-    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A77" t="s">
-        <v>136</v>
-      </c>
-      <c r="B77" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="78" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A78" t="s">
-        <v>134</v>
-      </c>
-      <c r="B78" t="s">
-        <v>129</v>
-      </c>
-      <c r="C78">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="79" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A79" t="s">
-        <v>134</v>
-      </c>
-      <c r="B79" t="s">
-        <v>131</v>
-      </c>
-      <c r="C79">
-        <v>999</v>
-      </c>
-    </row>
-    <row r="80" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A80" t="s">
-        <v>134</v>
-      </c>
-      <c r="B80" t="s">
-        <v>132</v>
-      </c>
-      <c r="C80" s="5">
-        <v>1000000000</v>
-      </c>
-    </row>
-    <row r="81" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A81" t="s">
-        <v>134</v>
-      </c>
-      <c r="B81" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="82" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A82" t="s">
-        <v>142</v>
-      </c>
-      <c r="B82" t="s">
-        <v>129</v>
-      </c>
-      <c r="C82">
-        <v>0.1</v>
-      </c>
-    </row>
-    <row r="83" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A83" t="s">
-        <v>142</v>
-      </c>
-      <c r="B83" t="s">
-        <v>131</v>
-      </c>
-      <c r="C83">
-        <v>999</v>
-      </c>
-    </row>
-    <row r="84" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A84" t="s">
-        <v>142</v>
-      </c>
-      <c r="B84" t="s">
-        <v>132</v>
-      </c>
-      <c r="C84" s="5">
-        <v>1000000000</v>
-      </c>
-    </row>
-    <row r="85" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A85" t="s">
-        <v>142</v>
-      </c>
-      <c r="B85" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="86" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A86" t="s">
-        <v>143</v>
-      </c>
-      <c r="B86" t="s">
-        <v>129</v>
-      </c>
-      <c r="C86">
-        <v>0.1</v>
-      </c>
-    </row>
-    <row r="87" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A87" t="s">
-        <v>143</v>
-      </c>
-      <c r="B87" t="s">
-        <v>131</v>
-      </c>
-      <c r="C87">
-        <v>999</v>
-      </c>
-    </row>
-    <row r="88" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A88" t="s">
-        <v>143</v>
-      </c>
-      <c r="B88" t="s">
-        <v>132</v>
-      </c>
-      <c r="C88" s="5">
-        <v>1000000000</v>
-      </c>
-    </row>
-    <row r="89" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A89" t="s">
-        <v>143</v>
-      </c>
-      <c r="B89" t="s">
-        <v>130</v>
-      </c>
-    </row>
-  </sheetData>
-  <autoFilter ref="A1:C1" xr:uid="{F64D4604-6735-4BAB-A260-3ED112DA39AC}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:C89">
-      <sortCondition ref="A1"/>
-    </sortState>
-  </autoFilter>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{97461BA3-2572-48E1-B51A-549B5CBBC0F1}">
   <dimension ref="A1:B7"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -15449,7 +17148,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:D1343"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -34268,7 +35967,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FEAC8083-8073-4708-9AE8-A894D58A1ECD}">
   <dimension ref="A1:AD313"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -44213,15 +45912,15 @@
         <v>0</v>
       </c>
       <c r="E259">
-        <f t="shared" ref="E259:E322" si="35">IF(B259="FUNGICIDES",D259*1,IF(B259="HERBICIDES",D259*1.2*1.33,IF(B259="GLYFOSAT",D259*1.33,IF(B259="INSECTICID",D259*1.33*2.5,"-"))))</f>
+        <f t="shared" ref="E259:E313" si="35">IF(B259="FUNGICIDES",D259*1,IF(B259="HERBICIDES",D259*1.2*1.33,IF(B259="GLYFOSAT",D259*1.33,IF(B259="INSECTICID",D259*1.33*2.5,"-"))))</f>
         <v>0</v>
       </c>
       <c r="F259">
-        <f t="shared" ref="F259:F322" si="36">E259*0.995^4</f>
+        <f t="shared" ref="F259:F313" si="36">E259*0.995^4</f>
         <v>0</v>
       </c>
       <c r="G259">
-        <f t="shared" ref="G259:G322" si="37">F259*0.9997^4</f>
+        <f t="shared" ref="G259:G313" si="37">F259*0.9997^4</f>
         <v>0</v>
       </c>
       <c r="H259">
@@ -44229,11 +45928,11 @@
         <v>0</v>
       </c>
       <c r="I259">
-        <f t="shared" ref="I259:I322" si="38">H259*0.995^5</f>
+        <f t="shared" ref="I259:I313" si="38">H259*0.995^5</f>
         <v>0</v>
       </c>
       <c r="J259">
-        <f t="shared" ref="J259:J322" si="39">I259*0.9997^5</f>
+        <f t="shared" ref="J259:J313" si="39">I259*0.9997^5</f>
         <v>0</v>
       </c>
       <c r="K259">
@@ -46385,7 +48084,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D959A23A-6549-4BFB-8CFE-8BFCAC8B0CB4}">
   <dimension ref="A1:D2155"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -76575,7 +78274,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9AC8E327-ABF8-4EDA-AC3F-CA18C56BB80A}">
   <dimension ref="A1:B40"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -76909,6 +78608,938 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F64D4604-6735-4BAB-A260-3ED112DA39AC}">
+  <dimension ref="A1:C89"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.85546875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>128</v>
+      </c>
+      <c r="B1" t="s">
+        <v>344</v>
+      </c>
+      <c r="C1" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2" t="s">
+        <v>129</v>
+      </c>
+      <c r="C2">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3" t="s">
+        <v>131</v>
+      </c>
+      <c r="C3">
+        <v>999</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4" t="s">
+        <v>132</v>
+      </c>
+      <c r="C4" s="5">
+        <v>1000000000</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>138</v>
+      </c>
+      <c r="B6" t="s">
+        <v>129</v>
+      </c>
+      <c r="C6">
+        <v>1E-4</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>138</v>
+      </c>
+      <c r="B7" t="s">
+        <v>131</v>
+      </c>
+      <c r="C7">
+        <v>999</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>138</v>
+      </c>
+      <c r="B8" t="s">
+        <v>132</v>
+      </c>
+      <c r="C8" s="5">
+        <v>1000000000</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>138</v>
+      </c>
+      <c r="B9" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>137</v>
+      </c>
+      <c r="B10" t="s">
+        <v>129</v>
+      </c>
+      <c r="C10">
+        <v>1E-4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>137</v>
+      </c>
+      <c r="B11" t="s">
+        <v>131</v>
+      </c>
+      <c r="C11">
+        <v>999</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>137</v>
+      </c>
+      <c r="B12" t="s">
+        <v>132</v>
+      </c>
+      <c r="C12" s="5">
+        <v>1000000000</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>137</v>
+      </c>
+      <c r="B13" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>140</v>
+      </c>
+      <c r="B14" t="s">
+        <v>129</v>
+      </c>
+      <c r="C14">
+        <v>1E-4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>140</v>
+      </c>
+      <c r="B15" t="s">
+        <v>131</v>
+      </c>
+      <c r="C15">
+        <v>999</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>140</v>
+      </c>
+      <c r="B16" t="s">
+        <v>132</v>
+      </c>
+      <c r="C16" s="5">
+        <v>1000000000</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>140</v>
+      </c>
+      <c r="B17" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>135</v>
+      </c>
+      <c r="B18" t="s">
+        <v>129</v>
+      </c>
+      <c r="C18">
+        <v>10.65</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>135</v>
+      </c>
+      <c r="B19" t="s">
+        <v>131</v>
+      </c>
+      <c r="C19">
+        <v>999</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>135</v>
+      </c>
+      <c r="B20" t="s">
+        <v>132</v>
+      </c>
+      <c r="C20" s="5">
+        <v>1000000000</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>135</v>
+      </c>
+      <c r="B21" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>144</v>
+      </c>
+      <c r="B22" t="s">
+        <v>129</v>
+      </c>
+      <c r="C22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>144</v>
+      </c>
+      <c r="B23" t="s">
+        <v>131</v>
+      </c>
+      <c r="C23">
+        <v>999</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>144</v>
+      </c>
+      <c r="B24" t="s">
+        <v>132</v>
+      </c>
+      <c r="C24" s="5">
+        <v>1000000000</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>144</v>
+      </c>
+      <c r="B25" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>57</v>
+      </c>
+      <c r="B26" t="s">
+        <v>129</v>
+      </c>
+      <c r="C26">
+        <v>1.83</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>57</v>
+      </c>
+      <c r="B27" t="s">
+        <v>131</v>
+      </c>
+      <c r="C27">
+        <v>999</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>57</v>
+      </c>
+      <c r="B28" t="s">
+        <v>132</v>
+      </c>
+      <c r="C28" s="5">
+        <v>1000000000</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>57</v>
+      </c>
+      <c r="B29" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>55</v>
+      </c>
+      <c r="B30" t="s">
+        <v>129</v>
+      </c>
+      <c r="C30">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>55</v>
+      </c>
+      <c r="B31" t="s">
+        <v>131</v>
+      </c>
+      <c r="C31">
+        <v>999</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>55</v>
+      </c>
+      <c r="B32" t="s">
+        <v>132</v>
+      </c>
+      <c r="C32" s="5">
+        <v>1000000000</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>55</v>
+      </c>
+      <c r="B33" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>48</v>
+      </c>
+      <c r="B34" t="s">
+        <v>129</v>
+      </c>
+      <c r="C34">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>48</v>
+      </c>
+      <c r="B35" t="s">
+        <v>131</v>
+      </c>
+      <c r="C35">
+        <v>999</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>48</v>
+      </c>
+      <c r="B36" t="s">
+        <v>132</v>
+      </c>
+      <c r="C36" s="5">
+        <v>1000000000</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>48</v>
+      </c>
+      <c r="B37" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>58</v>
+      </c>
+      <c r="B38" t="s">
+        <v>129</v>
+      </c>
+      <c r="C38">
+        <v>2.6120000000000001</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>58</v>
+      </c>
+      <c r="B39" t="s">
+        <v>131</v>
+      </c>
+      <c r="C39">
+        <v>999</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>58</v>
+      </c>
+      <c r="B40" t="s">
+        <v>132</v>
+      </c>
+      <c r="C40" s="5">
+        <v>1000000000</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>58</v>
+      </c>
+      <c r="B41" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>133</v>
+      </c>
+      <c r="B42" t="s">
+        <v>129</v>
+      </c>
+      <c r="C42">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>133</v>
+      </c>
+      <c r="B43" t="s">
+        <v>131</v>
+      </c>
+      <c r="C43">
+        <v>999</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>133</v>
+      </c>
+      <c r="B44" t="s">
+        <v>132</v>
+      </c>
+      <c r="C44" s="5">
+        <v>1000000000</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>133</v>
+      </c>
+      <c r="B45" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>92</v>
+      </c>
+      <c r="B46" t="s">
+        <v>129</v>
+      </c>
+      <c r="C46">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>92</v>
+      </c>
+      <c r="B47" t="s">
+        <v>131</v>
+      </c>
+      <c r="C47">
+        <v>999</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>92</v>
+      </c>
+      <c r="B48" t="s">
+        <v>132</v>
+      </c>
+      <c r="C48" s="5">
+        <v>1000000000</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>92</v>
+      </c>
+      <c r="B49" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>139</v>
+      </c>
+      <c r="B50" t="s">
+        <v>129</v>
+      </c>
+      <c r="C50">
+        <v>1E-4</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>139</v>
+      </c>
+      <c r="B51" t="s">
+        <v>131</v>
+      </c>
+      <c r="C51">
+        <v>999</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>139</v>
+      </c>
+      <c r="B52" t="s">
+        <v>132</v>
+      </c>
+      <c r="C52" s="5">
+        <v>1000000000</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>139</v>
+      </c>
+      <c r="B53" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>141</v>
+      </c>
+      <c r="B54" t="s">
+        <v>129</v>
+      </c>
+      <c r="C54">
+        <v>1E-4</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>141</v>
+      </c>
+      <c r="B55" t="s">
+        <v>131</v>
+      </c>
+      <c r="C55">
+        <v>999</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>141</v>
+      </c>
+      <c r="B56" t="s">
+        <v>132</v>
+      </c>
+      <c r="C56" s="5">
+        <v>1000000000</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>141</v>
+      </c>
+      <c r="B57" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>64</v>
+      </c>
+      <c r="B58" t="s">
+        <v>129</v>
+      </c>
+      <c r="C58">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>64</v>
+      </c>
+      <c r="B59" t="s">
+        <v>131</v>
+      </c>
+      <c r="C59">
+        <v>999</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>64</v>
+      </c>
+      <c r="B60" t="s">
+        <v>132</v>
+      </c>
+      <c r="C60" s="5">
+        <v>1000000000</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>64</v>
+      </c>
+      <c r="B61" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>24</v>
+      </c>
+      <c r="B62" t="s">
+        <v>129</v>
+      </c>
+      <c r="C62">
+        <v>1.28</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>24</v>
+      </c>
+      <c r="B63" t="s">
+        <v>131</v>
+      </c>
+      <c r="C63">
+        <v>999</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>24</v>
+      </c>
+      <c r="B64" t="s">
+        <v>132</v>
+      </c>
+      <c r="C64" s="5">
+        <v>1000000000</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>24</v>
+      </c>
+      <c r="B65" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>613</v>
+      </c>
+      <c r="B66" t="s">
+        <v>129</v>
+      </c>
+      <c r="C66">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>613</v>
+      </c>
+      <c r="B67" t="s">
+        <v>131</v>
+      </c>
+      <c r="C67">
+        <v>999</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>613</v>
+      </c>
+      <c r="B68" t="s">
+        <v>132</v>
+      </c>
+      <c r="C68" s="5">
+        <v>1000000000</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>613</v>
+      </c>
+      <c r="B69" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>25</v>
+      </c>
+      <c r="B70" t="s">
+        <v>129</v>
+      </c>
+      <c r="C70">
+        <v>1E-4</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
+        <v>25</v>
+      </c>
+      <c r="B71" t="s">
+        <v>131</v>
+      </c>
+      <c r="C71">
+        <v>999</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
+        <v>25</v>
+      </c>
+      <c r="B72" t="s">
+        <v>132</v>
+      </c>
+      <c r="C72" s="5">
+        <v>1000000000</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
+        <v>25</v>
+      </c>
+      <c r="B73" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
+        <v>136</v>
+      </c>
+      <c r="B74" t="s">
+        <v>129</v>
+      </c>
+      <c r="C74">
+        <v>1E-4</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
+        <v>136</v>
+      </c>
+      <c r="B75" t="s">
+        <v>131</v>
+      </c>
+      <c r="C75">
+        <v>999</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
+        <v>136</v>
+      </c>
+      <c r="B76" t="s">
+        <v>132</v>
+      </c>
+      <c r="C76" s="5">
+        <v>1000000000</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
+        <v>136</v>
+      </c>
+      <c r="B77" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
+        <v>134</v>
+      </c>
+      <c r="B78" t="s">
+        <v>129</v>
+      </c>
+      <c r="C78">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
+        <v>134</v>
+      </c>
+      <c r="B79" t="s">
+        <v>131</v>
+      </c>
+      <c r="C79">
+        <v>999</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A80" t="s">
+        <v>134</v>
+      </c>
+      <c r="B80" t="s">
+        <v>132</v>
+      </c>
+      <c r="C80" s="5">
+        <v>1000000000</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
+        <v>134</v>
+      </c>
+      <c r="B81" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="82" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A82" t="s">
+        <v>142</v>
+      </c>
+      <c r="B82" t="s">
+        <v>129</v>
+      </c>
+      <c r="C82">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="83" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A83" t="s">
+        <v>142</v>
+      </c>
+      <c r="B83" t="s">
+        <v>131</v>
+      </c>
+      <c r="C83">
+        <v>999</v>
+      </c>
+    </row>
+    <row r="84" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A84" t="s">
+        <v>142</v>
+      </c>
+      <c r="B84" t="s">
+        <v>132</v>
+      </c>
+      <c r="C84" s="5">
+        <v>1000000000</v>
+      </c>
+    </row>
+    <row r="85" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A85" t="s">
+        <v>142</v>
+      </c>
+      <c r="B85" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="86" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A86" t="s">
+        <v>143</v>
+      </c>
+      <c r="B86" t="s">
+        <v>129</v>
+      </c>
+      <c r="C86">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="87" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A87" t="s">
+        <v>143</v>
+      </c>
+      <c r="B87" t="s">
+        <v>131</v>
+      </c>
+      <c r="C87">
+        <v>999</v>
+      </c>
+    </row>
+    <row r="88" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A88" t="s">
+        <v>143</v>
+      </c>
+      <c r="B88" t="s">
+        <v>132</v>
+      </c>
+      <c r="C88" s="5">
+        <v>1000000000</v>
+      </c>
+    </row>
+    <row r="89" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A89" t="s">
+        <v>143</v>
+      </c>
+      <c r="B89" t="s">
+        <v>130</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:C1" xr:uid="{F64D4604-6735-4BAB-A260-3ED112DA39AC}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:C89">
+      <sortCondition ref="A1"/>
+    </sortState>
+  </autoFilter>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BBA1EDEA-E1C9-4B25-ADDE-06B6FB916511}">
   <dimension ref="A1:D131"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -78679,7 +81310,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{32D95BEB-DABC-4410-B5D8-F33F079CD882}">
   <dimension ref="A1:C93"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -79716,7 +82347,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F58BA3FF-82B5-4D1D-96F2-636FBA087A67}">
   <dimension ref="A1:C70"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -80499,7 +83130,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{464F1F31-BD57-477B-98CB-70C5803E8A70}">
   <dimension ref="A1:AB82"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -87586,7 +90217,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4D45AA73-608A-47C5-BDC1-A448A6C42A89}">
   <dimension ref="A1:D346"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -91827,7 +94458,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{62097657-CBE5-4411-876F-D67B21CD28D3}">
   <dimension ref="A1:F126"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -93091,2027 +95722,4 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F02DEA1A-0627-4FA3-8C95-326A86063434}">
-  <dimension ref="A1:C196"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="12.28515625" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>263</v>
-      </c>
-      <c r="B1" t="s">
-        <v>344</v>
-      </c>
-      <c r="C1" t="s">
-        <v>345</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>307</v>
-      </c>
-      <c r="B2" t="s">
-        <v>129</v>
-      </c>
-      <c r="C2">
-        <v>1.89</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>307</v>
-      </c>
-      <c r="B3" t="s">
-        <v>130</v>
-      </c>
-      <c r="C3">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>307</v>
-      </c>
-      <c r="B4" t="s">
-        <v>131</v>
-      </c>
-      <c r="C4">
-        <v>-0.9</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>307</v>
-      </c>
-      <c r="B5" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>307</v>
-      </c>
-      <c r="B6" t="s">
-        <v>132</v>
-      </c>
-      <c r="C6">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>308</v>
-      </c>
-      <c r="B7" t="s">
-        <v>129</v>
-      </c>
-      <c r="C7">
-        <v>1.79</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>308</v>
-      </c>
-      <c r="B8" t="s">
-        <v>130</v>
-      </c>
-      <c r="C8">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>308</v>
-      </c>
-      <c r="B9" t="s">
-        <v>131</v>
-      </c>
-      <c r="C9">
-        <v>-0.9</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>308</v>
-      </c>
-      <c r="B10" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>308</v>
-      </c>
-      <c r="B11" t="s">
-        <v>132</v>
-      </c>
-      <c r="C11">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>309</v>
-      </c>
-      <c r="B12" t="s">
-        <v>129</v>
-      </c>
-      <c r="C12">
-        <v>5.0199999999999996</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>309</v>
-      </c>
-      <c r="B13" t="s">
-        <v>130</v>
-      </c>
-      <c r="C13">
-        <v>450</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>309</v>
-      </c>
-      <c r="B14" t="s">
-        <v>131</v>
-      </c>
-      <c r="C14">
-        <v>-0.9</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>309</v>
-      </c>
-      <c r="B15" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>309</v>
-      </c>
-      <c r="B16" t="s">
-        <v>132</v>
-      </c>
-      <c r="C16">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>84</v>
-      </c>
-      <c r="B17" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>84</v>
-      </c>
-      <c r="B18" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>84</v>
-      </c>
-      <c r="B19" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>84</v>
-      </c>
-      <c r="B20" t="s">
-        <v>145</v>
-      </c>
-      <c r="C20">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>84</v>
-      </c>
-      <c r="B21" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
-        <v>310</v>
-      </c>
-      <c r="B22" t="s">
-        <v>129</v>
-      </c>
-      <c r="C22">
-        <v>14.6</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
-        <v>310</v>
-      </c>
-      <c r="B23" t="s">
-        <v>130</v>
-      </c>
-      <c r="C23">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
-        <v>310</v>
-      </c>
-      <c r="B24" t="s">
-        <v>131</v>
-      </c>
-      <c r="C24">
-        <v>-0.9</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
-        <v>310</v>
-      </c>
-      <c r="B25" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
-        <v>310</v>
-      </c>
-      <c r="B26" t="s">
-        <v>132</v>
-      </c>
-      <c r="C26">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
-        <v>311</v>
-      </c>
-      <c r="B27" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
-        <v>311</v>
-      </c>
-      <c r="B28" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
-        <v>311</v>
-      </c>
-      <c r="B29" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
-        <v>311</v>
-      </c>
-      <c r="B30" t="s">
-        <v>145</v>
-      </c>
-      <c r="C30">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A31" t="s">
-        <v>311</v>
-      </c>
-      <c r="B31" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A32" t="s">
-        <v>312</v>
-      </c>
-      <c r="B32" t="s">
-        <v>129</v>
-      </c>
-      <c r="C32">
-        <v>1.35</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A33" t="s">
-        <v>312</v>
-      </c>
-      <c r="B33" t="s">
-        <v>130</v>
-      </c>
-      <c r="C33">
-        <v>850</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A34" t="s">
-        <v>312</v>
-      </c>
-      <c r="B34" t="s">
-        <v>131</v>
-      </c>
-      <c r="C34">
-        <v>-0.9</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A35" t="s">
-        <v>312</v>
-      </c>
-      <c r="B35" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A36" t="s">
-        <v>312</v>
-      </c>
-      <c r="B36" t="s">
-        <v>132</v>
-      </c>
-      <c r="C36">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A37" t="s">
-        <v>313</v>
-      </c>
-      <c r="B37" t="s">
-        <v>129</v>
-      </c>
-      <c r="C37">
-        <v>5.45</v>
-      </c>
-    </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A38" t="s">
-        <v>313</v>
-      </c>
-      <c r="B38" t="s">
-        <v>130</v>
-      </c>
-      <c r="C38">
-        <v>402</v>
-      </c>
-    </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A39" t="s">
-        <v>313</v>
-      </c>
-      <c r="B39" t="s">
-        <v>131</v>
-      </c>
-      <c r="C39">
-        <v>-0.9</v>
-      </c>
-    </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A40" t="s">
-        <v>313</v>
-      </c>
-      <c r="B40" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A41" t="s">
-        <v>313</v>
-      </c>
-      <c r="B41" t="s">
-        <v>132</v>
-      </c>
-      <c r="C41">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A42" t="s">
-        <v>314</v>
-      </c>
-      <c r="B42" t="s">
-        <v>129</v>
-      </c>
-      <c r="C42">
-        <v>16.13</v>
-      </c>
-    </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A43" t="s">
-        <v>314</v>
-      </c>
-      <c r="B43" t="s">
-        <v>130</v>
-      </c>
-      <c r="C43">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A44" t="s">
-        <v>314</v>
-      </c>
-      <c r="B44" t="s">
-        <v>131</v>
-      </c>
-      <c r="C44">
-        <v>-0.9</v>
-      </c>
-    </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A45" t="s">
-        <v>314</v>
-      </c>
-      <c r="B45" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A46" t="s">
-        <v>314</v>
-      </c>
-      <c r="B46" t="s">
-        <v>132</v>
-      </c>
-      <c r="C46">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A47" t="s">
-        <v>315</v>
-      </c>
-      <c r="B47" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A48" t="s">
-        <v>315</v>
-      </c>
-      <c r="B48" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A49" t="s">
-        <v>315</v>
-      </c>
-      <c r="B49" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A50" t="s">
-        <v>315</v>
-      </c>
-      <c r="B50" t="s">
-        <v>145</v>
-      </c>
-      <c r="C50">
-        <v>363</v>
-      </c>
-    </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A51" t="s">
-        <v>315</v>
-      </c>
-      <c r="B51" t="s">
-        <v>132</v>
-      </c>
-      <c r="C51">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A52" t="s">
-        <v>316</v>
-      </c>
-      <c r="B52" t="s">
-        <v>129</v>
-      </c>
-      <c r="C52">
-        <v>6.33</v>
-      </c>
-    </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A53" t="s">
-        <v>316</v>
-      </c>
-      <c r="B53" t="s">
-        <v>130</v>
-      </c>
-      <c r="C53">
-        <v>923</v>
-      </c>
-    </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A54" t="s">
-        <v>316</v>
-      </c>
-      <c r="B54" t="s">
-        <v>131</v>
-      </c>
-      <c r="C54">
-        <v>-0.9</v>
-      </c>
-    </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A55" t="s">
-        <v>316</v>
-      </c>
-      <c r="B55" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A56" t="s">
-        <v>316</v>
-      </c>
-      <c r="B56" t="s">
-        <v>132</v>
-      </c>
-      <c r="C56">
-        <v>1500</v>
-      </c>
-    </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A57" t="s">
-        <v>317</v>
-      </c>
-      <c r="B57" t="s">
-        <v>129</v>
-      </c>
-      <c r="C57">
-        <v>46.07</v>
-      </c>
-    </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A58" t="s">
-        <v>317</v>
-      </c>
-      <c r="B58" t="s">
-        <v>130</v>
-      </c>
-      <c r="C58">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A59" t="s">
-        <v>317</v>
-      </c>
-      <c r="B59" t="s">
-        <v>131</v>
-      </c>
-      <c r="C59">
-        <v>-0.9</v>
-      </c>
-    </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A60" t="s">
-        <v>317</v>
-      </c>
-      <c r="B60" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A61" t="s">
-        <v>317</v>
-      </c>
-      <c r="B61" t="s">
-        <v>132</v>
-      </c>
-      <c r="C61">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A62" t="s">
-        <v>318</v>
-      </c>
-      <c r="B62" t="s">
-        <v>129</v>
-      </c>
-      <c r="C62">
-        <v>49.47</v>
-      </c>
-    </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A63" t="s">
-        <v>318</v>
-      </c>
-      <c r="B63" t="s">
-        <v>130</v>
-      </c>
-      <c r="C63">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A64" t="s">
-        <v>318</v>
-      </c>
-      <c r="B64" t="s">
-        <v>131</v>
-      </c>
-      <c r="C64">
-        <v>-0.9</v>
-      </c>
-    </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A65" t="s">
-        <v>318</v>
-      </c>
-      <c r="B65" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A66" t="s">
-        <v>318</v>
-      </c>
-      <c r="B66" t="s">
-        <v>132</v>
-      </c>
-      <c r="C66">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A67" t="s">
-        <v>319</v>
-      </c>
-      <c r="B67" t="s">
-        <v>129</v>
-      </c>
-      <c r="C67">
-        <v>36.020000000000003</v>
-      </c>
-    </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A68" t="s">
-        <v>319</v>
-      </c>
-      <c r="B68" t="s">
-        <v>130</v>
-      </c>
-      <c r="C68">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A69" t="s">
-        <v>319</v>
-      </c>
-      <c r="B69" t="s">
-        <v>131</v>
-      </c>
-      <c r="C69">
-        <v>-0.9</v>
-      </c>
-    </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A70" t="s">
-        <v>319</v>
-      </c>
-      <c r="B70" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A71" t="s">
-        <v>319</v>
-      </c>
-      <c r="B71" t="s">
-        <v>132</v>
-      </c>
-      <c r="C71">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A72" t="s">
-        <v>320</v>
-      </c>
-      <c r="B72" t="s">
-        <v>129</v>
-      </c>
-      <c r="C72">
-        <v>36.47</v>
-      </c>
-    </row>
-    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A73" t="s">
-        <v>320</v>
-      </c>
-      <c r="B73" t="s">
-        <v>130</v>
-      </c>
-      <c r="C73">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A74" t="s">
-        <v>320</v>
-      </c>
-      <c r="B74" t="s">
-        <v>131</v>
-      </c>
-      <c r="C74">
-        <v>-0.9</v>
-      </c>
-    </row>
-    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A75" t="s">
-        <v>320</v>
-      </c>
-      <c r="B75" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A76" t="s">
-        <v>320</v>
-      </c>
-      <c r="B76" t="s">
-        <v>132</v>
-      </c>
-      <c r="C76">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A77" t="s">
-        <v>321</v>
-      </c>
-      <c r="B77" t="s">
-        <v>129</v>
-      </c>
-      <c r="C77">
-        <v>54.81</v>
-      </c>
-    </row>
-    <row r="78" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A78" t="s">
-        <v>321</v>
-      </c>
-      <c r="B78" t="s">
-        <v>130</v>
-      </c>
-      <c r="C78">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="79" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A79" t="s">
-        <v>321</v>
-      </c>
-      <c r="B79" t="s">
-        <v>131</v>
-      </c>
-      <c r="C79">
-        <v>-0.9</v>
-      </c>
-    </row>
-    <row r="80" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A80" t="s">
-        <v>321</v>
-      </c>
-      <c r="B80" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="81" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A81" t="s">
-        <v>321</v>
-      </c>
-      <c r="B81" t="s">
-        <v>132</v>
-      </c>
-      <c r="C81">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="82" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A82" t="s">
-        <v>322</v>
-      </c>
-      <c r="B82" t="s">
-        <v>129</v>
-      </c>
-      <c r="C82">
-        <v>25.98</v>
-      </c>
-    </row>
-    <row r="83" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A83" t="s">
-        <v>322</v>
-      </c>
-      <c r="B83" t="s">
-        <v>130</v>
-      </c>
-      <c r="C83">
-        <v>295</v>
-      </c>
-    </row>
-    <row r="84" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A84" t="s">
-        <v>322</v>
-      </c>
-      <c r="B84" t="s">
-        <v>131</v>
-      </c>
-      <c r="C84">
-        <v>-0.9</v>
-      </c>
-    </row>
-    <row r="85" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A85" t="s">
-        <v>322</v>
-      </c>
-      <c r="B85" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="86" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A86" t="s">
-        <v>322</v>
-      </c>
-      <c r="B86" t="s">
-        <v>132</v>
-      </c>
-      <c r="C86">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="87" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A87" t="s">
-        <v>323</v>
-      </c>
-      <c r="B87" t="s">
-        <v>129</v>
-      </c>
-      <c r="C87">
-        <v>33.619999999999997</v>
-      </c>
-    </row>
-    <row r="88" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A88" t="s">
-        <v>323</v>
-      </c>
-      <c r="B88" t="s">
-        <v>130</v>
-      </c>
-      <c r="C88">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="89" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A89" t="s">
-        <v>323</v>
-      </c>
-      <c r="B89" t="s">
-        <v>131</v>
-      </c>
-      <c r="C89">
-        <v>-0.9</v>
-      </c>
-    </row>
-    <row r="90" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A90" t="s">
-        <v>323</v>
-      </c>
-      <c r="B90" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="91" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A91" t="s">
-        <v>323</v>
-      </c>
-      <c r="B91" t="s">
-        <v>132</v>
-      </c>
-      <c r="C91">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="92" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A92" t="s">
-        <v>324</v>
-      </c>
-      <c r="B92" t="s">
-        <v>129</v>
-      </c>
-      <c r="C92">
-        <v>64.87</v>
-      </c>
-    </row>
-    <row r="93" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A93" t="s">
-        <v>324</v>
-      </c>
-      <c r="B93" t="s">
-        <v>130</v>
-      </c>
-      <c r="C93">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="94" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A94" t="s">
-        <v>324</v>
-      </c>
-      <c r="B94" t="s">
-        <v>131</v>
-      </c>
-      <c r="C94">
-        <v>-0.9</v>
-      </c>
-    </row>
-    <row r="95" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A95" t="s">
-        <v>324</v>
-      </c>
-      <c r="B95" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="96" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A96" t="s">
-        <v>324</v>
-      </c>
-      <c r="B96" t="s">
-        <v>132</v>
-      </c>
-      <c r="C96">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="97" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A97" t="s">
-        <v>325</v>
-      </c>
-      <c r="B97" t="s">
-        <v>129</v>
-      </c>
-      <c r="C97">
-        <v>56.95</v>
-      </c>
-    </row>
-    <row r="98" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A98" t="s">
-        <v>325</v>
-      </c>
-      <c r="B98" t="s">
-        <v>130</v>
-      </c>
-      <c r="C98">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="99" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A99" t="s">
-        <v>325</v>
-      </c>
-      <c r="B99" t="s">
-        <v>131</v>
-      </c>
-      <c r="C99">
-        <v>-0.9</v>
-      </c>
-    </row>
-    <row r="100" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A100" t="s">
-        <v>325</v>
-      </c>
-      <c r="B100" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="101" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A101" t="s">
-        <v>325</v>
-      </c>
-      <c r="B101" t="s">
-        <v>132</v>
-      </c>
-      <c r="C101">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="102" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A102" t="s">
-        <v>326</v>
-      </c>
-      <c r="B102" t="s">
-        <v>129</v>
-      </c>
-      <c r="C102">
-        <v>37.479999999999997</v>
-      </c>
-    </row>
-    <row r="103" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A103" t="s">
-        <v>326</v>
-      </c>
-      <c r="B103" t="s">
-        <v>130</v>
-      </c>
-      <c r="C103">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="104" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A104" t="s">
-        <v>326</v>
-      </c>
-      <c r="B104" t="s">
-        <v>131</v>
-      </c>
-      <c r="C104">
-        <v>-0.9</v>
-      </c>
-    </row>
-    <row r="105" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A105" t="s">
-        <v>326</v>
-      </c>
-      <c r="B105" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="106" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A106" t="s">
-        <v>326</v>
-      </c>
-      <c r="B106" t="s">
-        <v>132</v>
-      </c>
-      <c r="C106">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="107" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A107" t="s">
-        <v>327</v>
-      </c>
-      <c r="B107" t="s">
-        <v>129</v>
-      </c>
-      <c r="C107">
-        <v>12.64</v>
-      </c>
-    </row>
-    <row r="108" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A108" t="s">
-        <v>327</v>
-      </c>
-      <c r="B108" t="s">
-        <v>130</v>
-      </c>
-      <c r="C108">
-        <v>940</v>
-      </c>
-    </row>
-    <row r="109" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A109" t="s">
-        <v>327</v>
-      </c>
-      <c r="B109" t="s">
-        <v>131</v>
-      </c>
-      <c r="C109">
-        <v>-0.9</v>
-      </c>
-    </row>
-    <row r="110" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A110" t="s">
-        <v>327</v>
-      </c>
-      <c r="B110" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="111" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A111" t="s">
-        <v>327</v>
-      </c>
-      <c r="B111" t="s">
-        <v>132</v>
-      </c>
-      <c r="C111">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="112" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A112" t="s">
-        <v>328</v>
-      </c>
-      <c r="B112" t="s">
-        <v>129</v>
-      </c>
-      <c r="C112">
-        <v>12.64</v>
-      </c>
-    </row>
-    <row r="113" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A113" t="s">
-        <v>328</v>
-      </c>
-      <c r="B113" t="s">
-        <v>130</v>
-      </c>
-      <c r="C113">
-        <v>845</v>
-      </c>
-    </row>
-    <row r="114" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A114" t="s">
-        <v>328</v>
-      </c>
-      <c r="B114" t="s">
-        <v>131</v>
-      </c>
-      <c r="C114">
-        <v>-0.9</v>
-      </c>
-    </row>
-    <row r="115" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A115" t="s">
-        <v>328</v>
-      </c>
-      <c r="B115" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="116" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A116" t="s">
-        <v>328</v>
-      </c>
-      <c r="B116" t="s">
-        <v>132</v>
-      </c>
-      <c r="C116">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="117" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A117" t="s">
-        <v>329</v>
-      </c>
-      <c r="B117" t="s">
-        <v>129</v>
-      </c>
-      <c r="C117">
-        <v>0.15</v>
-      </c>
-    </row>
-    <row r="118" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A118" t="s">
-        <v>329</v>
-      </c>
-      <c r="B118" t="s">
-        <v>130</v>
-      </c>
-      <c r="C118">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="119" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A119" t="s">
-        <v>329</v>
-      </c>
-      <c r="B119" t="s">
-        <v>131</v>
-      </c>
-      <c r="C119">
-        <v>-0.9</v>
-      </c>
-    </row>
-    <row r="120" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A120" t="s">
-        <v>329</v>
-      </c>
-      <c r="B120" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="121" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A121" t="s">
-        <v>329</v>
-      </c>
-      <c r="B121" t="s">
-        <v>132</v>
-      </c>
-      <c r="C121">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="122" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A122" t="s">
-        <v>268</v>
-      </c>
-      <c r="B122" t="s">
-        <v>129</v>
-      </c>
-      <c r="C122">
-        <v>1.75</v>
-      </c>
-    </row>
-    <row r="123" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A123" t="s">
-        <v>268</v>
-      </c>
-      <c r="B123" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="124" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A124" t="s">
-        <v>268</v>
-      </c>
-      <c r="B124" t="s">
-        <v>131</v>
-      </c>
-      <c r="C124">
-        <v>-999</v>
-      </c>
-    </row>
-    <row r="125" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A125" t="s">
-        <v>268</v>
-      </c>
-      <c r="B125" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="126" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A126" t="s">
-        <v>268</v>
-      </c>
-      <c r="B126" t="s">
-        <v>132</v>
-      </c>
-      <c r="C126">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="127" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A127" t="s">
-        <v>330</v>
-      </c>
-      <c r="B127" t="s">
-        <v>129</v>
-      </c>
-      <c r="C127">
-        <v>0.8</v>
-      </c>
-    </row>
-    <row r="128" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A128" t="s">
-        <v>330</v>
-      </c>
-      <c r="B128" t="s">
-        <v>130</v>
-      </c>
-      <c r="C128">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="129" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A129" t="s">
-        <v>330</v>
-      </c>
-      <c r="B129" t="s">
-        <v>131</v>
-      </c>
-      <c r="C129">
-        <v>-999</v>
-      </c>
-    </row>
-    <row r="130" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A130" t="s">
-        <v>330</v>
-      </c>
-      <c r="B130" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="131" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A131" t="s">
-        <v>330</v>
-      </c>
-      <c r="B131" t="s">
-        <v>132</v>
-      </c>
-      <c r="C131">
-        <v>5000</v>
-      </c>
-    </row>
-    <row r="132" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A132" t="s">
-        <v>331</v>
-      </c>
-      <c r="B132" t="s">
-        <v>129</v>
-      </c>
-      <c r="C132">
-        <v>5.2</v>
-      </c>
-    </row>
-    <row r="133" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A133" t="s">
-        <v>331</v>
-      </c>
-      <c r="B133" t="s">
-        <v>130</v>
-      </c>
-      <c r="C133">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="134" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A134" t="s">
-        <v>331</v>
-      </c>
-      <c r="B134" t="s">
-        <v>131</v>
-      </c>
-      <c r="C134">
-        <v>-999</v>
-      </c>
-    </row>
-    <row r="135" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A135" t="s">
-        <v>331</v>
-      </c>
-      <c r="B135" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="136" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A136" t="s">
-        <v>331</v>
-      </c>
-      <c r="B136" t="s">
-        <v>132</v>
-      </c>
-      <c r="C136">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="137" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A137" t="s">
-        <v>332</v>
-      </c>
-      <c r="B137" t="s">
-        <v>129</v>
-      </c>
-      <c r="C137">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="138" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A138" t="s">
-        <v>332</v>
-      </c>
-      <c r="B138" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="139" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A139" t="s">
-        <v>332</v>
-      </c>
-      <c r="B139" t="s">
-        <v>131</v>
-      </c>
-      <c r="C139">
-        <v>-999</v>
-      </c>
-    </row>
-    <row r="140" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A140" t="s">
-        <v>332</v>
-      </c>
-      <c r="B140" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="141" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A141" t="s">
-        <v>332</v>
-      </c>
-      <c r="B141" t="s">
-        <v>132</v>
-      </c>
-      <c r="C141">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="142" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A142" t="s">
-        <v>333</v>
-      </c>
-      <c r="B142" t="s">
-        <v>129</v>
-      </c>
-      <c r="C142">
-        <v>2.2000000000000002</v>
-      </c>
-    </row>
-    <row r="143" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A143" t="s">
-        <v>333</v>
-      </c>
-      <c r="B143" t="s">
-        <v>130</v>
-      </c>
-      <c r="C143">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="144" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A144" t="s">
-        <v>333</v>
-      </c>
-      <c r="B144" t="s">
-        <v>131</v>
-      </c>
-      <c r="C144">
-        <v>-0.1</v>
-      </c>
-    </row>
-    <row r="145" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A145" t="s">
-        <v>333</v>
-      </c>
-      <c r="B145" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="146" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A146" t="s">
-        <v>333</v>
-      </c>
-      <c r="B146" t="s">
-        <v>132</v>
-      </c>
-      <c r="C146">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="147" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A147" t="s">
-        <v>334</v>
-      </c>
-      <c r="B147" t="s">
-        <v>129</v>
-      </c>
-      <c r="C147">
-        <v>0.7</v>
-      </c>
-    </row>
-    <row r="148" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A148" t="s">
-        <v>334</v>
-      </c>
-      <c r="B148" t="s">
-        <v>130</v>
-      </c>
-      <c r="C148">
-        <v>460</v>
-      </c>
-    </row>
-    <row r="149" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A149" t="s">
-        <v>334</v>
-      </c>
-      <c r="B149" t="s">
-        <v>131</v>
-      </c>
-      <c r="C149">
-        <v>-0.5</v>
-      </c>
-    </row>
-    <row r="150" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A150" t="s">
-        <v>334</v>
-      </c>
-      <c r="B150" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="151" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A151" t="s">
-        <v>334</v>
-      </c>
-      <c r="B151" t="s">
-        <v>132</v>
-      </c>
-      <c r="C151">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="152" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A152" t="s">
-        <v>335</v>
-      </c>
-      <c r="B152" t="s">
-        <v>129</v>
-      </c>
-      <c r="C152">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="153" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A153" t="s">
-        <v>335</v>
-      </c>
-      <c r="B153" t="s">
-        <v>130</v>
-      </c>
-      <c r="C153">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="154" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A154" t="s">
-        <v>335</v>
-      </c>
-      <c r="B154" t="s">
-        <v>131</v>
-      </c>
-      <c r="C154">
-        <v>-0.5</v>
-      </c>
-    </row>
-    <row r="155" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A155" t="s">
-        <v>335</v>
-      </c>
-      <c r="B155" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="156" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A156" t="s">
-        <v>335</v>
-      </c>
-      <c r="B156" t="s">
-        <v>132</v>
-      </c>
-      <c r="C156">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="157" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A157" t="s">
-        <v>336</v>
-      </c>
-      <c r="B157" t="s">
-        <v>129</v>
-      </c>
-      <c r="C157">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="158" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A158" t="s">
-        <v>336</v>
-      </c>
-      <c r="B158" t="s">
-        <v>130</v>
-      </c>
-      <c r="C158">
-        <v>4.3</v>
-      </c>
-    </row>
-    <row r="159" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A159" t="s">
-        <v>336</v>
-      </c>
-      <c r="B159" t="s">
-        <v>131</v>
-      </c>
-      <c r="C159">
-        <v>-0.5</v>
-      </c>
-    </row>
-    <row r="160" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A160" t="s">
-        <v>336</v>
-      </c>
-      <c r="B160" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="161" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A161" t="s">
-        <v>336</v>
-      </c>
-      <c r="B161" t="s">
-        <v>132</v>
-      </c>
-      <c r="C161">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="162" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A162" t="s">
-        <v>337</v>
-      </c>
-      <c r="B162" t="s">
-        <v>129</v>
-      </c>
-      <c r="C162">
-        <v>2.5</v>
-      </c>
-    </row>
-    <row r="163" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A163" t="s">
-        <v>337</v>
-      </c>
-      <c r="B163" t="s">
-        <v>130</v>
-      </c>
-      <c r="C163">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="164" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A164" t="s">
-        <v>337</v>
-      </c>
-      <c r="B164" t="s">
-        <v>131</v>
-      </c>
-      <c r="C164">
-        <v>-0.5</v>
-      </c>
-    </row>
-    <row r="165" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A165" t="s">
-        <v>337</v>
-      </c>
-      <c r="B165" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="166" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A166" t="s">
-        <v>337</v>
-      </c>
-      <c r="B166" t="s">
-        <v>132</v>
-      </c>
-      <c r="C166">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="167" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A167" t="s">
-        <v>338</v>
-      </c>
-      <c r="B167" t="s">
-        <v>129</v>
-      </c>
-      <c r="C167">
-        <v>10.5</v>
-      </c>
-    </row>
-    <row r="168" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A168" t="s">
-        <v>338</v>
-      </c>
-      <c r="B168" t="s">
-        <v>130</v>
-      </c>
-      <c r="C168">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="169" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A169" t="s">
-        <v>338</v>
-      </c>
-      <c r="B169" t="s">
-        <v>131</v>
-      </c>
-      <c r="C169">
-        <v>-0.5</v>
-      </c>
-    </row>
-    <row r="170" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A170" t="s">
-        <v>338</v>
-      </c>
-      <c r="B170" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="171" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A171" t="s">
-        <v>338</v>
-      </c>
-      <c r="B171" t="s">
-        <v>132</v>
-      </c>
-      <c r="C171">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="172" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A172" t="s">
-        <v>339</v>
-      </c>
-      <c r="B172" t="s">
-        <v>129</v>
-      </c>
-      <c r="C172">
-        <v>1E-3</v>
-      </c>
-    </row>
-    <row r="173" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A173" t="s">
-        <v>339</v>
-      </c>
-      <c r="B173" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="174" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A174" t="s">
-        <v>339</v>
-      </c>
-      <c r="B174" t="s">
-        <v>131</v>
-      </c>
-      <c r="C174">
-        <v>-999</v>
-      </c>
-    </row>
-    <row r="175" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A175" t="s">
-        <v>339</v>
-      </c>
-      <c r="B175" t="s">
-        <v>145</v>
-      </c>
-      <c r="C175">
-        <v>38.83</v>
-      </c>
-    </row>
-    <row r="176" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A176" t="s">
-        <v>339</v>
-      </c>
-      <c r="B176" t="s">
-        <v>132</v>
-      </c>
-      <c r="C176">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="177" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A177" t="s">
-        <v>340</v>
-      </c>
-      <c r="B177" t="s">
-        <v>129</v>
-      </c>
-      <c r="C177">
-        <v>1E-3</v>
-      </c>
-    </row>
-    <row r="178" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A178" t="s">
-        <v>340</v>
-      </c>
-      <c r="B178" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="179" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A179" t="s">
-        <v>340</v>
-      </c>
-      <c r="B179" t="s">
-        <v>131</v>
-      </c>
-      <c r="C179">
-        <v>-999</v>
-      </c>
-    </row>
-    <row r="180" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A180" t="s">
-        <v>340</v>
-      </c>
-      <c r="B180" t="s">
-        <v>145</v>
-      </c>
-      <c r="C180">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="181" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A181" t="s">
-        <v>340</v>
-      </c>
-      <c r="B181" t="s">
-        <v>132</v>
-      </c>
-      <c r="C181">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="182" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A182" t="s">
-        <v>341</v>
-      </c>
-      <c r="B182" t="s">
-        <v>129</v>
-      </c>
-      <c r="C182">
-        <v>1E-3</v>
-      </c>
-    </row>
-    <row r="183" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A183" t="s">
-        <v>341</v>
-      </c>
-      <c r="B183" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="184" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A184" t="s">
-        <v>341</v>
-      </c>
-      <c r="B184" t="s">
-        <v>131</v>
-      </c>
-      <c r="C184">
-        <v>-999</v>
-      </c>
-    </row>
-    <row r="185" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A185" t="s">
-        <v>341</v>
-      </c>
-      <c r="B185" t="s">
-        <v>145</v>
-      </c>
-      <c r="C185">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="186" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A186" t="s">
-        <v>341</v>
-      </c>
-      <c r="B186" t="s">
-        <v>132</v>
-      </c>
-      <c r="C186">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="187" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A187" t="s">
-        <v>342</v>
-      </c>
-      <c r="B187" t="s">
-        <v>129</v>
-      </c>
-      <c r="C187">
-        <v>1E-3</v>
-      </c>
-    </row>
-    <row r="188" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A188" t="s">
-        <v>342</v>
-      </c>
-      <c r="B188" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="189" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A189" t="s">
-        <v>342</v>
-      </c>
-      <c r="B189" t="s">
-        <v>131</v>
-      </c>
-      <c r="C189">
-        <v>-999</v>
-      </c>
-    </row>
-    <row r="190" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A190" t="s">
-        <v>342</v>
-      </c>
-      <c r="B190" t="s">
-        <v>145</v>
-      </c>
-      <c r="C190">
-        <v>262</v>
-      </c>
-    </row>
-    <row r="191" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A191" t="s">
-        <v>342</v>
-      </c>
-      <c r="B191" t="s">
-        <v>132</v>
-      </c>
-      <c r="C191">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="192" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A192" t="s">
-        <v>343</v>
-      </c>
-      <c r="B192" t="s">
-        <v>129</v>
-      </c>
-      <c r="C192">
-        <v>1E-3</v>
-      </c>
-    </row>
-    <row r="193" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A193" t="s">
-        <v>343</v>
-      </c>
-      <c r="B193" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="194" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A194" t="s">
-        <v>343</v>
-      </c>
-      <c r="B194" t="s">
-        <v>131</v>
-      </c>
-      <c r="C194">
-        <v>-999</v>
-      </c>
-    </row>
-    <row r="195" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A195" t="s">
-        <v>343</v>
-      </c>
-      <c r="B195" t="s">
-        <v>145</v>
-      </c>
-      <c r="C195">
-        <v>1028</v>
-      </c>
-    </row>
-    <row r="196" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A196" t="s">
-        <v>343</v>
-      </c>
-      <c r="B196" t="s">
-        <v>132</v>
-      </c>
-      <c r="C196">
-        <v>8000</v>
-      </c>
-    </row>
-  </sheetData>
-  <autoFilter ref="A1:C196" xr:uid="{F02DEA1A-0627-4FA3-8C95-326A86063434}"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>
--- a/data/data.xlsx
+++ b/data/data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Cecilia\Documents\Modellering\SASM\Github\SASM\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A263B727-EA24-4787-AEA9-B479BEBD3EAD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB227237-D8BB-4B95-A538-C17E70F4B6C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="878" firstSheet="8" activeTab="20" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="878" firstSheet="3" activeTab="16" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="index" sheetId="44" r:id="rId1"/>
@@ -29,14 +29,15 @@
     <sheet name="ECR(R,CR,IP)" sheetId="32" r:id="rId14"/>
     <sheet name="ECR2(R,CR,IP)" sheetId="37" r:id="rId15"/>
     <sheet name="ECR3(R,CR,IP)" sheetId="38" r:id="rId16"/>
-    <sheet name="MANURE(AS,IP)" sheetId="34" r:id="rId17"/>
-    <sheet name="NSUB(AS,SR)" sheetId="35" r:id="rId18"/>
-    <sheet name="NUTRIENT(P,NUTX)" sheetId="36" r:id="rId19"/>
-    <sheet name="POP(R)" sheetId="40" r:id="rId20"/>
-    <sheet name="PRODCOEFC_SA" sheetId="1" r:id="rId21"/>
-    <sheet name="PRODCOEFC2_PO" sheetId="42" r:id="rId22"/>
-    <sheet name="PRODCOEFL_SA" sheetId="5" r:id="rId23"/>
-    <sheet name="UT(IP)" sheetId="41" r:id="rId24"/>
+    <sheet name="histFrac(SR,IS)" sheetId="45" r:id="rId17"/>
+    <sheet name="MANURE(AS,IP)" sheetId="34" r:id="rId18"/>
+    <sheet name="NSUB(AS,SR)" sheetId="35" r:id="rId19"/>
+    <sheet name="NUTRIENT(P,NUTX)" sheetId="36" r:id="rId20"/>
+    <sheet name="POP(R)" sheetId="40" r:id="rId21"/>
+    <sheet name="PRODCOEFC_SA" sheetId="1" r:id="rId22"/>
+    <sheet name="PRODCOEFC2_PO" sheetId="42" r:id="rId23"/>
+    <sheet name="PRODCOEFL_SA" sheetId="5" r:id="rId24"/>
+    <sheet name="UT(IP)" sheetId="41" r:id="rId25"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'BIN(IN,SDP)'!$A$1:$C$1</definedName>
@@ -47,9 +48,9 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'BPSI_SA(SA,PS)'!$A$1:$C$49</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'CONST(IP,AS)'!$A$1:$C$178</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="13" hidden="1">'ECR(R,CR,IP)'!$A$1:$D$98</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="20" hidden="1">PRODCOEFC_SA!$A$1:$D$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="21" hidden="1">PRODCOEFC2_PO!$A$1:$D$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="22" hidden="1">PRODCOEFL_SA!$A$1:$D$2155</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="21" hidden="1">PRODCOEFC_SA!$A$1:$D$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="22" hidden="1">PRODCOEFC2_PO!$A$1:$D$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="23" hidden="1">PRODCOEFL_SA!$A$1:$D$2155</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -69,7 +70,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16594" uniqueCount="570">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16683" uniqueCount="576">
   <si>
     <t>AS</t>
   </si>
@@ -1625,139 +1626,70 @@
     <t xml:space="preserve">PRODCOEFC_SA   </t>
   </si>
   <si>
-    <t xml:space="preserve"> PRODCOEFC_SA!A2     </t>
-  </si>
-  <si>
     <t xml:space="preserve">PRODCOEFC2_PO  </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> PRODCOEFC2_PO!A2    </t>
   </si>
   <si>
     <t xml:space="preserve">PRODCOEFL_SA   </t>
   </si>
   <si>
-    <t xml:space="preserve"> PRODCOEFL_SA!A2     </t>
-  </si>
-  <si>
     <t xml:space="preserve">BIN            </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> BIN(IN,SDP)!A2      </t>
   </si>
   <si>
     <t xml:space="preserve">BIR            </t>
   </si>
   <si>
-    <t xml:space="preserve"> BIR(R,IR,SDP)!A2    </t>
-  </si>
-  <si>
     <t xml:space="preserve">BIRF           </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> BIRF(IR,R)!A2       </t>
   </si>
   <si>
     <t xml:space="preserve">BIRI           </t>
   </si>
   <si>
-    <t xml:space="preserve"> BIRI(IR,R)!A2       </t>
-  </si>
-  <si>
     <t xml:space="preserve">BISFA          </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> BISFA(SR,IS)!A1     </t>
   </si>
   <si>
     <t xml:space="preserve">BMR            </t>
   </si>
   <si>
-    <t xml:space="preserve"> BMR(R,PR,TRD)!A2    </t>
-  </si>
-  <si>
     <t xml:space="preserve">BPN            </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> BPN(PN,SDP)!A2      </t>
   </si>
   <si>
     <t xml:space="preserve">BPRN           </t>
   </si>
   <si>
-    <t xml:space="preserve"> BPRN(PR,SDP)!A2     </t>
-  </si>
-  <si>
     <t xml:space="preserve">BPSI_SA        </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> BPSI_SA(SA,PS)!A2   </t>
   </si>
   <si>
     <t xml:space="preserve">BXR            </t>
   </si>
   <si>
-    <t xml:space="preserve"> BXR(R,PR,TRD)!A2    </t>
-  </si>
-  <si>
     <t xml:space="preserve">DT             </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> DT(RS,RD)!A2        </t>
   </si>
   <si>
     <t xml:space="preserve">CONST          </t>
   </si>
   <si>
-    <t xml:space="preserve"> CONST(IP,AS)!A2     </t>
-  </si>
-  <si>
     <t xml:space="preserve">ECR            </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> ECR(R,CR,IP)!A2     </t>
   </si>
   <si>
     <t xml:space="preserve">ECR2           </t>
   </si>
   <si>
-    <t xml:space="preserve"> ECR2(R,CR,IP)!A2    </t>
-  </si>
-  <si>
     <t xml:space="preserve">ECR3           </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> ECR3(R,CR,IP)!A2    </t>
   </si>
   <si>
     <t xml:space="preserve">MANURE         </t>
   </si>
   <si>
-    <t xml:space="preserve"> MANURE(AS,IP)!A2    </t>
-  </si>
-  <si>
     <t xml:space="preserve">NSUB           </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> NSUB(AS,SR)!A2      </t>
   </si>
   <si>
     <t xml:space="preserve">NUTRIENT       </t>
   </si>
   <si>
-    <t xml:space="preserve"> NUTRIENT(P,NUTX)!A2 </t>
-  </si>
-  <si>
     <t xml:space="preserve">POP            </t>
   </si>
   <si>
-    <t xml:space="preserve"> POP(R)!A2           </t>
-  </si>
-  <si>
     <t xml:space="preserve">UT             </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> UT(IP)!A2           </t>
   </si>
   <si>
     <t>range</t>
@@ -1780,11 +1712,102 @@
   <si>
     <t>par</t>
   </si>
+  <si>
+    <t>histCropland</t>
+  </si>
+  <si>
+    <t>histPermPasture</t>
+  </si>
+  <si>
+    <t>histPermChalet</t>
+  </si>
+  <si>
+    <t>histPermMeadow</t>
+  </si>
+  <si>
+    <t>histFrac</t>
+  </si>
+  <si>
+    <t>PRODCOEFC_SA!A2</t>
+  </si>
+  <si>
+    <t>PRODCOEFC2_PO!A2</t>
+  </si>
+  <si>
+    <t>PRODCOEFL_SA!A2</t>
+  </si>
+  <si>
+    <t>BIN(IN,SDP)!A2</t>
+  </si>
+  <si>
+    <t>BIR(R,IR,SDP)!A2</t>
+  </si>
+  <si>
+    <t>BIRF(IR,R)!A2</t>
+  </si>
+  <si>
+    <t>BIRI(IR,R)!A2</t>
+  </si>
+  <si>
+    <t>BISFA(SR,IS)!A1</t>
+  </si>
+  <si>
+    <t>BMR(R,PR,TRD)!A2</t>
+  </si>
+  <si>
+    <t>BPN(PN,SDP)!A2</t>
+  </si>
+  <si>
+    <t>BPRN(PR,SDP)!A2</t>
+  </si>
+  <si>
+    <t>BPSI_SA(SA,PS)!A2</t>
+  </si>
+  <si>
+    <t>BXR(R,PR,TRD)!A2</t>
+  </si>
+  <si>
+    <t>DT(RS,RD)!A2</t>
+  </si>
+  <si>
+    <t>CONST(IP,AS)!A2</t>
+  </si>
+  <si>
+    <t>ECR(R,CR,IP)!A2</t>
+  </si>
+  <si>
+    <t>ECR2(R,CR,IP)!A2</t>
+  </si>
+  <si>
+    <t>ECR3(R,CR,IP)!A2</t>
+  </si>
+  <si>
+    <t>MANURE(AS,IP)!A2</t>
+  </si>
+  <si>
+    <t>NSUB(AS,SR)!A2</t>
+  </si>
+  <si>
+    <t>NUTRIENT(P,NUTX)!A2</t>
+  </si>
+  <si>
+    <t>POP(R)!A2</t>
+  </si>
+  <si>
+    <t>UT(IP)!A2</t>
+  </si>
+  <si>
+    <t>histFrac(SR,IS)!A1</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.000"/>
+    <numFmt numFmtId="165" formatCode="0.00000"/>
+  </numFmts>
   <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -1855,7 +1878,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
@@ -1866,7 +1889,8 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2169,7 +2193,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FC09F416-B83A-444C-8E2A-32773041705C}">
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E29"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.7109375" customWidth="1"/>
@@ -2179,35 +2203,35 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>567</v>
+        <v>544</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
-        <v>568</v>
+        <v>545</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>566</v>
+        <v>543</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>563</v>
+        <v>540</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>564</v>
+        <v>541</v>
       </c>
       <c r="E5" s="7" t="s">
-        <v>565</v>
+        <v>542</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>569</v>
+        <v>546</v>
       </c>
       <c r="B6" t="s">
         <v>517</v>
       </c>
       <c r="C6" t="s">
-        <v>518</v>
+        <v>552</v>
       </c>
       <c r="D6">
         <v>3</v>
@@ -2218,13 +2242,13 @@
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>569</v>
+        <v>546</v>
       </c>
       <c r="B7" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="C7" t="s">
-        <v>520</v>
+        <v>553</v>
       </c>
       <c r="D7">
         <v>3</v>
@@ -2235,13 +2259,13 @@
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>569</v>
+        <v>546</v>
       </c>
       <c r="B8" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="C8" t="s">
-        <v>522</v>
+        <v>554</v>
       </c>
       <c r="D8">
         <v>3</v>
@@ -2252,13 +2276,13 @@
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>569</v>
+        <v>546</v>
       </c>
       <c r="B9" t="s">
-        <v>523</v>
+        <v>520</v>
       </c>
       <c r="C9" t="s">
-        <v>524</v>
+        <v>555</v>
       </c>
       <c r="D9">
         <v>2</v>
@@ -2269,13 +2293,13 @@
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>569</v>
+        <v>546</v>
       </c>
       <c r="B10" t="s">
-        <v>525</v>
+        <v>521</v>
       </c>
       <c r="C10" t="s">
-        <v>526</v>
+        <v>556</v>
       </c>
       <c r="D10">
         <v>3</v>
@@ -2286,13 +2310,13 @@
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>569</v>
+        <v>546</v>
       </c>
       <c r="B11" t="s">
-        <v>527</v>
+        <v>522</v>
       </c>
       <c r="C11" t="s">
-        <v>528</v>
+        <v>557</v>
       </c>
       <c r="D11">
         <v>2</v>
@@ -2303,13 +2327,13 @@
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>569</v>
+        <v>546</v>
       </c>
       <c r="B12" t="s">
-        <v>529</v>
+        <v>523</v>
       </c>
       <c r="C12" t="s">
-        <v>530</v>
+        <v>558</v>
       </c>
       <c r="D12">
         <v>2</v>
@@ -2320,13 +2344,13 @@
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>569</v>
+        <v>546</v>
       </c>
       <c r="B13" t="s">
-        <v>531</v>
+        <v>524</v>
       </c>
       <c r="C13" t="s">
-        <v>532</v>
+        <v>559</v>
       </c>
       <c r="D13">
         <v>1</v>
@@ -2337,13 +2361,13 @@
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>569</v>
+        <v>546</v>
       </c>
       <c r="B14" t="s">
-        <v>533</v>
+        <v>525</v>
       </c>
       <c r="C14" t="s">
-        <v>534</v>
+        <v>560</v>
       </c>
       <c r="D14">
         <v>3</v>
@@ -2354,13 +2378,13 @@
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>569</v>
+        <v>546</v>
       </c>
       <c r="B15" t="s">
-        <v>535</v>
+        <v>526</v>
       </c>
       <c r="C15" t="s">
-        <v>536</v>
+        <v>561</v>
       </c>
       <c r="D15">
         <v>2</v>
@@ -2371,13 +2395,13 @@
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>569</v>
+        <v>546</v>
       </c>
       <c r="B16" t="s">
-        <v>537</v>
+        <v>527</v>
       </c>
       <c r="C16" t="s">
-        <v>538</v>
+        <v>562</v>
       </c>
       <c r="D16">
         <v>2</v>
@@ -2388,13 +2412,13 @@
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>569</v>
+        <v>546</v>
       </c>
       <c r="B17" t="s">
-        <v>539</v>
+        <v>528</v>
       </c>
       <c r="C17" t="s">
-        <v>540</v>
+        <v>563</v>
       </c>
       <c r="D17">
         <v>2</v>
@@ -2405,13 +2429,13 @@
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>569</v>
+        <v>546</v>
       </c>
       <c r="B18" t="s">
-        <v>541</v>
+        <v>529</v>
       </c>
       <c r="C18" t="s">
-        <v>542</v>
+        <v>564</v>
       </c>
       <c r="D18">
         <v>3</v>
@@ -2422,13 +2446,13 @@
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>569</v>
+        <v>546</v>
       </c>
       <c r="B19" t="s">
-        <v>543</v>
+        <v>530</v>
       </c>
       <c r="C19" t="s">
-        <v>544</v>
+        <v>565</v>
       </c>
       <c r="D19">
         <v>2</v>
@@ -2439,13 +2463,13 @@
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>569</v>
+        <v>546</v>
       </c>
       <c r="B20" t="s">
-        <v>545</v>
+        <v>531</v>
       </c>
       <c r="C20" t="s">
-        <v>546</v>
+        <v>566</v>
       </c>
       <c r="D20">
         <v>2</v>
@@ -2456,13 +2480,13 @@
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>569</v>
+        <v>546</v>
       </c>
       <c r="B21" t="s">
-        <v>547</v>
+        <v>532</v>
       </c>
       <c r="C21" t="s">
-        <v>548</v>
+        <v>567</v>
       </c>
       <c r="D21">
         <v>3</v>
@@ -2473,13 +2497,13 @@
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>569</v>
+        <v>546</v>
       </c>
       <c r="B22" t="s">
-        <v>549</v>
+        <v>533</v>
       </c>
       <c r="C22" t="s">
-        <v>550</v>
+        <v>568</v>
       </c>
       <c r="D22">
         <v>3</v>
@@ -2490,13 +2514,13 @@
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
+        <v>546</v>
+      </c>
+      <c r="B23" t="s">
+        <v>534</v>
+      </c>
+      <c r="C23" t="s">
         <v>569</v>
-      </c>
-      <c r="B23" t="s">
-        <v>551</v>
-      </c>
-      <c r="C23" t="s">
-        <v>552</v>
       </c>
       <c r="D23">
         <v>3</v>
@@ -2507,30 +2531,30 @@
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>569</v>
+        <v>546</v>
       </c>
       <c r="B24" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
       <c r="C24" t="s">
-        <v>554</v>
+        <v>575</v>
       </c>
       <c r="D24">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E24">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>569</v>
+        <v>546</v>
       </c>
       <c r="B25" t="s">
-        <v>555</v>
+        <v>535</v>
       </c>
       <c r="C25" t="s">
-        <v>556</v>
+        <v>570</v>
       </c>
       <c r="D25">
         <v>2</v>
@@ -2541,13 +2565,13 @@
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>569</v>
+        <v>546</v>
       </c>
       <c r="B26" t="s">
-        <v>557</v>
+        <v>536</v>
       </c>
       <c r="C26" t="s">
-        <v>558</v>
+        <v>571</v>
       </c>
       <c r="D26">
         <v>2</v>
@@ -2558,16 +2582,16 @@
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>569</v>
+        <v>546</v>
       </c>
       <c r="B27" t="s">
-        <v>559</v>
+        <v>537</v>
       </c>
       <c r="C27" t="s">
-        <v>560</v>
+        <v>572</v>
       </c>
       <c r="D27">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E27">
         <v>0</v>
@@ -2575,18 +2599,35 @@
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>569</v>
+        <v>546</v>
       </c>
       <c r="B28" t="s">
-        <v>561</v>
+        <v>538</v>
       </c>
       <c r="C28" t="s">
-        <v>562</v>
+        <v>573</v>
       </c>
       <c r="D28">
         <v>1</v>
       </c>
       <c r="E28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>546</v>
+      </c>
+      <c r="B29" t="s">
+        <v>539</v>
+      </c>
+      <c r="C29" t="s">
+        <v>574</v>
+      </c>
+      <c r="D29">
+        <v>1</v>
+      </c>
+      <c r="E29">
         <v>0</v>
       </c>
     </row>
@@ -8085,7 +8126,7 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.85546875" style="8" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.85546875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="12.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -8093,7 +8134,7 @@
       <c r="A1" t="s">
         <v>146</v>
       </c>
-      <c r="B1" s="8" t="s">
+      <c r="B1" t="s">
         <v>369</v>
       </c>
       <c r="C1" t="s">
@@ -8107,7 +8148,7 @@
       <c r="A2" t="s">
         <v>159</v>
       </c>
-      <c r="B2" s="8" t="s">
+      <c r="B2" t="s">
         <v>382</v>
       </c>
       <c r="C2" t="s">
@@ -8121,7 +8162,7 @@
       <c r="A3" t="s">
         <v>159</v>
       </c>
-      <c r="B3" s="8" t="s">
+      <c r="B3" t="s">
         <v>382</v>
       </c>
       <c r="C3" t="s">
@@ -8135,7 +8176,7 @@
       <c r="A4" t="s">
         <v>159</v>
       </c>
-      <c r="B4" s="8" t="s">
+      <c r="B4" t="s">
         <v>382</v>
       </c>
       <c r="C4" t="s">
@@ -8149,7 +8190,7 @@
       <c r="A5" t="s">
         <v>159</v>
       </c>
-      <c r="B5" s="8" t="s">
+      <c r="B5" t="s">
         <v>382</v>
       </c>
       <c r="C5" t="s">
@@ -8163,7 +8204,7 @@
       <c r="A6" t="s">
         <v>159</v>
       </c>
-      <c r="B6" s="8" t="s">
+      <c r="B6" t="s">
         <v>401</v>
       </c>
       <c r="C6" t="s">
@@ -8177,7 +8218,7 @@
       <c r="A7" t="s">
         <v>159</v>
       </c>
-      <c r="B7" s="8" t="s">
+      <c r="B7" t="s">
         <v>401</v>
       </c>
       <c r="C7" t="s">
@@ -8191,7 +8232,7 @@
       <c r="A8" t="s">
         <v>159</v>
       </c>
-      <c r="B8" s="8" t="s">
+      <c r="B8" t="s">
         <v>370</v>
       </c>
       <c r="C8" t="s">
@@ -8205,7 +8246,7 @@
       <c r="A9" t="s">
         <v>159</v>
       </c>
-      <c r="B9" s="8" t="s">
+      <c r="B9" t="s">
         <v>370</v>
       </c>
       <c r="C9" t="s">
@@ -8219,7 +8260,7 @@
       <c r="A10" t="s">
         <v>159</v>
       </c>
-      <c r="B10" s="8" t="s">
+      <c r="B10" t="s">
         <v>370</v>
       </c>
       <c r="C10" t="s">
@@ -8233,7 +8274,7 @@
       <c r="A11" t="s">
         <v>159</v>
       </c>
-      <c r="B11" s="8" t="s">
+      <c r="B11" t="s">
         <v>370</v>
       </c>
       <c r="C11" t="s">
@@ -8247,7 +8288,7 @@
       <c r="A12" t="s">
         <v>159</v>
       </c>
-      <c r="B12" s="8" t="s">
+      <c r="B12" t="s">
         <v>378</v>
       </c>
       <c r="C12" t="s">
@@ -8261,7 +8302,7 @@
       <c r="A13" t="s">
         <v>159</v>
       </c>
-      <c r="B13" s="8" t="s">
+      <c r="B13" t="s">
         <v>378</v>
       </c>
       <c r="C13" t="s">
@@ -8275,7 +8316,7 @@
       <c r="A14" t="s">
         <v>159</v>
       </c>
-      <c r="B14" s="8" t="s">
+      <c r="B14" t="s">
         <v>378</v>
       </c>
       <c r="C14" t="s">
@@ -8289,7 +8330,7 @@
       <c r="A15" t="s">
         <v>159</v>
       </c>
-      <c r="B15" s="8" t="s">
+      <c r="B15" t="s">
         <v>378</v>
       </c>
       <c r="C15" t="s">
@@ -8303,7 +8344,7 @@
       <c r="A16" t="s">
         <v>159</v>
       </c>
-      <c r="B16" s="8" t="s">
+      <c r="B16" t="s">
         <v>378</v>
       </c>
       <c r="C16" t="s">
@@ -8317,7 +8358,7 @@
       <c r="A17" t="s">
         <v>159</v>
       </c>
-      <c r="B17" s="8" t="s">
+      <c r="B17" t="s">
         <v>402</v>
       </c>
       <c r="C17" t="s">
@@ -8331,7 +8372,7 @@
       <c r="A18" t="s">
         <v>159</v>
       </c>
-      <c r="B18" s="8" t="s">
+      <c r="B18" t="s">
         <v>402</v>
       </c>
       <c r="C18" t="s">
@@ -8345,7 +8386,7 @@
       <c r="A19" t="s">
         <v>159</v>
       </c>
-      <c r="B19" s="8" t="s">
+      <c r="B19" t="s">
         <v>371</v>
       </c>
       <c r="C19" t="s">
@@ -8359,7 +8400,7 @@
       <c r="A20" t="s">
         <v>159</v>
       </c>
-      <c r="B20" s="8" t="s">
+      <c r="B20" t="s">
         <v>371</v>
       </c>
       <c r="C20" t="s">
@@ -8373,7 +8414,7 @@
       <c r="A21" t="s">
         <v>159</v>
       </c>
-      <c r="B21" s="8" t="s">
+      <c r="B21" t="s">
         <v>371</v>
       </c>
       <c r="C21" t="s">
@@ -8387,7 +8428,7 @@
       <c r="A22" t="s">
         <v>159</v>
       </c>
-      <c r="B22" s="8" t="s">
+      <c r="B22" t="s">
         <v>371</v>
       </c>
       <c r="C22" t="s">
@@ -8401,7 +8442,7 @@
       <c r="A23" t="s">
         <v>159</v>
       </c>
-      <c r="B23" s="8" t="s">
+      <c r="B23" t="s">
         <v>377</v>
       </c>
       <c r="C23" t="s">
@@ -8415,7 +8456,7 @@
       <c r="A24" t="s">
         <v>159</v>
       </c>
-      <c r="B24" s="8" t="s">
+      <c r="B24" t="s">
         <v>377</v>
       </c>
       <c r="C24" t="s">
@@ -8429,7 +8470,7 @@
       <c r="A25" t="s">
         <v>159</v>
       </c>
-      <c r="B25" s="8" t="s">
+      <c r="B25" t="s">
         <v>377</v>
       </c>
       <c r="C25" t="s">
@@ -8443,7 +8484,7 @@
       <c r="A26" t="s">
         <v>159</v>
       </c>
-      <c r="B26" s="8" t="s">
+      <c r="B26" t="s">
         <v>377</v>
       </c>
       <c r="C26" t="s">
@@ -8457,7 +8498,7 @@
       <c r="A27" t="s">
         <v>159</v>
       </c>
-      <c r="B27" s="8" t="s">
+      <c r="B27" t="s">
         <v>377</v>
       </c>
       <c r="C27" t="s">
@@ -8471,7 +8512,7 @@
       <c r="A28" t="s">
         <v>159</v>
       </c>
-      <c r="B28" s="8" t="s">
+      <c r="B28" t="s">
         <v>379</v>
       </c>
       <c r="C28" t="s">
@@ -8485,7 +8526,7 @@
       <c r="A29" t="s">
         <v>159</v>
       </c>
-      <c r="B29" s="8" t="s">
+      <c r="B29" t="s">
         <v>379</v>
       </c>
       <c r="C29" t="s">
@@ -8499,7 +8540,7 @@
       <c r="A30" t="s">
         <v>159</v>
       </c>
-      <c r="B30" s="8" t="s">
+      <c r="B30" t="s">
         <v>379</v>
       </c>
       <c r="C30" t="s">
@@ -8513,7 +8554,7 @@
       <c r="A31" t="s">
         <v>159</v>
       </c>
-      <c r="B31" s="8" t="s">
+      <c r="B31" t="s">
         <v>379</v>
       </c>
       <c r="C31" t="s">
@@ -8527,7 +8568,7 @@
       <c r="A32" t="s">
         <v>159</v>
       </c>
-      <c r="B32" s="8" t="s">
+      <c r="B32" t="s">
         <v>379</v>
       </c>
       <c r="C32" t="s">
@@ -8541,7 +8582,7 @@
       <c r="A33" t="s">
         <v>159</v>
       </c>
-      <c r="B33" s="8" t="s">
+      <c r="B33" t="s">
         <v>380</v>
       </c>
       <c r="C33" t="s">
@@ -8555,7 +8596,7 @@
       <c r="A34" t="s">
         <v>159</v>
       </c>
-      <c r="B34" s="8" t="s">
+      <c r="B34" t="s">
         <v>380</v>
       </c>
       <c r="C34" t="s">
@@ -8569,7 +8610,7 @@
       <c r="A35" t="s">
         <v>159</v>
       </c>
-      <c r="B35" s="8" t="s">
+      <c r="B35" t="s">
         <v>380</v>
       </c>
       <c r="C35" t="s">
@@ -8583,7 +8624,7 @@
       <c r="A36" t="s">
         <v>159</v>
       </c>
-      <c r="B36" s="8" t="s">
+      <c r="B36" t="s">
         <v>380</v>
       </c>
       <c r="C36" t="s">
@@ -8597,7 +8638,7 @@
       <c r="A37" t="s">
         <v>159</v>
       </c>
-      <c r="B37" s="8" t="s">
+      <c r="B37" t="s">
         <v>380</v>
       </c>
       <c r="C37" t="s">
@@ -8611,7 +8652,7 @@
       <c r="A38" t="s">
         <v>159</v>
       </c>
-      <c r="B38" s="8" t="s">
+      <c r="B38" t="s">
         <v>381</v>
       </c>
       <c r="C38" t="s">
@@ -8625,7 +8666,7 @@
       <c r="A39" t="s">
         <v>159</v>
       </c>
-      <c r="B39" s="8" t="s">
+      <c r="B39" t="s">
         <v>381</v>
       </c>
       <c r="C39" t="s">
@@ -8639,7 +8680,7 @@
       <c r="A40" t="s">
         <v>159</v>
       </c>
-      <c r="B40" s="8" t="s">
+      <c r="B40" t="s">
         <v>381</v>
       </c>
       <c r="C40" t="s">
@@ -8653,7 +8694,7 @@
       <c r="A41" t="s">
         <v>159</v>
       </c>
-      <c r="B41" s="8" t="s">
+      <c r="B41" t="s">
         <v>381</v>
       </c>
       <c r="C41" t="s">
@@ -8667,7 +8708,7 @@
       <c r="A42" t="s">
         <v>159</v>
       </c>
-      <c r="B42" s="8" t="s">
+      <c r="B42" t="s">
         <v>381</v>
       </c>
       <c r="C42" t="s">
@@ -8681,7 +8722,7 @@
       <c r="A43" t="s">
         <v>159</v>
       </c>
-      <c r="B43" s="8" t="s">
+      <c r="B43" t="s">
         <v>389</v>
       </c>
       <c r="C43" t="s">
@@ -8695,7 +8736,7 @@
       <c r="A44" t="s">
         <v>159</v>
       </c>
-      <c r="B44" s="8" t="s">
+      <c r="B44" t="s">
         <v>389</v>
       </c>
       <c r="C44" t="s">
@@ -8709,7 +8750,7 @@
       <c r="A45" t="s">
         <v>159</v>
       </c>
-      <c r="B45" s="8" t="s">
+      <c r="B45" t="s">
         <v>389</v>
       </c>
       <c r="C45" t="s">
@@ -8723,7 +8764,7 @@
       <c r="A46" t="s">
         <v>159</v>
       </c>
-      <c r="B46" s="8" t="s">
+      <c r="B46" t="s">
         <v>389</v>
       </c>
       <c r="C46" t="s">
@@ -8737,7 +8778,7 @@
       <c r="A47" t="s">
         <v>159</v>
       </c>
-      <c r="B47" s="8" t="s">
+      <c r="B47" t="s">
         <v>385</v>
       </c>
       <c r="C47" t="s">
@@ -8751,7 +8792,7 @@
       <c r="A48" t="s">
         <v>159</v>
       </c>
-      <c r="B48" s="8" t="s">
+      <c r="B48" t="s">
         <v>385</v>
       </c>
       <c r="C48" t="s">
@@ -8765,7 +8806,7 @@
       <c r="A49" t="s">
         <v>159</v>
       </c>
-      <c r="B49" s="8" t="s">
+      <c r="B49" t="s">
         <v>385</v>
       </c>
       <c r="C49" t="s">
@@ -8779,7 +8820,7 @@
       <c r="A50" t="s">
         <v>159</v>
       </c>
-      <c r="B50" s="8" t="s">
+      <c r="B50" t="s">
         <v>372</v>
       </c>
       <c r="C50" t="s">
@@ -8793,7 +8834,7 @@
       <c r="A51" t="s">
         <v>159</v>
       </c>
-      <c r="B51" s="8" t="s">
+      <c r="B51" t="s">
         <v>372</v>
       </c>
       <c r="C51" t="s">
@@ -8807,7 +8848,7 @@
       <c r="A52" t="s">
         <v>159</v>
       </c>
-      <c r="B52" s="8" t="s">
+      <c r="B52" t="s">
         <v>372</v>
       </c>
       <c r="C52" t="s">
@@ -8821,7 +8862,7 @@
       <c r="A53" t="s">
         <v>159</v>
       </c>
-      <c r="B53" s="8" t="s">
+      <c r="B53" t="s">
         <v>372</v>
       </c>
       <c r="C53" t="s">
@@ -8835,7 +8876,7 @@
       <c r="A54" t="s">
         <v>159</v>
       </c>
-      <c r="B54" s="8" t="s">
+      <c r="B54" t="s">
         <v>376</v>
       </c>
       <c r="C54" t="s">
@@ -8849,7 +8890,7 @@
       <c r="A55" t="s">
         <v>159</v>
       </c>
-      <c r="B55" s="8" t="s">
+      <c r="B55" t="s">
         <v>376</v>
       </c>
       <c r="C55" t="s">
@@ -8863,7 +8904,7 @@
       <c r="A56" t="s">
         <v>159</v>
       </c>
-      <c r="B56" s="8" t="s">
+      <c r="B56" t="s">
         <v>376</v>
       </c>
       <c r="C56" t="s">
@@ -8877,7 +8918,7 @@
       <c r="A57" t="s">
         <v>159</v>
       </c>
-      <c r="B57" s="8" t="s">
+      <c r="B57" t="s">
         <v>376</v>
       </c>
       <c r="C57" t="s">
@@ -8891,7 +8932,7 @@
       <c r="A58" t="s">
         <v>159</v>
       </c>
-      <c r="B58" s="8" t="s">
+      <c r="B58" t="s">
         <v>376</v>
       </c>
       <c r="C58" t="s">
@@ -8905,7 +8946,7 @@
       <c r="A59" t="s">
         <v>159</v>
       </c>
-      <c r="B59" s="8" t="s">
+      <c r="B59" t="s">
         <v>386</v>
       </c>
       <c r="C59" t="s">
@@ -8919,7 +8960,7 @@
       <c r="A60" t="s">
         <v>159</v>
       </c>
-      <c r="B60" s="8" t="s">
+      <c r="B60" t="s">
         <v>386</v>
       </c>
       <c r="C60" t="s">
@@ -8933,7 +8974,7 @@
       <c r="A61" t="s">
         <v>159</v>
       </c>
-      <c r="B61" s="8" t="s">
+      <c r="B61" t="s">
         <v>386</v>
       </c>
       <c r="C61" t="s">
@@ -8947,7 +8988,7 @@
       <c r="A62" t="s">
         <v>159</v>
       </c>
-      <c r="B62" s="8" t="s">
+      <c r="B62" t="s">
         <v>383</v>
       </c>
       <c r="C62" t="s">
@@ -8961,7 +9002,7 @@
       <c r="A63" t="s">
         <v>159</v>
       </c>
-      <c r="B63" s="8" t="s">
+      <c r="B63" t="s">
         <v>383</v>
       </c>
       <c r="C63" t="s">
@@ -8975,7 +9016,7 @@
       <c r="A64" t="s">
         <v>159</v>
       </c>
-      <c r="B64" s="8" t="s">
+      <c r="B64" t="s">
         <v>383</v>
       </c>
       <c r="C64" t="s">
@@ -8989,7 +9030,7 @@
       <c r="A65" t="s">
         <v>159</v>
       </c>
-      <c r="B65" s="8" t="s">
+      <c r="B65" t="s">
         <v>383</v>
       </c>
       <c r="C65" t="s">
@@ -9003,7 +9044,7 @@
       <c r="A66" t="s">
         <v>159</v>
       </c>
-      <c r="B66" s="8" t="s">
+      <c r="B66" t="s">
         <v>374</v>
       </c>
       <c r="C66" t="s">
@@ -9017,7 +9058,7 @@
       <c r="A67" t="s">
         <v>159</v>
       </c>
-      <c r="B67" s="8" t="s">
+      <c r="B67" t="s">
         <v>374</v>
       </c>
       <c r="C67" t="s">
@@ -9031,7 +9072,7 @@
       <c r="A68" t="s">
         <v>159</v>
       </c>
-      <c r="B68" s="8" t="s">
+      <c r="B68" t="s">
         <v>374</v>
       </c>
       <c r="C68" t="s">
@@ -9045,7 +9086,7 @@
       <c r="A69" t="s">
         <v>159</v>
       </c>
-      <c r="B69" s="8" t="s">
+      <c r="B69" t="s">
         <v>374</v>
       </c>
       <c r="C69" t="s">
@@ -9059,7 +9100,7 @@
       <c r="A70" t="s">
         <v>159</v>
       </c>
-      <c r="B70" s="8" t="s">
+      <c r="B70" t="s">
         <v>384</v>
       </c>
       <c r="C70" t="s">
@@ -9073,7 +9114,7 @@
       <c r="A71" t="s">
         <v>159</v>
       </c>
-      <c r="B71" s="8" t="s">
+      <c r="B71" t="s">
         <v>384</v>
       </c>
       <c r="C71" t="s">
@@ -9087,7 +9128,7 @@
       <c r="A72" t="s">
         <v>159</v>
       </c>
-      <c r="B72" s="8" t="s">
+      <c r="B72" t="s">
         <v>384</v>
       </c>
       <c r="C72" t="s">
@@ -9101,7 +9142,7 @@
       <c r="A73" t="s">
         <v>159</v>
       </c>
-      <c r="B73" s="8" t="s">
+      <c r="B73" t="s">
         <v>384</v>
       </c>
       <c r="C73" t="s">
@@ -9115,7 +9156,7 @@
       <c r="A74" t="s">
         <v>159</v>
       </c>
-      <c r="B74" s="8" t="s">
+      <c r="B74" t="s">
         <v>375</v>
       </c>
       <c r="C74" t="s">
@@ -9129,7 +9170,7 @@
       <c r="A75" t="s">
         <v>159</v>
       </c>
-      <c r="B75" s="8" t="s">
+      <c r="B75" t="s">
         <v>375</v>
       </c>
       <c r="C75" t="s">
@@ -9143,7 +9184,7 @@
       <c r="A76" t="s">
         <v>159</v>
       </c>
-      <c r="B76" s="8" t="s">
+      <c r="B76" t="s">
         <v>375</v>
       </c>
       <c r="C76" t="s">
@@ -9157,7 +9198,7 @@
       <c r="A77" t="s">
         <v>159</v>
       </c>
-      <c r="B77" s="8" t="s">
+      <c r="B77" t="s">
         <v>375</v>
       </c>
       <c r="C77" t="s">
@@ -9171,7 +9212,7 @@
       <c r="A78" t="s">
         <v>159</v>
       </c>
-      <c r="B78" s="8" t="s">
+      <c r="B78" t="s">
         <v>391</v>
       </c>
       <c r="C78" t="s">
@@ -9185,7 +9226,7 @@
       <c r="A79" t="s">
         <v>159</v>
       </c>
-      <c r="B79" s="8" t="s">
+      <c r="B79" t="s">
         <v>391</v>
       </c>
       <c r="C79" t="s">
@@ -9199,7 +9240,7 @@
       <c r="A80" t="s">
         <v>159</v>
       </c>
-      <c r="B80" s="8" t="s">
+      <c r="B80" t="s">
         <v>391</v>
       </c>
       <c r="C80" t="s">
@@ -9213,7 +9254,7 @@
       <c r="A81" t="s">
         <v>159</v>
       </c>
-      <c r="B81" s="8" t="s">
+      <c r="B81" t="s">
         <v>373</v>
       </c>
       <c r="C81" t="s">
@@ -9227,7 +9268,7 @@
       <c r="A82" t="s">
         <v>159</v>
       </c>
-      <c r="B82" s="8" t="s">
+      <c r="B82" t="s">
         <v>373</v>
       </c>
       <c r="C82" t="s">
@@ -9241,7 +9282,7 @@
       <c r="A83" t="s">
         <v>159</v>
       </c>
-      <c r="B83" s="8" t="s">
+      <c r="B83" t="s">
         <v>373</v>
       </c>
       <c r="C83" t="s">
@@ -9255,7 +9296,7 @@
       <c r="A84" t="s">
         <v>159</v>
       </c>
-      <c r="B84" s="8" t="s">
+      <c r="B84" t="s">
         <v>388</v>
       </c>
       <c r="C84" t="s">
@@ -9269,7 +9310,7 @@
       <c r="A85" t="s">
         <v>159</v>
       </c>
-      <c r="B85" s="8" t="s">
+      <c r="B85" t="s">
         <v>388</v>
       </c>
       <c r="C85" t="s">
@@ -9283,7 +9324,7 @@
       <c r="A86" t="s">
         <v>159</v>
       </c>
-      <c r="B86" s="8" t="s">
+      <c r="B86" t="s">
         <v>388</v>
       </c>
       <c r="C86" t="s">
@@ -9297,7 +9338,7 @@
       <c r="A87" t="s">
         <v>159</v>
       </c>
-      <c r="B87" s="8" t="s">
+      <c r="B87" t="s">
         <v>388</v>
       </c>
       <c r="C87" t="s">
@@ -9311,7 +9352,7 @@
       <c r="A88" t="s">
         <v>159</v>
       </c>
-      <c r="B88" s="8" t="s">
+      <c r="B88" t="s">
         <v>399</v>
       </c>
       <c r="C88" t="s">
@@ -9325,7 +9366,7 @@
       <c r="A89" t="s">
         <v>159</v>
       </c>
-      <c r="B89" s="8" t="s">
+      <c r="B89" t="s">
         <v>399</v>
       </c>
       <c r="C89" t="s">
@@ -9339,7 +9380,7 @@
       <c r="A90" t="s">
         <v>159</v>
       </c>
-      <c r="B90" s="8" t="s">
+      <c r="B90" t="s">
         <v>387</v>
       </c>
       <c r="C90" t="s">
@@ -9353,7 +9394,7 @@
       <c r="A91" t="s">
         <v>159</v>
       </c>
-      <c r="B91" s="8" t="s">
+      <c r="B91" t="s">
         <v>387</v>
       </c>
       <c r="C91" t="s">
@@ -9367,7 +9408,7 @@
       <c r="A92" t="s">
         <v>159</v>
       </c>
-      <c r="B92" s="8" t="s">
+      <c r="B92" t="s">
         <v>387</v>
       </c>
       <c r="C92" t="s">
@@ -9381,7 +9422,7 @@
       <c r="A93" t="s">
         <v>159</v>
       </c>
-      <c r="B93" s="8" t="s">
+      <c r="B93" t="s">
         <v>387</v>
       </c>
       <c r="C93" t="s">
@@ -9395,7 +9436,7 @@
       <c r="A94" t="s">
         <v>159</v>
       </c>
-      <c r="B94" s="8" t="s">
+      <c r="B94" t="s">
         <v>390</v>
       </c>
       <c r="C94" t="s">
@@ -9409,7 +9450,7 @@
       <c r="A95" t="s">
         <v>159</v>
       </c>
-      <c r="B95" s="8" t="s">
+      <c r="B95" t="s">
         <v>390</v>
       </c>
       <c r="C95" t="s">
@@ -9423,7 +9464,7 @@
       <c r="A96" t="s">
         <v>159</v>
       </c>
-      <c r="B96" s="8" t="s">
+      <c r="B96" t="s">
         <v>390</v>
       </c>
       <c r="C96" t="s">
@@ -9437,7 +9478,7 @@
       <c r="A97" t="s">
         <v>159</v>
       </c>
-      <c r="B97" s="8" t="s">
+      <c r="B97" t="s">
         <v>390</v>
       </c>
       <c r="C97" t="s">
@@ -9451,7 +9492,7 @@
       <c r="A98" t="s">
         <v>159</v>
       </c>
-      <c r="B98" s="8" t="s">
+      <c r="B98" t="s">
         <v>390</v>
       </c>
       <c r="C98" t="s">
@@ -10288,6 +10329,1171 @@
 </file>
 
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7FC8E18F-6C4D-4E79-95C6-12AA8E1945EB}">
+  <dimension ref="A1:E83"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="12.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="16.85546875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" t="s">
+        <v>547</v>
+      </c>
+      <c r="C1" t="s">
+        <v>548</v>
+      </c>
+      <c r="D1" t="s">
+        <v>549</v>
+      </c>
+      <c r="E1" t="s">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" s="9">
+        <v>0.15966</v>
+      </c>
+      <c r="C2" s="9">
+        <v>3.1980000000000001E-2</v>
+      </c>
+      <c r="E2" s="9">
+        <v>7.7979999999999994E-2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>192</v>
+      </c>
+      <c r="B3" s="9">
+        <v>1.298E-2</v>
+      </c>
+      <c r="C3" s="9">
+        <v>1.6500000000000001E-2</v>
+      </c>
+      <c r="D3">
+        <v>0.13413</v>
+      </c>
+      <c r="E3" s="9">
+        <v>4.5690000000000001E-2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>193</v>
+      </c>
+      <c r="B4" s="9">
+        <v>7.4329999999999993E-2</v>
+      </c>
+      <c r="C4" s="9">
+        <v>0.11271</v>
+      </c>
+      <c r="E4" s="9">
+        <v>4.3610000000000003E-2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>194</v>
+      </c>
+      <c r="B5" s="9">
+        <v>1.5270000000000001E-2</v>
+      </c>
+      <c r="C5" s="9">
+        <v>6.5979999999999997E-2</v>
+      </c>
+      <c r="D5">
+        <v>0.14641999999999999</v>
+      </c>
+      <c r="E5" s="9">
+        <v>1.64E-3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>49</v>
+      </c>
+      <c r="B6" s="9">
+        <v>8.4100000000000008E-3</v>
+      </c>
+      <c r="C6" s="9">
+        <v>4.3920000000000001E-2</v>
+      </c>
+      <c r="D6">
+        <v>0.18093000000000001</v>
+      </c>
+      <c r="E6" s="9">
+        <v>8.0999999999999996E-3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>7</v>
+      </c>
+      <c r="B7" s="9">
+        <v>2.017E-2</v>
+      </c>
+      <c r="C7" s="9">
+        <v>0.1893</v>
+      </c>
+      <c r="E7" s="9">
+        <v>1.3480000000000001E-2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>195</v>
+      </c>
+      <c r="B8" s="9">
+        <v>2.043E-2</v>
+      </c>
+      <c r="C8" s="9">
+        <v>0.14116000000000001</v>
+      </c>
+      <c r="D8">
+        <v>0.10986</v>
+      </c>
+      <c r="E8" s="9">
+        <v>2.2030000000000001E-2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>196</v>
+      </c>
+      <c r="B9" s="9">
+        <v>7.0899999999999999E-3</v>
+      </c>
+      <c r="C9" s="9">
+        <v>5.219E-2</v>
+      </c>
+      <c r="D9">
+        <v>0.27805000000000002</v>
+      </c>
+      <c r="E9" s="9">
+        <v>4.8320000000000002E-2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>8</v>
+      </c>
+      <c r="B10" s="9">
+        <v>5.64E-3</v>
+      </c>
+      <c r="C10" s="9">
+        <v>8.3089999999999997E-2</v>
+      </c>
+      <c r="E10" s="9"/>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>9</v>
+      </c>
+      <c r="B11" s="9">
+        <v>7.2199999999999999E-3</v>
+      </c>
+      <c r="C11" s="9">
+        <v>6.9879999999999998E-2</v>
+      </c>
+      <c r="D11">
+        <v>0.13275000000000001</v>
+      </c>
+      <c r="E11" s="9">
+        <v>1.5509999999999999E-2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>197</v>
+      </c>
+      <c r="B12" s="9">
+        <v>1.17E-3</v>
+      </c>
+      <c r="C12" s="9">
+        <v>1.404E-2</v>
+      </c>
+      <c r="E12" s="9">
+        <v>1.6000000000000001E-4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>10</v>
+      </c>
+      <c r="B13" s="9">
+        <v>9.8499999999999994E-3</v>
+      </c>
+      <c r="C13" s="9">
+        <v>9.2880000000000004E-2</v>
+      </c>
+      <c r="D13">
+        <v>3.823E-2</v>
+      </c>
+      <c r="E13" s="9">
+        <v>0.13804</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>198</v>
+      </c>
+      <c r="B14" s="9">
+        <v>1.9720000000000001E-2</v>
+      </c>
+      <c r="C14" s="9">
+        <v>7.1029999999999996E-2</v>
+      </c>
+      <c r="E14" s="9">
+        <v>8.0769999999999995E-2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>50</v>
+      </c>
+      <c r="B15" s="9">
+        <v>1.4250000000000001E-2</v>
+      </c>
+      <c r="C15" s="9">
+        <v>5.5899999999999998E-2</v>
+      </c>
+      <c r="D15">
+        <v>2.7449999999999999E-2</v>
+      </c>
+      <c r="E15" s="9"/>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>199</v>
+      </c>
+      <c r="B16" s="9">
+        <v>7.5100000000000002E-3</v>
+      </c>
+      <c r="C16" s="9">
+        <v>1.558E-2</v>
+      </c>
+      <c r="E16" s="9">
+        <v>1.9820000000000001E-2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>200</v>
+      </c>
+      <c r="B17" s="9">
+        <v>3.397E-2</v>
+      </c>
+      <c r="C17" s="9">
+        <v>8.8230000000000003E-2</v>
+      </c>
+      <c r="D17">
+        <v>8.695E-2</v>
+      </c>
+      <c r="E17" s="9">
+        <v>0.23178000000000001</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>201</v>
+      </c>
+      <c r="B18" s="9">
+        <v>6.8500000000000002E-3</v>
+      </c>
+      <c r="C18" s="9">
+        <v>4.1919999999999999E-2</v>
+      </c>
+      <c r="E18" s="9">
+        <v>8.0000000000000007E-5</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>202</v>
+      </c>
+      <c r="B19" s="9">
+        <v>5.8100000000000001E-3</v>
+      </c>
+      <c r="C19" s="9">
+        <v>9.0900000000000009E-3</v>
+      </c>
+      <c r="E19" s="9">
+        <v>3.3189999999999997E-2</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>51</v>
+      </c>
+      <c r="B20" s="9">
+        <v>7.9810000000000006E-2</v>
+      </c>
+      <c r="C20" s="9">
+        <v>4.82E-2</v>
+      </c>
+      <c r="E20" s="9"/>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>203</v>
+      </c>
+      <c r="B21" s="9">
+        <v>0.11771</v>
+      </c>
+      <c r="C21" s="9">
+        <v>7.6410000000000006E-2</v>
+      </c>
+      <c r="E21" s="9">
+        <v>3.492E-2</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>204</v>
+      </c>
+      <c r="B22" s="9">
+        <v>6.923E-2</v>
+      </c>
+      <c r="C22" s="9">
+        <v>6.019E-2</v>
+      </c>
+      <c r="E22" s="9">
+        <v>0.17216000000000001</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>205</v>
+      </c>
+      <c r="B23" s="9">
+        <v>0.12694</v>
+      </c>
+      <c r="C23" s="9">
+        <v>0.12697</v>
+      </c>
+      <c r="E23" s="9">
+        <v>0.19883000000000001</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>206</v>
+      </c>
+      <c r="B24" s="9">
+        <v>0.23297999999999999</v>
+      </c>
+      <c r="C24" s="9">
+        <v>0.11595999999999999</v>
+      </c>
+      <c r="E24" s="9">
+        <v>1.4420000000000001E-2</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>207</v>
+      </c>
+      <c r="B25" s="9">
+        <v>2.1090000000000001E-2</v>
+      </c>
+      <c r="C25" s="9">
+        <v>8.3360000000000004E-2</v>
+      </c>
+      <c r="E25" s="9"/>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>208</v>
+      </c>
+      <c r="B26" s="9">
+        <v>4.2320000000000003E-2</v>
+      </c>
+      <c r="C26" s="9">
+        <v>8.3760000000000001E-2</v>
+      </c>
+      <c r="E26" s="9">
+        <v>0.15517</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>11</v>
+      </c>
+      <c r="B27" s="9">
+        <v>5.5500000000000002E-3</v>
+      </c>
+      <c r="C27" s="9">
+        <v>1.6910000000000001E-2</v>
+      </c>
+      <c r="E27" s="9">
+        <v>1.523E-2</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>209</v>
+      </c>
+      <c r="B28" s="9">
+        <v>9.5240000000000005E-2</v>
+      </c>
+      <c r="C28" s="9">
+        <v>4.3180000000000003E-2</v>
+      </c>
+      <c r="E28" s="9">
+        <v>6.2399999999999997E-2</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>210</v>
+      </c>
+      <c r="B29" s="9">
+        <v>6.4490000000000006E-2</v>
+      </c>
+      <c r="C29" s="9">
+        <v>5.6989999999999999E-2</v>
+      </c>
+      <c r="E29" s="9">
+        <v>2.9199999999999999E-3</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>211</v>
+      </c>
+      <c r="B30" s="9">
+        <v>6.2480000000000001E-2</v>
+      </c>
+      <c r="C30" s="9">
+        <v>5.2650000000000002E-2</v>
+      </c>
+      <c r="E30" s="9">
+        <v>0.10173</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>212</v>
+      </c>
+      <c r="B31" s="9">
+        <v>0.16317999999999999</v>
+      </c>
+      <c r="C31" s="9">
+        <v>0.10635</v>
+      </c>
+      <c r="E31" s="9">
+        <v>0.75083999999999995</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>213</v>
+      </c>
+      <c r="B32" s="9">
+        <v>1.291E-2</v>
+      </c>
+      <c r="C32" s="9">
+        <v>3.9730000000000001E-2</v>
+      </c>
+      <c r="E32" s="9"/>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>214</v>
+      </c>
+      <c r="B33" s="9">
+        <v>6.9269999999999998E-2</v>
+      </c>
+      <c r="C33" s="9">
+        <v>6.7239999999999994E-2</v>
+      </c>
+      <c r="E33" s="9">
+        <v>9.1370000000000007E-2</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>12</v>
+      </c>
+      <c r="B34" s="9">
+        <v>3.3360000000000001E-2</v>
+      </c>
+      <c r="C34" s="9">
+        <v>0.10623</v>
+      </c>
+      <c r="E34" s="9">
+        <v>0.31896000000000002</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>215</v>
+      </c>
+      <c r="B35" s="9">
+        <v>5.6899999999999997E-3</v>
+      </c>
+      <c r="C35" s="9">
+        <v>2.2699999999999999E-3</v>
+      </c>
+      <c r="E35" s="9"/>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>216</v>
+      </c>
+      <c r="B36" s="9">
+        <v>0.17901</v>
+      </c>
+      <c r="C36" s="9">
+        <v>8.0089999999999995E-2</v>
+      </c>
+      <c r="E36" s="9"/>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>217</v>
+      </c>
+      <c r="B37" s="9">
+        <v>3.0300000000000001E-2</v>
+      </c>
+      <c r="C37" s="9">
+        <v>4.9299999999999997E-2</v>
+      </c>
+      <c r="E37" s="9">
+        <v>0.17380000000000001</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>218</v>
+      </c>
+      <c r="B38" s="9">
+        <v>0.12252</v>
+      </c>
+      <c r="C38" s="9">
+        <v>8.7489999999999998E-2</v>
+      </c>
+      <c r="E38" s="9">
+        <v>0.30692000000000003</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>219</v>
+      </c>
+      <c r="B39" s="9">
+        <v>5.3670000000000002E-2</v>
+      </c>
+      <c r="C39" s="9">
+        <v>5.0479999999999997E-2</v>
+      </c>
+      <c r="E39" s="9"/>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>220</v>
+      </c>
+      <c r="B40" s="9">
+        <v>0.1081</v>
+      </c>
+      <c r="C40" s="9">
+        <v>0.14080999999999999</v>
+      </c>
+      <c r="E40" s="9">
+        <v>0.44716</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>221</v>
+      </c>
+      <c r="B41" s="9">
+        <v>2.5000000000000001E-2</v>
+      </c>
+      <c r="C41" s="9">
+        <v>5.1700000000000001E-3</v>
+      </c>
+      <c r="E41" s="9">
+        <v>1.3390000000000001E-2</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>222</v>
+      </c>
+      <c r="B42" s="9">
+        <v>4.1750000000000002E-2</v>
+      </c>
+      <c r="C42" s="9">
+        <v>0.13517000000000001</v>
+      </c>
+      <c r="E42" s="9">
+        <v>0.61514000000000002</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>223</v>
+      </c>
+      <c r="B43" s="9">
+        <v>3.14E-3</v>
+      </c>
+      <c r="C43" s="9">
+        <v>8.5800000000000008E-3</v>
+      </c>
+      <c r="E43" s="9"/>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>13</v>
+      </c>
+      <c r="B44" s="9">
+        <v>7.1249999999999994E-2</v>
+      </c>
+      <c r="C44" s="9">
+        <v>8.3199999999999996E-2</v>
+      </c>
+      <c r="E44" s="9">
+        <v>0.15623000000000001</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>224</v>
+      </c>
+      <c r="B45" s="9">
+        <v>8.7600000000000004E-3</v>
+      </c>
+      <c r="C45" s="9">
+        <v>2.2200000000000002E-3</v>
+      </c>
+      <c r="E45" s="9"/>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>225</v>
+      </c>
+      <c r="B46" s="9">
+        <v>9.0310000000000001E-2</v>
+      </c>
+      <c r="C46" s="9">
+        <v>6.2300000000000001E-2</v>
+      </c>
+      <c r="E46" s="9">
+        <v>1.0580000000000001E-2</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>226</v>
+      </c>
+      <c r="B47" s="9">
+        <v>1.251E-2</v>
+      </c>
+      <c r="C47" s="9">
+        <v>3.0130000000000001E-2</v>
+      </c>
+      <c r="E47" s="9">
+        <v>2.6870000000000002E-2</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>227</v>
+      </c>
+      <c r="B48" s="9">
+        <v>9.3670000000000003E-2</v>
+      </c>
+      <c r="C48" s="9">
+        <v>8.2030000000000006E-2</v>
+      </c>
+      <c r="E48" s="9">
+        <v>0.34797</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>228</v>
+      </c>
+      <c r="B49" s="9">
+        <v>0.13993</v>
+      </c>
+      <c r="C49" s="9">
+        <v>0.13708000000000001</v>
+      </c>
+      <c r="E49" s="9">
+        <v>0.30248000000000003</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>229</v>
+      </c>
+      <c r="B50" s="9">
+        <v>9.9500000000000005E-2</v>
+      </c>
+      <c r="C50" s="9">
+        <v>0.10402</v>
+      </c>
+      <c r="E50" s="9">
+        <v>0.19621</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>52</v>
+      </c>
+      <c r="B51" s="9">
+        <v>1.4300000000000001E-3</v>
+      </c>
+      <c r="C51" s="9">
+        <v>2.6540000000000001E-2</v>
+      </c>
+      <c r="E51" s="9">
+        <v>2.15E-3</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>230</v>
+      </c>
+      <c r="B52" s="9">
+        <v>7.918E-2</v>
+      </c>
+      <c r="C52" s="9">
+        <v>4.9979999999999997E-2</v>
+      </c>
+      <c r="E52" s="9">
+        <v>0.45939000000000002</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>231</v>
+      </c>
+      <c r="B53" s="9">
+        <v>3.356E-2</v>
+      </c>
+      <c r="C53" s="9">
+        <v>6.9510000000000002E-2</v>
+      </c>
+      <c r="E53" s="9">
+        <v>0.74536000000000002</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>232</v>
+      </c>
+      <c r="B54" s="9">
+        <v>7.3340000000000002E-2</v>
+      </c>
+      <c r="C54" s="9">
+        <v>1.2840000000000001E-2</v>
+      </c>
+      <c r="E54" s="9">
+        <v>4.0499999999999998E-3</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>233</v>
+      </c>
+      <c r="B55" s="9">
+        <v>7.714E-2</v>
+      </c>
+      <c r="C55" s="9">
+        <v>7.5069999999999998E-2</v>
+      </c>
+      <c r="E55" s="9"/>
+    </row>
+    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>234</v>
+      </c>
+      <c r="B56" s="9">
+        <v>1.9449999999999999E-2</v>
+      </c>
+      <c r="C56" s="9">
+        <v>3.2649999999999998E-2</v>
+      </c>
+      <c r="E56" s="9">
+        <v>3.6600000000000001E-2</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>235</v>
+      </c>
+      <c r="B57" s="9">
+        <v>9.7890000000000005E-2</v>
+      </c>
+      <c r="C57" s="9">
+        <v>9.2480000000000007E-2</v>
+      </c>
+      <c r="E57" s="9">
+        <v>1.9980000000000001E-2</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>236</v>
+      </c>
+      <c r="B58" s="9">
+        <v>9.3640000000000001E-2</v>
+      </c>
+      <c r="C58" s="9">
+        <v>0.10761</v>
+      </c>
+      <c r="E58" s="9">
+        <v>8.1780000000000005E-2</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>237</v>
+      </c>
+      <c r="B59" s="9">
+        <v>4.258E-2</v>
+      </c>
+      <c r="C59" s="9">
+        <v>9.5530000000000004E-2</v>
+      </c>
+      <c r="E59" s="9"/>
+    </row>
+    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>238</v>
+      </c>
+      <c r="B60" s="9">
+        <v>5.4350000000000002E-2</v>
+      </c>
+      <c r="C60" s="9">
+        <v>9.1199999999999996E-3</v>
+      </c>
+      <c r="E60" s="9"/>
+    </row>
+    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>239</v>
+      </c>
+      <c r="B61" s="9">
+        <v>1.8010000000000002E-2</v>
+      </c>
+      <c r="C61" s="9">
+        <v>1.2710000000000001E-2</v>
+      </c>
+      <c r="E61" s="9">
+        <v>6.25E-2</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>14</v>
+      </c>
+      <c r="B62" s="9">
+        <v>5.1119999999999999E-2</v>
+      </c>
+      <c r="C62" s="9">
+        <v>9.5259999999999997E-2</v>
+      </c>
+      <c r="E62" s="9"/>
+    </row>
+    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>240</v>
+      </c>
+      <c r="B63" s="9">
+        <v>3.134E-2</v>
+      </c>
+      <c r="C63" s="9">
+        <v>5.1049999999999998E-2</v>
+      </c>
+      <c r="E63" s="9">
+        <v>0.16006000000000001</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>241</v>
+      </c>
+      <c r="B64" s="9">
+        <v>4.1349999999999998E-2</v>
+      </c>
+      <c r="C64" s="9">
+        <v>4.5629999999999997E-2</v>
+      </c>
+      <c r="E64" s="9">
+        <v>0.11323</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>242</v>
+      </c>
+      <c r="B65" s="9">
+        <v>0.12227</v>
+      </c>
+      <c r="C65" s="9">
+        <v>8.2180000000000003E-2</v>
+      </c>
+      <c r="E65" s="9">
+        <v>9.3329999999999996E-2</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>243</v>
+      </c>
+      <c r="B66" s="9">
+        <v>7.8780000000000003E-2</v>
+      </c>
+      <c r="C66" s="9">
+        <v>2.572E-2</v>
+      </c>
+      <c r="E66" s="9">
+        <v>0.20397000000000001</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>244</v>
+      </c>
+      <c r="B67" s="9">
+        <v>2.818E-2</v>
+      </c>
+      <c r="C67" s="9">
+        <v>1.6900000000000001E-3</v>
+      </c>
+      <c r="E67" s="9"/>
+    </row>
+    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>245</v>
+      </c>
+      <c r="B68" s="9">
+        <v>4.3729999999999998E-2</v>
+      </c>
+      <c r="C68" s="9">
+        <v>9.1579999999999995E-2</v>
+      </c>
+      <c r="E68" s="9"/>
+    </row>
+    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>246</v>
+      </c>
+      <c r="B69" s="9">
+        <v>3.5699999999999998E-3</v>
+      </c>
+      <c r="C69" s="9">
+        <v>1.9939999999999999E-2</v>
+      </c>
+      <c r="E69" s="9">
+        <v>7.535E-2</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>15</v>
+      </c>
+      <c r="B70" s="9">
+        <v>6.6710000000000005E-2</v>
+      </c>
+      <c r="C70" s="9">
+        <v>7.7090000000000006E-2</v>
+      </c>
+      <c r="E70" s="9">
+        <v>5.5870000000000003E-2</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
+        <v>247</v>
+      </c>
+      <c r="B71" s="9">
+        <v>9.6149999999999999E-2</v>
+      </c>
+      <c r="C71" s="9">
+        <v>6.4850000000000005E-2</v>
+      </c>
+      <c r="E71" s="9">
+        <v>2.1499999999999998E-2</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
+        <v>248</v>
+      </c>
+      <c r="B72" s="9">
+        <v>4.3159999999999997E-2</v>
+      </c>
+      <c r="C72" s="9">
+        <v>2.5569999999999999E-2</v>
+      </c>
+      <c r="E72" s="9">
+        <v>3.8760000000000003E-2</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
+        <v>249</v>
+      </c>
+      <c r="B73" s="9">
+        <v>3.8359999999999998E-2</v>
+      </c>
+      <c r="C73" s="9">
+        <v>4.5280000000000001E-2</v>
+      </c>
+      <c r="E73" s="9">
+        <v>0.25383</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
+        <v>250</v>
+      </c>
+      <c r="B74" s="9">
+        <v>3.7620000000000001E-2</v>
+      </c>
+      <c r="C74" s="9">
+        <v>8.4949999999999998E-2</v>
+      </c>
+      <c r="E74" s="9">
+        <v>7.9460000000000003E-2</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
+        <v>16</v>
+      </c>
+      <c r="B75" s="9">
+        <v>8.7309999999999999E-2</v>
+      </c>
+      <c r="C75" s="9">
+        <v>0.12786</v>
+      </c>
+      <c r="E75" s="9">
+        <v>0.44885000000000003</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
+        <v>251</v>
+      </c>
+      <c r="B76" s="9">
+        <v>7.2100000000000003E-3</v>
+      </c>
+      <c r="C76" s="9">
+        <v>5.7400000000000003E-3</v>
+      </c>
+      <c r="E76" s="9"/>
+    </row>
+    <row r="77" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
+        <v>17</v>
+      </c>
+      <c r="B77" s="9">
+        <v>3.705E-2</v>
+      </c>
+      <c r="C77" s="9">
+        <v>5.5939999999999997E-2</v>
+      </c>
+      <c r="E77" s="9">
+        <v>0.28910000000000002</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
+        <v>60</v>
+      </c>
+      <c r="B78" s="9">
+        <v>1.685E-2</v>
+      </c>
+      <c r="C78" s="9">
+        <v>4.1480000000000003E-2</v>
+      </c>
+      <c r="E78" s="9">
+        <v>8.6849999999999997E-2</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
+        <v>18</v>
+      </c>
+      <c r="B79" s="9">
+        <v>9.4009999999999996E-2</v>
+      </c>
+      <c r="C79" s="9">
+        <v>5.0799999999999998E-2</v>
+      </c>
+      <c r="E79" s="9">
+        <v>0.16173999999999999</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A80" t="s">
+        <v>59</v>
+      </c>
+      <c r="B80" s="9">
+        <v>2.4899999999999999E-2</v>
+      </c>
+      <c r="C80" s="9">
+        <v>7.2760000000000005E-2</v>
+      </c>
+      <c r="E80" s="9">
+        <v>0.25317000000000001</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
+        <v>19</v>
+      </c>
+      <c r="B81" s="9">
+        <v>2.5409999999999999E-2</v>
+      </c>
+      <c r="C81" s="9">
+        <v>1.0370000000000001E-2</v>
+      </c>
+      <c r="E81" s="9"/>
+    </row>
+    <row r="82" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A82" t="s">
+        <v>252</v>
+      </c>
+      <c r="B82" s="9">
+        <v>1.3780000000000001E-2</v>
+      </c>
+      <c r="C82" s="9">
+        <v>7.775E-2</v>
+      </c>
+      <c r="E82" s="9">
+        <v>0.23533000000000001</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B83" s="9"/>
+      <c r="C83" s="9"/>
+      <c r="D83" s="9"/>
+      <c r="E83" s="9"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{118A6323-FA6A-47F1-8FD7-71097682A301}">
   <dimension ref="A1:C183"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -12081,7 +13287,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{61D05816-00FF-458D-8921-8D01423DCE8A}">
   <dimension ref="A1:C61"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -12755,1183 +13961,6 @@
       </c>
       <c r="C61">
         <v>-2.1</v>
-      </c>
-    </row>
-  </sheetData>
-  <sheetProtection sheet="1" objects="1" scenarios="1"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0206C416-5E99-4BF3-A01A-B219B8D6BE2C}">
-  <dimension ref="A1:C106"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>362</v>
-      </c>
-      <c r="B1" t="s">
-        <v>363</v>
-      </c>
-      <c r="C1" t="s">
-        <v>345</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>307</v>
-      </c>
-      <c r="B2" t="s">
-        <v>364</v>
-      </c>
-      <c r="C2">
-        <v>1404</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>307</v>
-      </c>
-      <c r="B3" t="s">
-        <v>365</v>
-      </c>
-      <c r="C3">
-        <v>10.7</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>307</v>
-      </c>
-      <c r="B4" t="s">
-        <v>366</v>
-      </c>
-      <c r="C4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>307</v>
-      </c>
-      <c r="B5" t="s">
-        <v>367</v>
-      </c>
-      <c r="C5">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>307</v>
-      </c>
-      <c r="B6" t="s">
-        <v>368</v>
-      </c>
-      <c r="C6">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>308</v>
-      </c>
-      <c r="B7" t="s">
-        <v>364</v>
-      </c>
-      <c r="C7">
-        <v>1428</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>308</v>
-      </c>
-      <c r="B8" t="s">
-        <v>365</v>
-      </c>
-      <c r="C8">
-        <v>9.1999999999999993</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>308</v>
-      </c>
-      <c r="B9" t="s">
-        <v>366</v>
-      </c>
-      <c r="C9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>308</v>
-      </c>
-      <c r="B10" t="s">
-        <v>367</v>
-      </c>
-      <c r="C10">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>308</v>
-      </c>
-      <c r="B11" t="s">
-        <v>368</v>
-      </c>
-      <c r="C11">
-        <v>64.7</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>309</v>
-      </c>
-      <c r="B12" t="s">
-        <v>364</v>
-      </c>
-      <c r="C12">
-        <v>1473</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>309</v>
-      </c>
-      <c r="B13" t="s">
-        <v>365</v>
-      </c>
-      <c r="C13">
-        <v>8.4700000000000006</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>309</v>
-      </c>
-      <c r="B14" t="s">
-        <v>366</v>
-      </c>
-      <c r="C14">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>309</v>
-      </c>
-      <c r="B15" t="s">
-        <v>367</v>
-      </c>
-      <c r="C15">
-        <v>1.88</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>309</v>
-      </c>
-      <c r="B16" t="s">
-        <v>368</v>
-      </c>
-      <c r="C16">
-        <v>72.400000000000006</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>310</v>
-      </c>
-      <c r="B17" t="s">
-        <v>364</v>
-      </c>
-      <c r="C17">
-        <v>3700</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>310</v>
-      </c>
-      <c r="B18" t="s">
-        <v>365</v>
-      </c>
-      <c r="C18">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>310</v>
-      </c>
-      <c r="B19" t="s">
-        <v>366</v>
-      </c>
-      <c r="C19">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>310</v>
-      </c>
-      <c r="B20" t="s">
-        <v>367</v>
-      </c>
-      <c r="C20">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>310</v>
-      </c>
-      <c r="B21" t="s">
-        <v>368</v>
-      </c>
-      <c r="C21">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
-        <v>312</v>
-      </c>
-      <c r="B22" t="s">
-        <v>364</v>
-      </c>
-      <c r="C22">
-        <v>329</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
-        <v>312</v>
-      </c>
-      <c r="B23" t="s">
-        <v>365</v>
-      </c>
-      <c r="C23">
-        <v>1.74</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
-        <v>312</v>
-      </c>
-      <c r="B24" t="s">
-        <v>366</v>
-      </c>
-      <c r="C24">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
-        <v>312</v>
-      </c>
-      <c r="B25" t="s">
-        <v>367</v>
-      </c>
-      <c r="C25">
-        <v>0.1</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
-        <v>312</v>
-      </c>
-      <c r="B26" t="s">
-        <v>368</v>
-      </c>
-      <c r="C26">
-        <v>16.399999999999999</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
-        <v>313</v>
-      </c>
-      <c r="B27" t="s">
-        <v>364</v>
-      </c>
-      <c r="C27">
-        <v>1693</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
-        <v>313</v>
-      </c>
-      <c r="B28" t="s">
-        <v>365</v>
-      </c>
-      <c r="C28">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
-        <v>313</v>
-      </c>
-      <c r="B29" t="s">
-        <v>366</v>
-      </c>
-      <c r="C29">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
-        <v>313</v>
-      </c>
-      <c r="B30" t="s">
-        <v>367</v>
-      </c>
-      <c r="C30">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A31" t="s">
-        <v>313</v>
-      </c>
-      <c r="B31" t="s">
-        <v>368</v>
-      </c>
-      <c r="C31">
-        <v>99.6</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A32" t="s">
-        <v>324</v>
-      </c>
-      <c r="B32" t="s">
-        <v>364</v>
-      </c>
-      <c r="C32">
-        <v>850</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A33" t="s">
-        <v>324</v>
-      </c>
-      <c r="B33" t="s">
-        <v>365</v>
-      </c>
-      <c r="C33">
-        <v>18.5</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A34" t="s">
-        <v>324</v>
-      </c>
-      <c r="B34" t="s">
-        <v>366</v>
-      </c>
-      <c r="C34">
-        <v>18.5</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A35" t="s">
-        <v>324</v>
-      </c>
-      <c r="B35" t="s">
-        <v>367</v>
-      </c>
-      <c r="C35">
-        <v>14.2</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A36" t="s">
-        <v>324</v>
-      </c>
-      <c r="B36" t="s">
-        <v>368</v>
-      </c>
-      <c r="C36">
-        <v>0.17</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A37" t="s">
-        <v>314</v>
-      </c>
-      <c r="B37" t="s">
-        <v>364</v>
-      </c>
-      <c r="C37">
-        <v>575</v>
-      </c>
-    </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A38" t="s">
-        <v>314</v>
-      </c>
-      <c r="B38" t="s">
-        <v>365</v>
-      </c>
-      <c r="C38">
-        <v>12.3</v>
-      </c>
-    </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A39" t="s">
-        <v>314</v>
-      </c>
-      <c r="B39" t="s">
-        <v>366</v>
-      </c>
-      <c r="C39">
-        <v>12.3</v>
-      </c>
-    </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A40" t="s">
-        <v>314</v>
-      </c>
-      <c r="B40" t="s">
-        <v>367</v>
-      </c>
-      <c r="C40">
-        <v>9.73</v>
-      </c>
-    </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A41" t="s">
-        <v>314</v>
-      </c>
-      <c r="B41" t="s">
-        <v>368</v>
-      </c>
-      <c r="C41">
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A42" t="s">
-        <v>316</v>
-      </c>
-      <c r="B42" t="s">
-        <v>364</v>
-      </c>
-      <c r="C42">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A43" t="s">
-        <v>316</v>
-      </c>
-      <c r="B43" t="s">
-        <v>365</v>
-      </c>
-      <c r="C43">
-        <v>3.5</v>
-      </c>
-    </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A44" t="s">
-        <v>316</v>
-      </c>
-      <c r="B44" t="s">
-        <v>366</v>
-      </c>
-      <c r="C44">
-        <v>3.5</v>
-      </c>
-    </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A45" t="s">
-        <v>316</v>
-      </c>
-      <c r="B45" t="s">
-        <v>367</v>
-      </c>
-      <c r="C45">
-        <v>1.9</v>
-      </c>
-    </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A46" t="s">
-        <v>316</v>
-      </c>
-      <c r="B46" t="s">
-        <v>368</v>
-      </c>
-      <c r="C46">
-        <v>4.8</v>
-      </c>
-    </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A47" t="s">
-        <v>317</v>
-      </c>
-      <c r="B47" t="s">
-        <v>364</v>
-      </c>
-      <c r="C47">
-        <v>1377</v>
-      </c>
-    </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A48" t="s">
-        <v>317</v>
-      </c>
-      <c r="B48" t="s">
-        <v>365</v>
-      </c>
-      <c r="C48">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A49" t="s">
-        <v>317</v>
-      </c>
-      <c r="B49" t="s">
-        <v>366</v>
-      </c>
-      <c r="C49">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A50" t="s">
-        <v>317</v>
-      </c>
-      <c r="B50" t="s">
-        <v>367</v>
-      </c>
-      <c r="C50">
-        <v>27.3</v>
-      </c>
-    </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A51" t="s">
-        <v>317</v>
-      </c>
-      <c r="B51" t="s">
-        <v>368</v>
-      </c>
-      <c r="C51">
-        <v>1.7</v>
-      </c>
-    </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A52" t="s">
-        <v>318</v>
-      </c>
-      <c r="B52" t="s">
-        <v>364</v>
-      </c>
-      <c r="C52">
-        <v>3049</v>
-      </c>
-    </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A53" t="s">
-        <v>318</v>
-      </c>
-      <c r="B53" t="s">
-        <v>365</v>
-      </c>
-      <c r="C53">
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A54" t="s">
-        <v>318</v>
-      </c>
-      <c r="B54" t="s">
-        <v>366</v>
-      </c>
-      <c r="C54">
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A55" t="s">
-        <v>318</v>
-      </c>
-      <c r="B55" t="s">
-        <v>367</v>
-      </c>
-      <c r="C55">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A56" t="s">
-        <v>318</v>
-      </c>
-      <c r="B56" t="s">
-        <v>368</v>
-      </c>
-      <c r="C56">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A57" t="s">
-        <v>319</v>
-      </c>
-      <c r="B57" t="s">
-        <v>364</v>
-      </c>
-      <c r="C57">
-        <v>1319</v>
-      </c>
-    </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A58" t="s">
-        <v>319</v>
-      </c>
-      <c r="B58" t="s">
-        <v>365</v>
-      </c>
-      <c r="C58">
-        <v>2.4</v>
-      </c>
-    </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A59" t="s">
-        <v>319</v>
-      </c>
-      <c r="B59" t="s">
-        <v>366</v>
-      </c>
-      <c r="C59">
-        <v>2.4</v>
-      </c>
-    </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A60" t="s">
-        <v>319</v>
-      </c>
-      <c r="B60" t="s">
-        <v>367</v>
-      </c>
-      <c r="C60">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A61" t="s">
-        <v>319</v>
-      </c>
-      <c r="B61" t="s">
-        <v>368</v>
-      </c>
-      <c r="C61">
-        <v>3.3</v>
-      </c>
-    </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A62" t="s">
-        <v>320</v>
-      </c>
-      <c r="B62" t="s">
-        <v>364</v>
-      </c>
-      <c r="C62">
-        <v>1570</v>
-      </c>
-    </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A63" t="s">
-        <v>320</v>
-      </c>
-      <c r="B63" t="s">
-        <v>365</v>
-      </c>
-      <c r="C63">
-        <v>36.200000000000003</v>
-      </c>
-    </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A64" t="s">
-        <v>320</v>
-      </c>
-      <c r="B64" t="s">
-        <v>366</v>
-      </c>
-      <c r="C64">
-        <v>36.200000000000003</v>
-      </c>
-    </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A65" t="s">
-        <v>320</v>
-      </c>
-      <c r="B65" t="s">
-        <v>367</v>
-      </c>
-      <c r="C65">
-        <v>1.92</v>
-      </c>
-    </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A66" t="s">
-        <v>320</v>
-      </c>
-      <c r="B66" t="s">
-        <v>368</v>
-      </c>
-      <c r="C66">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A67" t="s">
-        <v>321</v>
-      </c>
-      <c r="B67" t="s">
-        <v>364</v>
-      </c>
-      <c r="C67">
-        <v>789</v>
-      </c>
-    </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A68" t="s">
-        <v>321</v>
-      </c>
-      <c r="B68" t="s">
-        <v>365</v>
-      </c>
-      <c r="C68">
-        <v>19.600000000000001</v>
-      </c>
-    </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A69" t="s">
-        <v>321</v>
-      </c>
-      <c r="B69" t="s">
-        <v>366</v>
-      </c>
-      <c r="C69">
-        <v>19.600000000000001</v>
-      </c>
-    </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A70" t="s">
-        <v>321</v>
-      </c>
-      <c r="B70" t="s">
-        <v>367</v>
-      </c>
-      <c r="C70">
-        <v>12.2</v>
-      </c>
-    </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A71" t="s">
-        <v>321</v>
-      </c>
-      <c r="B71" t="s">
-        <v>368</v>
-      </c>
-      <c r="C71">
-        <v>0.21</v>
-      </c>
-    </row>
-    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A72" t="s">
-        <v>322</v>
-      </c>
-      <c r="B72" t="s">
-        <v>364</v>
-      </c>
-      <c r="C72">
-        <v>1029</v>
-      </c>
-    </row>
-    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A73" t="s">
-        <v>322</v>
-      </c>
-      <c r="B73" t="s">
-        <v>365</v>
-      </c>
-      <c r="C73">
-        <v>16.2</v>
-      </c>
-    </row>
-    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A74" t="s">
-        <v>322</v>
-      </c>
-      <c r="B74" t="s">
-        <v>366</v>
-      </c>
-      <c r="C74">
-        <v>16.2</v>
-      </c>
-    </row>
-    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A75" t="s">
-        <v>322</v>
-      </c>
-      <c r="B75" t="s">
-        <v>367</v>
-      </c>
-      <c r="C75">
-        <v>20.3</v>
-      </c>
-    </row>
-    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A76" t="s">
-        <v>322</v>
-      </c>
-      <c r="B76" t="s">
-        <v>368</v>
-      </c>
-      <c r="C76">
-        <v>0.14000000000000001</v>
-      </c>
-    </row>
-    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A77" t="s">
-        <v>323</v>
-      </c>
-      <c r="B77" t="s">
-        <v>364</v>
-      </c>
-      <c r="C77">
-        <v>426</v>
-      </c>
-    </row>
-    <row r="78" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A78" t="s">
-        <v>323</v>
-      </c>
-      <c r="B78" t="s">
-        <v>365</v>
-      </c>
-      <c r="C78">
-        <v>11.5</v>
-      </c>
-    </row>
-    <row r="79" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A79" t="s">
-        <v>323</v>
-      </c>
-      <c r="B79" t="s">
-        <v>366</v>
-      </c>
-      <c r="C79">
-        <v>11.5</v>
-      </c>
-    </row>
-    <row r="80" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A80" t="s">
-        <v>323</v>
-      </c>
-      <c r="B80" t="s">
-        <v>367</v>
-      </c>
-      <c r="C80">
-        <v>6.2</v>
-      </c>
-    </row>
-    <row r="81" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A81" t="s">
-        <v>323</v>
-      </c>
-      <c r="B81" t="s">
-        <v>368</v>
-      </c>
-      <c r="C81">
-        <v>0.1</v>
-      </c>
-    </row>
-    <row r="82" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A82" t="s">
-        <v>325</v>
-      </c>
-      <c r="B82" t="s">
-        <v>364</v>
-      </c>
-      <c r="C82">
-        <v>548</v>
-      </c>
-    </row>
-    <row r="83" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A83" t="s">
-        <v>325</v>
-      </c>
-      <c r="B83" t="s">
-        <v>365</v>
-      </c>
-      <c r="C83">
-        <v>18.100000000000001</v>
-      </c>
-    </row>
-    <row r="84" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A84" t="s">
-        <v>325</v>
-      </c>
-      <c r="B84" t="s">
-        <v>366</v>
-      </c>
-      <c r="C84">
-        <v>18.100000000000001</v>
-      </c>
-    </row>
-    <row r="85" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A85" t="s">
-        <v>325</v>
-      </c>
-      <c r="B85" t="s">
-        <v>367</v>
-      </c>
-      <c r="C85">
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="86" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A86" t="s">
-        <v>325</v>
-      </c>
-      <c r="B86" t="s">
-        <v>368</v>
-      </c>
-      <c r="C86">
-        <v>0.99</v>
-      </c>
-    </row>
-    <row r="87" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A87" t="s">
-        <v>326</v>
-      </c>
-      <c r="B87" t="s">
-        <v>364</v>
-      </c>
-      <c r="C87">
-        <v>685</v>
-      </c>
-    </row>
-    <row r="88" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A88" t="s">
-        <v>326</v>
-      </c>
-      <c r="B88" t="s">
-        <v>365</v>
-      </c>
-      <c r="C88">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="89" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A89" t="s">
-        <v>326</v>
-      </c>
-      <c r="B89" t="s">
-        <v>366</v>
-      </c>
-      <c r="C89">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="90" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A90" t="s">
-        <v>326</v>
-      </c>
-      <c r="B90" t="s">
-        <v>367</v>
-      </c>
-      <c r="C90">
-        <v>10.5</v>
-      </c>
-    </row>
-    <row r="91" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A91" t="s">
-        <v>326</v>
-      </c>
-      <c r="B91" t="s">
-        <v>368</v>
-      </c>
-      <c r="C91">
-        <v>4.8499999999999996</v>
-      </c>
-    </row>
-    <row r="92" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A92" t="s">
-        <v>327</v>
-      </c>
-      <c r="B92" t="s">
-        <v>364</v>
-      </c>
-      <c r="C92">
-        <v>387</v>
-      </c>
-    </row>
-    <row r="93" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A93" t="s">
-        <v>327</v>
-      </c>
-      <c r="B93" t="s">
-        <v>365</v>
-      </c>
-      <c r="C93">
-        <v>1.7</v>
-      </c>
-    </row>
-    <row r="94" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A94" t="s">
-        <v>327</v>
-      </c>
-      <c r="B94" t="s">
-        <v>366</v>
-      </c>
-      <c r="C94">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="95" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A95" t="s">
-        <v>327</v>
-      </c>
-      <c r="B95" t="s">
-        <v>367</v>
-      </c>
-      <c r="C95">
-        <v>2.6</v>
-      </c>
-    </row>
-    <row r="96" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A96" t="s">
-        <v>327</v>
-      </c>
-      <c r="B96" t="s">
-        <v>368</v>
-      </c>
-      <c r="C96">
-        <v>14.3</v>
-      </c>
-    </row>
-    <row r="97" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A97" t="s">
-        <v>328</v>
-      </c>
-      <c r="B97" t="s">
-        <v>364</v>
-      </c>
-      <c r="C97">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="98" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A98" t="s">
-        <v>328</v>
-      </c>
-      <c r="B98" t="s">
-        <v>365</v>
-      </c>
-      <c r="C98">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="99" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A99" t="s">
-        <v>328</v>
-      </c>
-      <c r="B99" t="s">
-        <v>366</v>
-      </c>
-      <c r="C99">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="100" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A100" t="s">
-        <v>328</v>
-      </c>
-      <c r="B100" t="s">
-        <v>367</v>
-      </c>
-      <c r="C100">
-        <v>0.1</v>
-      </c>
-    </row>
-    <row r="101" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A101" t="s">
-        <v>328</v>
-      </c>
-      <c r="B101" t="s">
-        <v>368</v>
-      </c>
-      <c r="C101">
-        <v>4.1399999999999997</v>
-      </c>
-    </row>
-    <row r="102" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A102" t="s">
-        <v>329</v>
-      </c>
-      <c r="B102" t="s">
-        <v>364</v>
-      </c>
-      <c r="C102">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="103" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A103" t="s">
-        <v>329</v>
-      </c>
-      <c r="B103" t="s">
-        <v>365</v>
-      </c>
-      <c r="C103">
-        <v>0.7</v>
-      </c>
-    </row>
-    <row r="104" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A104" t="s">
-        <v>329</v>
-      </c>
-      <c r="B104" t="s">
-        <v>366</v>
-      </c>
-      <c r="C104">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="105" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A105" t="s">
-        <v>329</v>
-      </c>
-      <c r="B105" t="s">
-        <v>367</v>
-      </c>
-      <c r="C105">
-        <v>0.8</v>
-      </c>
-    </row>
-    <row r="106" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A106" t="s">
-        <v>329</v>
-      </c>
-      <c r="B106" t="s">
-        <v>368</v>
-      </c>
-      <c r="C106">
-        <v>9.1</v>
       </c>
     </row>
   </sheetData>
@@ -14869,6 +14898,1183 @@
 </file>
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0206C416-5E99-4BF3-A01A-B219B8D6BE2C}">
+  <dimension ref="A1:C106"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>362</v>
+      </c>
+      <c r="B1" t="s">
+        <v>363</v>
+      </c>
+      <c r="C1" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>307</v>
+      </c>
+      <c r="B2" t="s">
+        <v>364</v>
+      </c>
+      <c r="C2">
+        <v>1404</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>307</v>
+      </c>
+      <c r="B3" t="s">
+        <v>365</v>
+      </c>
+      <c r="C3">
+        <v>10.7</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>307</v>
+      </c>
+      <c r="B4" t="s">
+        <v>366</v>
+      </c>
+      <c r="C4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>307</v>
+      </c>
+      <c r="B5" t="s">
+        <v>367</v>
+      </c>
+      <c r="C5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>307</v>
+      </c>
+      <c r="B6" t="s">
+        <v>368</v>
+      </c>
+      <c r="C6">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>308</v>
+      </c>
+      <c r="B7" t="s">
+        <v>364</v>
+      </c>
+      <c r="C7">
+        <v>1428</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>308</v>
+      </c>
+      <c r="B8" t="s">
+        <v>365</v>
+      </c>
+      <c r="C8">
+        <v>9.1999999999999993</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>308</v>
+      </c>
+      <c r="B9" t="s">
+        <v>366</v>
+      </c>
+      <c r="C9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>308</v>
+      </c>
+      <c r="B10" t="s">
+        <v>367</v>
+      </c>
+      <c r="C10">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>308</v>
+      </c>
+      <c r="B11" t="s">
+        <v>368</v>
+      </c>
+      <c r="C11">
+        <v>64.7</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>309</v>
+      </c>
+      <c r="B12" t="s">
+        <v>364</v>
+      </c>
+      <c r="C12">
+        <v>1473</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>309</v>
+      </c>
+      <c r="B13" t="s">
+        <v>365</v>
+      </c>
+      <c r="C13">
+        <v>8.4700000000000006</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>309</v>
+      </c>
+      <c r="B14" t="s">
+        <v>366</v>
+      </c>
+      <c r="C14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>309</v>
+      </c>
+      <c r="B15" t="s">
+        <v>367</v>
+      </c>
+      <c r="C15">
+        <v>1.88</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>309</v>
+      </c>
+      <c r="B16" t="s">
+        <v>368</v>
+      </c>
+      <c r="C16">
+        <v>72.400000000000006</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>310</v>
+      </c>
+      <c r="B17" t="s">
+        <v>364</v>
+      </c>
+      <c r="C17">
+        <v>3700</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>310</v>
+      </c>
+      <c r="B18" t="s">
+        <v>365</v>
+      </c>
+      <c r="C18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>310</v>
+      </c>
+      <c r="B19" t="s">
+        <v>366</v>
+      </c>
+      <c r="C19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>310</v>
+      </c>
+      <c r="B20" t="s">
+        <v>367</v>
+      </c>
+      <c r="C20">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>310</v>
+      </c>
+      <c r="B21" t="s">
+        <v>368</v>
+      </c>
+      <c r="C21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>312</v>
+      </c>
+      <c r="B22" t="s">
+        <v>364</v>
+      </c>
+      <c r="C22">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>312</v>
+      </c>
+      <c r="B23" t="s">
+        <v>365</v>
+      </c>
+      <c r="C23">
+        <v>1.74</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>312</v>
+      </c>
+      <c r="B24" t="s">
+        <v>366</v>
+      </c>
+      <c r="C24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>312</v>
+      </c>
+      <c r="B25" t="s">
+        <v>367</v>
+      </c>
+      <c r="C25">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>312</v>
+      </c>
+      <c r="B26" t="s">
+        <v>368</v>
+      </c>
+      <c r="C26">
+        <v>16.399999999999999</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>313</v>
+      </c>
+      <c r="B27" t="s">
+        <v>364</v>
+      </c>
+      <c r="C27">
+        <v>1693</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>313</v>
+      </c>
+      <c r="B28" t="s">
+        <v>365</v>
+      </c>
+      <c r="C28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>313</v>
+      </c>
+      <c r="B29" t="s">
+        <v>366</v>
+      </c>
+      <c r="C29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>313</v>
+      </c>
+      <c r="B30" t="s">
+        <v>367</v>
+      </c>
+      <c r="C30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>313</v>
+      </c>
+      <c r="B31" t="s">
+        <v>368</v>
+      </c>
+      <c r="C31">
+        <v>99.6</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>324</v>
+      </c>
+      <c r="B32" t="s">
+        <v>364</v>
+      </c>
+      <c r="C32">
+        <v>850</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>324</v>
+      </c>
+      <c r="B33" t="s">
+        <v>365</v>
+      </c>
+      <c r="C33">
+        <v>18.5</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>324</v>
+      </c>
+      <c r="B34" t="s">
+        <v>366</v>
+      </c>
+      <c r="C34">
+        <v>18.5</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>324</v>
+      </c>
+      <c r="B35" t="s">
+        <v>367</v>
+      </c>
+      <c r="C35">
+        <v>14.2</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>324</v>
+      </c>
+      <c r="B36" t="s">
+        <v>368</v>
+      </c>
+      <c r="C36">
+        <v>0.17</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>314</v>
+      </c>
+      <c r="B37" t="s">
+        <v>364</v>
+      </c>
+      <c r="C37">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>314</v>
+      </c>
+      <c r="B38" t="s">
+        <v>365</v>
+      </c>
+      <c r="C38">
+        <v>12.3</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>314</v>
+      </c>
+      <c r="B39" t="s">
+        <v>366</v>
+      </c>
+      <c r="C39">
+        <v>12.3</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>314</v>
+      </c>
+      <c r="B40" t="s">
+        <v>367</v>
+      </c>
+      <c r="C40">
+        <v>9.73</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>314</v>
+      </c>
+      <c r="B41" t="s">
+        <v>368</v>
+      </c>
+      <c r="C41">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>316</v>
+      </c>
+      <c r="B42" t="s">
+        <v>364</v>
+      </c>
+      <c r="C42">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>316</v>
+      </c>
+      <c r="B43" t="s">
+        <v>365</v>
+      </c>
+      <c r="C43">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>316</v>
+      </c>
+      <c r="B44" t="s">
+        <v>366</v>
+      </c>
+      <c r="C44">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>316</v>
+      </c>
+      <c r="B45" t="s">
+        <v>367</v>
+      </c>
+      <c r="C45">
+        <v>1.9</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>316</v>
+      </c>
+      <c r="B46" t="s">
+        <v>368</v>
+      </c>
+      <c r="C46">
+        <v>4.8</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>317</v>
+      </c>
+      <c r="B47" t="s">
+        <v>364</v>
+      </c>
+      <c r="C47">
+        <v>1377</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>317</v>
+      </c>
+      <c r="B48" t="s">
+        <v>365</v>
+      </c>
+      <c r="C48">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>317</v>
+      </c>
+      <c r="B49" t="s">
+        <v>366</v>
+      </c>
+      <c r="C49">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>317</v>
+      </c>
+      <c r="B50" t="s">
+        <v>367</v>
+      </c>
+      <c r="C50">
+        <v>27.3</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>317</v>
+      </c>
+      <c r="B51" t="s">
+        <v>368</v>
+      </c>
+      <c r="C51">
+        <v>1.7</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>318</v>
+      </c>
+      <c r="B52" t="s">
+        <v>364</v>
+      </c>
+      <c r="C52">
+        <v>3049</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>318</v>
+      </c>
+      <c r="B53" t="s">
+        <v>365</v>
+      </c>
+      <c r="C53">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>318</v>
+      </c>
+      <c r="B54" t="s">
+        <v>366</v>
+      </c>
+      <c r="C54">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>318</v>
+      </c>
+      <c r="B55" t="s">
+        <v>367</v>
+      </c>
+      <c r="C55">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>318</v>
+      </c>
+      <c r="B56" t="s">
+        <v>368</v>
+      </c>
+      <c r="C56">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>319</v>
+      </c>
+      <c r="B57" t="s">
+        <v>364</v>
+      </c>
+      <c r="C57">
+        <v>1319</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>319</v>
+      </c>
+      <c r="B58" t="s">
+        <v>365</v>
+      </c>
+      <c r="C58">
+        <v>2.4</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>319</v>
+      </c>
+      <c r="B59" t="s">
+        <v>366</v>
+      </c>
+      <c r="C59">
+        <v>2.4</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>319</v>
+      </c>
+      <c r="B60" t="s">
+        <v>367</v>
+      </c>
+      <c r="C60">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>319</v>
+      </c>
+      <c r="B61" t="s">
+        <v>368</v>
+      </c>
+      <c r="C61">
+        <v>3.3</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>320</v>
+      </c>
+      <c r="B62" t="s">
+        <v>364</v>
+      </c>
+      <c r="C62">
+        <v>1570</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>320</v>
+      </c>
+      <c r="B63" t="s">
+        <v>365</v>
+      </c>
+      <c r="C63">
+        <v>36.200000000000003</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>320</v>
+      </c>
+      <c r="B64" t="s">
+        <v>366</v>
+      </c>
+      <c r="C64">
+        <v>36.200000000000003</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>320</v>
+      </c>
+      <c r="B65" t="s">
+        <v>367</v>
+      </c>
+      <c r="C65">
+        <v>1.92</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>320</v>
+      </c>
+      <c r="B66" t="s">
+        <v>368</v>
+      </c>
+      <c r="C66">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>321</v>
+      </c>
+      <c r="B67" t="s">
+        <v>364</v>
+      </c>
+      <c r="C67">
+        <v>789</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>321</v>
+      </c>
+      <c r="B68" t="s">
+        <v>365</v>
+      </c>
+      <c r="C68">
+        <v>19.600000000000001</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>321</v>
+      </c>
+      <c r="B69" t="s">
+        <v>366</v>
+      </c>
+      <c r="C69">
+        <v>19.600000000000001</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>321</v>
+      </c>
+      <c r="B70" t="s">
+        <v>367</v>
+      </c>
+      <c r="C70">
+        <v>12.2</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
+        <v>321</v>
+      </c>
+      <c r="B71" t="s">
+        <v>368</v>
+      </c>
+      <c r="C71">
+        <v>0.21</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
+        <v>322</v>
+      </c>
+      <c r="B72" t="s">
+        <v>364</v>
+      </c>
+      <c r="C72">
+        <v>1029</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
+        <v>322</v>
+      </c>
+      <c r="B73" t="s">
+        <v>365</v>
+      </c>
+      <c r="C73">
+        <v>16.2</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
+        <v>322</v>
+      </c>
+      <c r="B74" t="s">
+        <v>366</v>
+      </c>
+      <c r="C74">
+        <v>16.2</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
+        <v>322</v>
+      </c>
+      <c r="B75" t="s">
+        <v>367</v>
+      </c>
+      <c r="C75">
+        <v>20.3</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
+        <v>322</v>
+      </c>
+      <c r="B76" t="s">
+        <v>368</v>
+      </c>
+      <c r="C76">
+        <v>0.14000000000000001</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
+        <v>323</v>
+      </c>
+      <c r="B77" t="s">
+        <v>364</v>
+      </c>
+      <c r="C77">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
+        <v>323</v>
+      </c>
+      <c r="B78" t="s">
+        <v>365</v>
+      </c>
+      <c r="C78">
+        <v>11.5</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
+        <v>323</v>
+      </c>
+      <c r="B79" t="s">
+        <v>366</v>
+      </c>
+      <c r="C79">
+        <v>11.5</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A80" t="s">
+        <v>323</v>
+      </c>
+      <c r="B80" t="s">
+        <v>367</v>
+      </c>
+      <c r="C80">
+        <v>6.2</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
+        <v>323</v>
+      </c>
+      <c r="B81" t="s">
+        <v>368</v>
+      </c>
+      <c r="C81">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="82" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A82" t="s">
+        <v>325</v>
+      </c>
+      <c r="B82" t="s">
+        <v>364</v>
+      </c>
+      <c r="C82">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="83" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A83" t="s">
+        <v>325</v>
+      </c>
+      <c r="B83" t="s">
+        <v>365</v>
+      </c>
+      <c r="C83">
+        <v>18.100000000000001</v>
+      </c>
+    </row>
+    <row r="84" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A84" t="s">
+        <v>325</v>
+      </c>
+      <c r="B84" t="s">
+        <v>366</v>
+      </c>
+      <c r="C84">
+        <v>18.100000000000001</v>
+      </c>
+    </row>
+    <row r="85" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A85" t="s">
+        <v>325</v>
+      </c>
+      <c r="B85" t="s">
+        <v>367</v>
+      </c>
+      <c r="C85">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="86" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A86" t="s">
+        <v>325</v>
+      </c>
+      <c r="B86" t="s">
+        <v>368</v>
+      </c>
+      <c r="C86">
+        <v>0.99</v>
+      </c>
+    </row>
+    <row r="87" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A87" t="s">
+        <v>326</v>
+      </c>
+      <c r="B87" t="s">
+        <v>364</v>
+      </c>
+      <c r="C87">
+        <v>685</v>
+      </c>
+    </row>
+    <row r="88" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A88" t="s">
+        <v>326</v>
+      </c>
+      <c r="B88" t="s">
+        <v>365</v>
+      </c>
+      <c r="C88">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="89" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A89" t="s">
+        <v>326</v>
+      </c>
+      <c r="B89" t="s">
+        <v>366</v>
+      </c>
+      <c r="C89">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="90" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A90" t="s">
+        <v>326</v>
+      </c>
+      <c r="B90" t="s">
+        <v>367</v>
+      </c>
+      <c r="C90">
+        <v>10.5</v>
+      </c>
+    </row>
+    <row r="91" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A91" t="s">
+        <v>326</v>
+      </c>
+      <c r="B91" t="s">
+        <v>368</v>
+      </c>
+      <c r="C91">
+        <v>4.8499999999999996</v>
+      </c>
+    </row>
+    <row r="92" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A92" t="s">
+        <v>327</v>
+      </c>
+      <c r="B92" t="s">
+        <v>364</v>
+      </c>
+      <c r="C92">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="93" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A93" t="s">
+        <v>327</v>
+      </c>
+      <c r="B93" t="s">
+        <v>365</v>
+      </c>
+      <c r="C93">
+        <v>1.7</v>
+      </c>
+    </row>
+    <row r="94" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A94" t="s">
+        <v>327</v>
+      </c>
+      <c r="B94" t="s">
+        <v>366</v>
+      </c>
+      <c r="C94">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A95" t="s">
+        <v>327</v>
+      </c>
+      <c r="B95" t="s">
+        <v>367</v>
+      </c>
+      <c r="C95">
+        <v>2.6</v>
+      </c>
+    </row>
+    <row r="96" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A96" t="s">
+        <v>327</v>
+      </c>
+      <c r="B96" t="s">
+        <v>368</v>
+      </c>
+      <c r="C96">
+        <v>14.3</v>
+      </c>
+    </row>
+    <row r="97" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A97" t="s">
+        <v>328</v>
+      </c>
+      <c r="B97" t="s">
+        <v>364</v>
+      </c>
+      <c r="C97">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="98" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A98" t="s">
+        <v>328</v>
+      </c>
+      <c r="B98" t="s">
+        <v>365</v>
+      </c>
+      <c r="C98">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="99" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A99" t="s">
+        <v>328</v>
+      </c>
+      <c r="B99" t="s">
+        <v>366</v>
+      </c>
+      <c r="C99">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A100" t="s">
+        <v>328</v>
+      </c>
+      <c r="B100" t="s">
+        <v>367</v>
+      </c>
+      <c r="C100">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="101" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A101" t="s">
+        <v>328</v>
+      </c>
+      <c r="B101" t="s">
+        <v>368</v>
+      </c>
+      <c r="C101">
+        <v>4.1399999999999997</v>
+      </c>
+    </row>
+    <row r="102" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A102" t="s">
+        <v>329</v>
+      </c>
+      <c r="B102" t="s">
+        <v>364</v>
+      </c>
+      <c r="C102">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="103" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A103" t="s">
+        <v>329</v>
+      </c>
+      <c r="B103" t="s">
+        <v>365</v>
+      </c>
+      <c r="C103">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="104" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A104" t="s">
+        <v>329</v>
+      </c>
+      <c r="B104" t="s">
+        <v>366</v>
+      </c>
+      <c r="C104">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="105" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A105" t="s">
+        <v>329</v>
+      </c>
+      <c r="B105" t="s">
+        <v>367</v>
+      </c>
+      <c r="C105">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="106" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A106" t="s">
+        <v>329</v>
+      </c>
+      <c r="B106" t="s">
+        <v>368</v>
+      </c>
+      <c r="C106">
+        <v>9.1</v>
+      </c>
+    </row>
+  </sheetData>
+  <sheetProtection sheet="1" objects="1" scenarios="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{97461BA3-2572-48E1-B51A-549B5CBBC0F1}">
   <dimension ref="A1:B7"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -14935,7 +16141,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:D1343"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -33754,7 +34960,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FEAC8083-8073-4708-9AE8-A894D58A1ECD}">
   <dimension ref="A1:W312"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -38191,7 +39397,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D959A23A-6549-4BFB-8CFE-8BFCAC8B0CB4}">
   <dimension ref="A1:D2155"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -68377,7 +69583,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9AC8E327-ABF8-4EDA-AC3F-CA18C56BB80A}">
   <dimension ref="A1:B40"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -72310,27 +73516,22 @@
   <cols>
     <col min="1" max="1" width="6.140625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="10.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.42578125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="10.42578125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="10.85546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="8.42578125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="8.5703125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="9.5703125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="10.28515625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="11.85546875" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="9" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="10" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="10.42578125" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="8" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="8.140625" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="8.7109375" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="9.85546875" bestFit="1" customWidth="1"/>
-    <col min="22" max="23" width="9.7109375" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="8.7109375" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="10.28515625" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="9.85546875" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="9.5703125" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.5703125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.28515625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="9" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="10" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="8" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="8.7109375" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="8.7109375" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="10.28515625" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="9.5703125" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="9.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:28" x14ac:dyDescent="0.25">
@@ -72423,7 +73624,7 @@
       <c r="A2" t="s">
         <v>6</v>
       </c>
-      <c r="B2">
+      <c r="B2" s="8">
         <v>2.14</v>
       </c>
       <c r="C2">
@@ -79386,7 +80587,6 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection sheet="1" objects="1" scenarios="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>

--- a/data/data.xlsx
+++ b/data/data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Cecilia\Documents\Modellering\SASM\Github\SASM\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Cecilia\Documents\Modellering\SASM\Github\SASM_scen-histosol\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A263B727-EA24-4787-AEA9-B479BEBD3EAD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FED983CA-2D6E-424F-BCCC-1A95F3F297D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="878" firstSheet="8" activeTab="20" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="878" firstSheet="3" activeTab="16" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="index" sheetId="44" r:id="rId1"/>
@@ -29,14 +29,15 @@
     <sheet name="ECR(R,CR,IP)" sheetId="32" r:id="rId14"/>
     <sheet name="ECR2(R,CR,IP)" sheetId="37" r:id="rId15"/>
     <sheet name="ECR3(R,CR,IP)" sheetId="38" r:id="rId16"/>
-    <sheet name="MANURE(AS,IP)" sheetId="34" r:id="rId17"/>
-    <sheet name="NSUB(AS,SR)" sheetId="35" r:id="rId18"/>
-    <sheet name="NUTRIENT(P,NUTX)" sheetId="36" r:id="rId19"/>
-    <sheet name="POP(R)" sheetId="40" r:id="rId20"/>
-    <sheet name="PRODCOEFC_SA" sheetId="1" r:id="rId21"/>
-    <sheet name="PRODCOEFC2_PO" sheetId="42" r:id="rId22"/>
-    <sheet name="PRODCOEFL_SA" sheetId="5" r:id="rId23"/>
-    <sheet name="UT(IP)" sheetId="41" r:id="rId24"/>
+    <sheet name="histFrac(SR,IS)" sheetId="45" r:id="rId17"/>
+    <sheet name="MANURE(AS,IP)" sheetId="34" r:id="rId18"/>
+    <sheet name="NSUB(AS,SR)" sheetId="35" r:id="rId19"/>
+    <sheet name="NUTRIENT(P,NUTX)" sheetId="36" r:id="rId20"/>
+    <sheet name="POP(R)" sheetId="40" r:id="rId21"/>
+    <sheet name="PRODCOEFC_SA" sheetId="1" r:id="rId22"/>
+    <sheet name="PRODCOEFC2_PO" sheetId="42" r:id="rId23"/>
+    <sheet name="PRODCOEFL_SA" sheetId="5" r:id="rId24"/>
+    <sheet name="UT(IP)" sheetId="41" r:id="rId25"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'BIN(IN,SDP)'!$A$1:$C$1</definedName>
@@ -47,9 +48,9 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'BPSI_SA(SA,PS)'!$A$1:$C$49</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'CONST(IP,AS)'!$A$1:$C$178</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="13" hidden="1">'ECR(R,CR,IP)'!$A$1:$D$98</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="20" hidden="1">PRODCOEFC_SA!$A$1:$D$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="21" hidden="1">PRODCOEFC2_PO!$A$1:$D$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="22" hidden="1">PRODCOEFL_SA!$A$1:$D$2155</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="21" hidden="1">PRODCOEFC_SA!$A$1:$D$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="22" hidden="1">PRODCOEFC2_PO!$A$1:$D$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="23" hidden="1">PRODCOEFL_SA!$A$1:$D$2155</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -69,7 +70,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16594" uniqueCount="570">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16684" uniqueCount="577">
   <si>
     <t>AS</t>
   </si>
@@ -1625,139 +1626,70 @@
     <t xml:space="preserve">PRODCOEFC_SA   </t>
   </si>
   <si>
-    <t xml:space="preserve"> PRODCOEFC_SA!A2     </t>
-  </si>
-  <si>
     <t xml:space="preserve">PRODCOEFC2_PO  </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> PRODCOEFC2_PO!A2    </t>
   </si>
   <si>
     <t xml:space="preserve">PRODCOEFL_SA   </t>
   </si>
   <si>
-    <t xml:space="preserve"> PRODCOEFL_SA!A2     </t>
-  </si>
-  <si>
     <t xml:space="preserve">BIN            </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> BIN(IN,SDP)!A2      </t>
   </si>
   <si>
     <t xml:space="preserve">BIR            </t>
   </si>
   <si>
-    <t xml:space="preserve"> BIR(R,IR,SDP)!A2    </t>
-  </si>
-  <si>
     <t xml:space="preserve">BIRF           </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> BIRF(IR,R)!A2       </t>
   </si>
   <si>
     <t xml:space="preserve">BIRI           </t>
   </si>
   <si>
-    <t xml:space="preserve"> BIRI(IR,R)!A2       </t>
-  </si>
-  <si>
     <t xml:space="preserve">BISFA          </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> BISFA(SR,IS)!A1     </t>
   </si>
   <si>
     <t xml:space="preserve">BMR            </t>
   </si>
   <si>
-    <t xml:space="preserve"> BMR(R,PR,TRD)!A2    </t>
-  </si>
-  <si>
     <t xml:space="preserve">BPN            </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> BPN(PN,SDP)!A2      </t>
   </si>
   <si>
     <t xml:space="preserve">BPRN           </t>
   </si>
   <si>
-    <t xml:space="preserve"> BPRN(PR,SDP)!A2     </t>
-  </si>
-  <si>
     <t xml:space="preserve">BPSI_SA        </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> BPSI_SA(SA,PS)!A2   </t>
   </si>
   <si>
     <t xml:space="preserve">BXR            </t>
   </si>
   <si>
-    <t xml:space="preserve"> BXR(R,PR,TRD)!A2    </t>
-  </si>
-  <si>
     <t xml:space="preserve">DT             </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> DT(RS,RD)!A2        </t>
   </si>
   <si>
     <t xml:space="preserve">CONST          </t>
   </si>
   <si>
-    <t xml:space="preserve"> CONST(IP,AS)!A2     </t>
-  </si>
-  <si>
     <t xml:space="preserve">ECR            </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> ECR(R,CR,IP)!A2     </t>
   </si>
   <si>
     <t xml:space="preserve">ECR2           </t>
   </si>
   <si>
-    <t xml:space="preserve"> ECR2(R,CR,IP)!A2    </t>
-  </si>
-  <si>
     <t xml:space="preserve">ECR3           </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> ECR3(R,CR,IP)!A2    </t>
   </si>
   <si>
     <t xml:space="preserve">MANURE         </t>
   </si>
   <si>
-    <t xml:space="preserve"> MANURE(AS,IP)!A2    </t>
-  </si>
-  <si>
     <t xml:space="preserve">NSUB           </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> NSUB(AS,SR)!A2      </t>
   </si>
   <si>
     <t xml:space="preserve">NUTRIENT       </t>
   </si>
   <si>
-    <t xml:space="preserve"> NUTRIENT(P,NUTX)!A2 </t>
-  </si>
-  <si>
     <t xml:space="preserve">POP            </t>
   </si>
   <si>
-    <t xml:space="preserve"> POP(R)!A2           </t>
-  </si>
-  <si>
     <t xml:space="preserve">UT             </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> UT(IP)!A2           </t>
   </si>
   <si>
     <t>range</t>
@@ -1780,11 +1712,105 @@
   <si>
     <t>par</t>
   </si>
+  <si>
+    <t>histCropland</t>
+  </si>
+  <si>
+    <t>histPermPasture</t>
+  </si>
+  <si>
+    <t>histPermChalet</t>
+  </si>
+  <si>
+    <t>histPermMeadow</t>
+  </si>
+  <si>
+    <t>histFrac</t>
+  </si>
+  <si>
+    <t>PRODCOEFC_SA!A2</t>
+  </si>
+  <si>
+    <t>PRODCOEFC2_PO!A2</t>
+  </si>
+  <si>
+    <t>PRODCOEFL_SA!A2</t>
+  </si>
+  <si>
+    <t>BIN(IN,SDP)!A2</t>
+  </si>
+  <si>
+    <t>BIR(R,IR,SDP)!A2</t>
+  </si>
+  <si>
+    <t>BIRF(IR,R)!A2</t>
+  </si>
+  <si>
+    <t>BIRI(IR,R)!A2</t>
+  </si>
+  <si>
+    <t>BISFA(SR,IS)!A1</t>
+  </si>
+  <si>
+    <t>BMR(R,PR,TRD)!A2</t>
+  </si>
+  <si>
+    <t>BPN(PN,SDP)!A2</t>
+  </si>
+  <si>
+    <t>BPRN(PR,SDP)!A2</t>
+  </si>
+  <si>
+    <t>BPSI_SA(SA,PS)!A2</t>
+  </si>
+  <si>
+    <t>BXR(R,PR,TRD)!A2</t>
+  </si>
+  <si>
+    <t>DT(RS,RD)!A2</t>
+  </si>
+  <si>
+    <t>CONST(IP,AS)!A2</t>
+  </si>
+  <si>
+    <t>ECR(R,CR,IP)!A2</t>
+  </si>
+  <si>
+    <t>ECR2(R,CR,IP)!A2</t>
+  </si>
+  <si>
+    <t>ECR3(R,CR,IP)!A2</t>
+  </si>
+  <si>
+    <t>MANURE(AS,IP)!A2</t>
+  </si>
+  <si>
+    <t>NSUB(AS,SR)!A2</t>
+  </si>
+  <si>
+    <t>NUTRIENT(P,NUTX)!A2</t>
+  </si>
+  <si>
+    <t>POP(R)!A2</t>
+  </si>
+  <si>
+    <t>UT(IP)!A2</t>
+  </si>
+  <si>
+    <t>histFrac(SR,IS)!A1</t>
+  </si>
+  <si>
+    <t>histUAA</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.000"/>
+    <numFmt numFmtId="165" formatCode="0.00000"/>
+  </numFmts>
   <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -1855,7 +1881,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
@@ -1866,7 +1892,8 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2169,7 +2196,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FC09F416-B83A-444C-8E2A-32773041705C}">
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E29"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.7109375" customWidth="1"/>
@@ -2179,35 +2206,35 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>567</v>
+        <v>544</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
-        <v>568</v>
+        <v>545</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>566</v>
+        <v>543</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>563</v>
+        <v>540</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>564</v>
+        <v>541</v>
       </c>
       <c r="E5" s="7" t="s">
-        <v>565</v>
+        <v>542</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>569</v>
+        <v>546</v>
       </c>
       <c r="B6" t="s">
         <v>517</v>
       </c>
       <c r="C6" t="s">
-        <v>518</v>
+        <v>552</v>
       </c>
       <c r="D6">
         <v>3</v>
@@ -2218,13 +2245,13 @@
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>569</v>
+        <v>546</v>
       </c>
       <c r="B7" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="C7" t="s">
-        <v>520</v>
+        <v>553</v>
       </c>
       <c r="D7">
         <v>3</v>
@@ -2235,13 +2262,13 @@
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>569</v>
+        <v>546</v>
       </c>
       <c r="B8" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="C8" t="s">
-        <v>522</v>
+        <v>554</v>
       </c>
       <c r="D8">
         <v>3</v>
@@ -2252,13 +2279,13 @@
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>569</v>
+        <v>546</v>
       </c>
       <c r="B9" t="s">
-        <v>523</v>
+        <v>520</v>
       </c>
       <c r="C9" t="s">
-        <v>524</v>
+        <v>555</v>
       </c>
       <c r="D9">
         <v>2</v>
@@ -2269,13 +2296,13 @@
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>569</v>
+        <v>546</v>
       </c>
       <c r="B10" t="s">
-        <v>525</v>
+        <v>521</v>
       </c>
       <c r="C10" t="s">
-        <v>526</v>
+        <v>556</v>
       </c>
       <c r="D10">
         <v>3</v>
@@ -2286,13 +2313,13 @@
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>569</v>
+        <v>546</v>
       </c>
       <c r="B11" t="s">
-        <v>527</v>
+        <v>522</v>
       </c>
       <c r="C11" t="s">
-        <v>528</v>
+        <v>557</v>
       </c>
       <c r="D11">
         <v>2</v>
@@ -2303,13 +2330,13 @@
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>569</v>
+        <v>546</v>
       </c>
       <c r="B12" t="s">
-        <v>529</v>
+        <v>523</v>
       </c>
       <c r="C12" t="s">
-        <v>530</v>
+        <v>558</v>
       </c>
       <c r="D12">
         <v>2</v>
@@ -2320,13 +2347,13 @@
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>569</v>
+        <v>546</v>
       </c>
       <c r="B13" t="s">
-        <v>531</v>
+        <v>524</v>
       </c>
       <c r="C13" t="s">
-        <v>532</v>
+        <v>559</v>
       </c>
       <c r="D13">
         <v>1</v>
@@ -2337,13 +2364,13 @@
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>569</v>
+        <v>546</v>
       </c>
       <c r="B14" t="s">
-        <v>533</v>
+        <v>525</v>
       </c>
       <c r="C14" t="s">
-        <v>534</v>
+        <v>560</v>
       </c>
       <c r="D14">
         <v>3</v>
@@ -2354,13 +2381,13 @@
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>569</v>
+        <v>546</v>
       </c>
       <c r="B15" t="s">
-        <v>535</v>
+        <v>526</v>
       </c>
       <c r="C15" t="s">
-        <v>536</v>
+        <v>561</v>
       </c>
       <c r="D15">
         <v>2</v>
@@ -2371,13 +2398,13 @@
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>569</v>
+        <v>546</v>
       </c>
       <c r="B16" t="s">
-        <v>537</v>
+        <v>527</v>
       </c>
       <c r="C16" t="s">
-        <v>538</v>
+        <v>562</v>
       </c>
       <c r="D16">
         <v>2</v>
@@ -2388,13 +2415,13 @@
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>569</v>
+        <v>546</v>
       </c>
       <c r="B17" t="s">
-        <v>539</v>
+        <v>528</v>
       </c>
       <c r="C17" t="s">
-        <v>540</v>
+        <v>563</v>
       </c>
       <c r="D17">
         <v>2</v>
@@ -2405,13 +2432,13 @@
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>569</v>
+        <v>546</v>
       </c>
       <c r="B18" t="s">
-        <v>541</v>
+        <v>529</v>
       </c>
       <c r="C18" t="s">
-        <v>542</v>
+        <v>564</v>
       </c>
       <c r="D18">
         <v>3</v>
@@ -2422,13 +2449,13 @@
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>569</v>
+        <v>546</v>
       </c>
       <c r="B19" t="s">
-        <v>543</v>
+        <v>530</v>
       </c>
       <c r="C19" t="s">
-        <v>544</v>
+        <v>565</v>
       </c>
       <c r="D19">
         <v>2</v>
@@ -2439,13 +2466,13 @@
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>569</v>
+        <v>546</v>
       </c>
       <c r="B20" t="s">
-        <v>545</v>
+        <v>531</v>
       </c>
       <c r="C20" t="s">
-        <v>546</v>
+        <v>566</v>
       </c>
       <c r="D20">
         <v>2</v>
@@ -2456,13 +2483,13 @@
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>569</v>
+        <v>546</v>
       </c>
       <c r="B21" t="s">
-        <v>547</v>
+        <v>532</v>
       </c>
       <c r="C21" t="s">
-        <v>548</v>
+        <v>567</v>
       </c>
       <c r="D21">
         <v>3</v>
@@ -2473,13 +2500,13 @@
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>569</v>
+        <v>546</v>
       </c>
       <c r="B22" t="s">
-        <v>549</v>
+        <v>533</v>
       </c>
       <c r="C22" t="s">
-        <v>550</v>
+        <v>568</v>
       </c>
       <c r="D22">
         <v>3</v>
@@ -2490,13 +2517,13 @@
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
+        <v>546</v>
+      </c>
+      <c r="B23" t="s">
+        <v>534</v>
+      </c>
+      <c r="C23" t="s">
         <v>569</v>
-      </c>
-      <c r="B23" t="s">
-        <v>551</v>
-      </c>
-      <c r="C23" t="s">
-        <v>552</v>
       </c>
       <c r="D23">
         <v>3</v>
@@ -2507,30 +2534,30 @@
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>569</v>
+        <v>546</v>
       </c>
       <c r="B24" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
       <c r="C24" t="s">
-        <v>554</v>
+        <v>575</v>
       </c>
       <c r="D24">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E24">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>569</v>
+        <v>546</v>
       </c>
       <c r="B25" t="s">
-        <v>555</v>
+        <v>535</v>
       </c>
       <c r="C25" t="s">
-        <v>556</v>
+        <v>570</v>
       </c>
       <c r="D25">
         <v>2</v>
@@ -2541,13 +2568,13 @@
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>569</v>
+        <v>546</v>
       </c>
       <c r="B26" t="s">
-        <v>557</v>
+        <v>536</v>
       </c>
       <c r="C26" t="s">
-        <v>558</v>
+        <v>571</v>
       </c>
       <c r="D26">
         <v>2</v>
@@ -2558,16 +2585,16 @@
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>569</v>
+        <v>546</v>
       </c>
       <c r="B27" t="s">
-        <v>559</v>
+        <v>537</v>
       </c>
       <c r="C27" t="s">
-        <v>560</v>
+        <v>572</v>
       </c>
       <c r="D27">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E27">
         <v>0</v>
@@ -2575,18 +2602,35 @@
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>569</v>
+        <v>546</v>
       </c>
       <c r="B28" t="s">
-        <v>561</v>
+        <v>538</v>
       </c>
       <c r="C28" t="s">
-        <v>562</v>
+        <v>573</v>
       </c>
       <c r="D28">
         <v>1</v>
       </c>
       <c r="E28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>546</v>
+      </c>
+      <c r="B29" t="s">
+        <v>539</v>
+      </c>
+      <c r="C29" t="s">
+        <v>574</v>
+      </c>
+      <c r="D29">
+        <v>1</v>
+      </c>
+      <c r="E29">
         <v>0</v>
       </c>
     </row>
@@ -8085,7 +8129,7 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.85546875" style="8" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.85546875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="12.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -8093,7 +8137,7 @@
       <c r="A1" t="s">
         <v>146</v>
       </c>
-      <c r="B1" s="8" t="s">
+      <c r="B1" t="s">
         <v>369</v>
       </c>
       <c r="C1" t="s">
@@ -8107,7 +8151,7 @@
       <c r="A2" t="s">
         <v>159</v>
       </c>
-      <c r="B2" s="8" t="s">
+      <c r="B2" t="s">
         <v>382</v>
       </c>
       <c r="C2" t="s">
@@ -8121,7 +8165,7 @@
       <c r="A3" t="s">
         <v>159</v>
       </c>
-      <c r="B3" s="8" t="s">
+      <c r="B3" t="s">
         <v>382</v>
       </c>
       <c r="C3" t="s">
@@ -8135,7 +8179,7 @@
       <c r="A4" t="s">
         <v>159</v>
       </c>
-      <c r="B4" s="8" t="s">
+      <c r="B4" t="s">
         <v>382</v>
       </c>
       <c r="C4" t="s">
@@ -8149,7 +8193,7 @@
       <c r="A5" t="s">
         <v>159</v>
       </c>
-      <c r="B5" s="8" t="s">
+      <c r="B5" t="s">
         <v>382</v>
       </c>
       <c r="C5" t="s">
@@ -8163,7 +8207,7 @@
       <c r="A6" t="s">
         <v>159</v>
       </c>
-      <c r="B6" s="8" t="s">
+      <c r="B6" t="s">
         <v>401</v>
       </c>
       <c r="C6" t="s">
@@ -8177,7 +8221,7 @@
       <c r="A7" t="s">
         <v>159</v>
       </c>
-      <c r="B7" s="8" t="s">
+      <c r="B7" t="s">
         <v>401</v>
       </c>
       <c r="C7" t="s">
@@ -8191,7 +8235,7 @@
       <c r="A8" t="s">
         <v>159</v>
       </c>
-      <c r="B8" s="8" t="s">
+      <c r="B8" t="s">
         <v>370</v>
       </c>
       <c r="C8" t="s">
@@ -8205,7 +8249,7 @@
       <c r="A9" t="s">
         <v>159</v>
       </c>
-      <c r="B9" s="8" t="s">
+      <c r="B9" t="s">
         <v>370</v>
       </c>
       <c r="C9" t="s">
@@ -8219,7 +8263,7 @@
       <c r="A10" t="s">
         <v>159</v>
       </c>
-      <c r="B10" s="8" t="s">
+      <c r="B10" t="s">
         <v>370</v>
       </c>
       <c r="C10" t="s">
@@ -8233,7 +8277,7 @@
       <c r="A11" t="s">
         <v>159</v>
       </c>
-      <c r="B11" s="8" t="s">
+      <c r="B11" t="s">
         <v>370</v>
       </c>
       <c r="C11" t="s">
@@ -8247,7 +8291,7 @@
       <c r="A12" t="s">
         <v>159</v>
       </c>
-      <c r="B12" s="8" t="s">
+      <c r="B12" t="s">
         <v>378</v>
       </c>
       <c r="C12" t="s">
@@ -8261,7 +8305,7 @@
       <c r="A13" t="s">
         <v>159</v>
       </c>
-      <c r="B13" s="8" t="s">
+      <c r="B13" t="s">
         <v>378</v>
       </c>
       <c r="C13" t="s">
@@ -8275,7 +8319,7 @@
       <c r="A14" t="s">
         <v>159</v>
       </c>
-      <c r="B14" s="8" t="s">
+      <c r="B14" t="s">
         <v>378</v>
       </c>
       <c r="C14" t="s">
@@ -8289,7 +8333,7 @@
       <c r="A15" t="s">
         <v>159</v>
       </c>
-      <c r="B15" s="8" t="s">
+      <c r="B15" t="s">
         <v>378</v>
       </c>
       <c r="C15" t="s">
@@ -8303,7 +8347,7 @@
       <c r="A16" t="s">
         <v>159</v>
       </c>
-      <c r="B16" s="8" t="s">
+      <c r="B16" t="s">
         <v>378</v>
       </c>
       <c r="C16" t="s">
@@ -8317,7 +8361,7 @@
       <c r="A17" t="s">
         <v>159</v>
       </c>
-      <c r="B17" s="8" t="s">
+      <c r="B17" t="s">
         <v>402</v>
       </c>
       <c r="C17" t="s">
@@ -8331,7 +8375,7 @@
       <c r="A18" t="s">
         <v>159</v>
       </c>
-      <c r="B18" s="8" t="s">
+      <c r="B18" t="s">
         <v>402</v>
       </c>
       <c r="C18" t="s">
@@ -8345,7 +8389,7 @@
       <c r="A19" t="s">
         <v>159</v>
       </c>
-      <c r="B19" s="8" t="s">
+      <c r="B19" t="s">
         <v>371</v>
       </c>
       <c r="C19" t="s">
@@ -8359,7 +8403,7 @@
       <c r="A20" t="s">
         <v>159</v>
       </c>
-      <c r="B20" s="8" t="s">
+      <c r="B20" t="s">
         <v>371</v>
       </c>
       <c r="C20" t="s">
@@ -8373,7 +8417,7 @@
       <c r="A21" t="s">
         <v>159</v>
       </c>
-      <c r="B21" s="8" t="s">
+      <c r="B21" t="s">
         <v>371</v>
       </c>
       <c r="C21" t="s">
@@ -8387,7 +8431,7 @@
       <c r="A22" t="s">
         <v>159</v>
       </c>
-      <c r="B22" s="8" t="s">
+      <c r="B22" t="s">
         <v>371</v>
       </c>
       <c r="C22" t="s">
@@ -8401,7 +8445,7 @@
       <c r="A23" t="s">
         <v>159</v>
       </c>
-      <c r="B23" s="8" t="s">
+      <c r="B23" t="s">
         <v>377</v>
       </c>
       <c r="C23" t="s">
@@ -8415,7 +8459,7 @@
       <c r="A24" t="s">
         <v>159</v>
       </c>
-      <c r="B24" s="8" t="s">
+      <c r="B24" t="s">
         <v>377</v>
       </c>
       <c r="C24" t="s">
@@ -8429,7 +8473,7 @@
       <c r="A25" t="s">
         <v>159</v>
       </c>
-      <c r="B25" s="8" t="s">
+      <c r="B25" t="s">
         <v>377</v>
       </c>
       <c r="C25" t="s">
@@ -8443,7 +8487,7 @@
       <c r="A26" t="s">
         <v>159</v>
       </c>
-      <c r="B26" s="8" t="s">
+      <c r="B26" t="s">
         <v>377</v>
       </c>
       <c r="C26" t="s">
@@ -8457,7 +8501,7 @@
       <c r="A27" t="s">
         <v>159</v>
       </c>
-      <c r="B27" s="8" t="s">
+      <c r="B27" t="s">
         <v>377</v>
       </c>
       <c r="C27" t="s">
@@ -8471,7 +8515,7 @@
       <c r="A28" t="s">
         <v>159</v>
       </c>
-      <c r="B28" s="8" t="s">
+      <c r="B28" t="s">
         <v>379</v>
       </c>
       <c r="C28" t="s">
@@ -8485,7 +8529,7 @@
       <c r="A29" t="s">
         <v>159</v>
       </c>
-      <c r="B29" s="8" t="s">
+      <c r="B29" t="s">
         <v>379</v>
       </c>
       <c r="C29" t="s">
@@ -8499,7 +8543,7 @@
       <c r="A30" t="s">
         <v>159</v>
       </c>
-      <c r="B30" s="8" t="s">
+      <c r="B30" t="s">
         <v>379</v>
       </c>
       <c r="C30" t="s">
@@ -8513,7 +8557,7 @@
       <c r="A31" t="s">
         <v>159</v>
       </c>
-      <c r="B31" s="8" t="s">
+      <c r="B31" t="s">
         <v>379</v>
       </c>
       <c r="C31" t="s">
@@ -8527,7 +8571,7 @@
       <c r="A32" t="s">
         <v>159</v>
       </c>
-      <c r="B32" s="8" t="s">
+      <c r="B32" t="s">
         <v>379</v>
       </c>
       <c r="C32" t="s">
@@ -8541,7 +8585,7 @@
       <c r="A33" t="s">
         <v>159</v>
       </c>
-      <c r="B33" s="8" t="s">
+      <c r="B33" t="s">
         <v>380</v>
       </c>
       <c r="C33" t="s">
@@ -8555,7 +8599,7 @@
       <c r="A34" t="s">
         <v>159</v>
       </c>
-      <c r="B34" s="8" t="s">
+      <c r="B34" t="s">
         <v>380</v>
       </c>
       <c r="C34" t="s">
@@ -8569,7 +8613,7 @@
       <c r="A35" t="s">
         <v>159</v>
       </c>
-      <c r="B35" s="8" t="s">
+      <c r="B35" t="s">
         <v>380</v>
       </c>
       <c r="C35" t="s">
@@ -8583,7 +8627,7 @@
       <c r="A36" t="s">
         <v>159</v>
       </c>
-      <c r="B36" s="8" t="s">
+      <c r="B36" t="s">
         <v>380</v>
       </c>
       <c r="C36" t="s">
@@ -8597,7 +8641,7 @@
       <c r="A37" t="s">
         <v>159</v>
       </c>
-      <c r="B37" s="8" t="s">
+      <c r="B37" t="s">
         <v>380</v>
       </c>
       <c r="C37" t="s">
@@ -8611,7 +8655,7 @@
       <c r="A38" t="s">
         <v>159</v>
       </c>
-      <c r="B38" s="8" t="s">
+      <c r="B38" t="s">
         <v>381</v>
       </c>
       <c r="C38" t="s">
@@ -8625,7 +8669,7 @@
       <c r="A39" t="s">
         <v>159</v>
       </c>
-      <c r="B39" s="8" t="s">
+      <c r="B39" t="s">
         <v>381</v>
       </c>
       <c r="C39" t="s">
@@ -8639,7 +8683,7 @@
       <c r="A40" t="s">
         <v>159</v>
       </c>
-      <c r="B40" s="8" t="s">
+      <c r="B40" t="s">
         <v>381</v>
       </c>
       <c r="C40" t="s">
@@ -8653,7 +8697,7 @@
       <c r="A41" t="s">
         <v>159</v>
       </c>
-      <c r="B41" s="8" t="s">
+      <c r="B41" t="s">
         <v>381</v>
       </c>
       <c r="C41" t="s">
@@ -8667,7 +8711,7 @@
       <c r="A42" t="s">
         <v>159</v>
       </c>
-      <c r="B42" s="8" t="s">
+      <c r="B42" t="s">
         <v>381</v>
       </c>
       <c r="C42" t="s">
@@ -8681,7 +8725,7 @@
       <c r="A43" t="s">
         <v>159</v>
       </c>
-      <c r="B43" s="8" t="s">
+      <c r="B43" t="s">
         <v>389</v>
       </c>
       <c r="C43" t="s">
@@ -8695,7 +8739,7 @@
       <c r="A44" t="s">
         <v>159</v>
       </c>
-      <c r="B44" s="8" t="s">
+      <c r="B44" t="s">
         <v>389</v>
       </c>
       <c r="C44" t="s">
@@ -8709,7 +8753,7 @@
       <c r="A45" t="s">
         <v>159</v>
       </c>
-      <c r="B45" s="8" t="s">
+      <c r="B45" t="s">
         <v>389</v>
       </c>
       <c r="C45" t="s">
@@ -8723,7 +8767,7 @@
       <c r="A46" t="s">
         <v>159</v>
       </c>
-      <c r="B46" s="8" t="s">
+      <c r="B46" t="s">
         <v>389</v>
       </c>
       <c r="C46" t="s">
@@ -8737,7 +8781,7 @@
       <c r="A47" t="s">
         <v>159</v>
       </c>
-      <c r="B47" s="8" t="s">
+      <c r="B47" t="s">
         <v>385</v>
       </c>
       <c r="C47" t="s">
@@ -8751,7 +8795,7 @@
       <c r="A48" t="s">
         <v>159</v>
       </c>
-      <c r="B48" s="8" t="s">
+      <c r="B48" t="s">
         <v>385</v>
       </c>
       <c r="C48" t="s">
@@ -8765,7 +8809,7 @@
       <c r="A49" t="s">
         <v>159</v>
       </c>
-      <c r="B49" s="8" t="s">
+      <c r="B49" t="s">
         <v>385</v>
       </c>
       <c r="C49" t="s">
@@ -8779,7 +8823,7 @@
       <c r="A50" t="s">
         <v>159</v>
       </c>
-      <c r="B50" s="8" t="s">
+      <c r="B50" t="s">
         <v>372</v>
       </c>
       <c r="C50" t="s">
@@ -8793,7 +8837,7 @@
       <c r="A51" t="s">
         <v>159</v>
       </c>
-      <c r="B51" s="8" t="s">
+      <c r="B51" t="s">
         <v>372</v>
       </c>
       <c r="C51" t="s">
@@ -8807,7 +8851,7 @@
       <c r="A52" t="s">
         <v>159</v>
       </c>
-      <c r="B52" s="8" t="s">
+      <c r="B52" t="s">
         <v>372</v>
       </c>
       <c r="C52" t="s">
@@ -8821,7 +8865,7 @@
       <c r="A53" t="s">
         <v>159</v>
       </c>
-      <c r="B53" s="8" t="s">
+      <c r="B53" t="s">
         <v>372</v>
       </c>
       <c r="C53" t="s">
@@ -8835,7 +8879,7 @@
       <c r="A54" t="s">
         <v>159</v>
       </c>
-      <c r="B54" s="8" t="s">
+      <c r="B54" t="s">
         <v>376</v>
       </c>
       <c r="C54" t="s">
@@ -8849,7 +8893,7 @@
       <c r="A55" t="s">
         <v>159</v>
       </c>
-      <c r="B55" s="8" t="s">
+      <c r="B55" t="s">
         <v>376</v>
       </c>
       <c r="C55" t="s">
@@ -8863,7 +8907,7 @@
       <c r="A56" t="s">
         <v>159</v>
       </c>
-      <c r="B56" s="8" t="s">
+      <c r="B56" t="s">
         <v>376</v>
       </c>
       <c r="C56" t="s">
@@ -8877,7 +8921,7 @@
       <c r="A57" t="s">
         <v>159</v>
       </c>
-      <c r="B57" s="8" t="s">
+      <c r="B57" t="s">
         <v>376</v>
       </c>
       <c r="C57" t="s">
@@ -8891,7 +8935,7 @@
       <c r="A58" t="s">
         <v>159</v>
       </c>
-      <c r="B58" s="8" t="s">
+      <c r="B58" t="s">
         <v>376</v>
       </c>
       <c r="C58" t="s">
@@ -8905,7 +8949,7 @@
       <c r="A59" t="s">
         <v>159</v>
       </c>
-      <c r="B59" s="8" t="s">
+      <c r="B59" t="s">
         <v>386</v>
       </c>
       <c r="C59" t="s">
@@ -8919,7 +8963,7 @@
       <c r="A60" t="s">
         <v>159</v>
       </c>
-      <c r="B60" s="8" t="s">
+      <c r="B60" t="s">
         <v>386</v>
       </c>
       <c r="C60" t="s">
@@ -8933,7 +8977,7 @@
       <c r="A61" t="s">
         <v>159</v>
       </c>
-      <c r="B61" s="8" t="s">
+      <c r="B61" t="s">
         <v>386</v>
       </c>
       <c r="C61" t="s">
@@ -8947,7 +8991,7 @@
       <c r="A62" t="s">
         <v>159</v>
       </c>
-      <c r="B62" s="8" t="s">
+      <c r="B62" t="s">
         <v>383</v>
       </c>
       <c r="C62" t="s">
@@ -8961,7 +9005,7 @@
       <c r="A63" t="s">
         <v>159</v>
       </c>
-      <c r="B63" s="8" t="s">
+      <c r="B63" t="s">
         <v>383</v>
       </c>
       <c r="C63" t="s">
@@ -8975,7 +9019,7 @@
       <c r="A64" t="s">
         <v>159</v>
       </c>
-      <c r="B64" s="8" t="s">
+      <c r="B64" t="s">
         <v>383</v>
       </c>
       <c r="C64" t="s">
@@ -8989,7 +9033,7 @@
       <c r="A65" t="s">
         <v>159</v>
       </c>
-      <c r="B65" s="8" t="s">
+      <c r="B65" t="s">
         <v>383</v>
       </c>
       <c r="C65" t="s">
@@ -9003,7 +9047,7 @@
       <c r="A66" t="s">
         <v>159</v>
       </c>
-      <c r="B66" s="8" t="s">
+      <c r="B66" t="s">
         <v>374</v>
       </c>
       <c r="C66" t="s">
@@ -9017,7 +9061,7 @@
       <c r="A67" t="s">
         <v>159</v>
       </c>
-      <c r="B67" s="8" t="s">
+      <c r="B67" t="s">
         <v>374</v>
       </c>
       <c r="C67" t="s">
@@ -9031,7 +9075,7 @@
       <c r="A68" t="s">
         <v>159</v>
       </c>
-      <c r="B68" s="8" t="s">
+      <c r="B68" t="s">
         <v>374</v>
       </c>
       <c r="C68" t="s">
@@ -9045,7 +9089,7 @@
       <c r="A69" t="s">
         <v>159</v>
       </c>
-      <c r="B69" s="8" t="s">
+      <c r="B69" t="s">
         <v>374</v>
       </c>
       <c r="C69" t="s">
@@ -9059,7 +9103,7 @@
       <c r="A70" t="s">
         <v>159</v>
       </c>
-      <c r="B70" s="8" t="s">
+      <c r="B70" t="s">
         <v>384</v>
       </c>
       <c r="C70" t="s">
@@ -9073,7 +9117,7 @@
       <c r="A71" t="s">
         <v>159</v>
       </c>
-      <c r="B71" s="8" t="s">
+      <c r="B71" t="s">
         <v>384</v>
       </c>
       <c r="C71" t="s">
@@ -9087,7 +9131,7 @@
       <c r="A72" t="s">
         <v>159</v>
       </c>
-      <c r="B72" s="8" t="s">
+      <c r="B72" t="s">
         <v>384</v>
       </c>
       <c r="C72" t="s">
@@ -9101,7 +9145,7 @@
       <c r="A73" t="s">
         <v>159</v>
       </c>
-      <c r="B73" s="8" t="s">
+      <c r="B73" t="s">
         <v>384</v>
       </c>
       <c r="C73" t="s">
@@ -9115,7 +9159,7 @@
       <c r="A74" t="s">
         <v>159</v>
       </c>
-      <c r="B74" s="8" t="s">
+      <c r="B74" t="s">
         <v>375</v>
       </c>
       <c r="C74" t="s">
@@ -9129,7 +9173,7 @@
       <c r="A75" t="s">
         <v>159</v>
       </c>
-      <c r="B75" s="8" t="s">
+      <c r="B75" t="s">
         <v>375</v>
       </c>
       <c r="C75" t="s">
@@ -9143,7 +9187,7 @@
       <c r="A76" t="s">
         <v>159</v>
       </c>
-      <c r="B76" s="8" t="s">
+      <c r="B76" t="s">
         <v>375</v>
       </c>
       <c r="C76" t="s">
@@ -9157,7 +9201,7 @@
       <c r="A77" t="s">
         <v>159</v>
       </c>
-      <c r="B77" s="8" t="s">
+      <c r="B77" t="s">
         <v>375</v>
       </c>
       <c r="C77" t="s">
@@ -9171,7 +9215,7 @@
       <c r="A78" t="s">
         <v>159</v>
       </c>
-      <c r="B78" s="8" t="s">
+      <c r="B78" t="s">
         <v>391</v>
       </c>
       <c r="C78" t="s">
@@ -9185,7 +9229,7 @@
       <c r="A79" t="s">
         <v>159</v>
       </c>
-      <c r="B79" s="8" t="s">
+      <c r="B79" t="s">
         <v>391</v>
       </c>
       <c r="C79" t="s">
@@ -9199,7 +9243,7 @@
       <c r="A80" t="s">
         <v>159</v>
       </c>
-      <c r="B80" s="8" t="s">
+      <c r="B80" t="s">
         <v>391</v>
       </c>
       <c r="C80" t="s">
@@ -9213,7 +9257,7 @@
       <c r="A81" t="s">
         <v>159</v>
       </c>
-      <c r="B81" s="8" t="s">
+      <c r="B81" t="s">
         <v>373</v>
       </c>
       <c r="C81" t="s">
@@ -9227,7 +9271,7 @@
       <c r="A82" t="s">
         <v>159</v>
       </c>
-      <c r="B82" s="8" t="s">
+      <c r="B82" t="s">
         <v>373</v>
       </c>
       <c r="C82" t="s">
@@ -9241,7 +9285,7 @@
       <c r="A83" t="s">
         <v>159</v>
       </c>
-      <c r="B83" s="8" t="s">
+      <c r="B83" t="s">
         <v>373</v>
       </c>
       <c r="C83" t="s">
@@ -9255,7 +9299,7 @@
       <c r="A84" t="s">
         <v>159</v>
       </c>
-      <c r="B84" s="8" t="s">
+      <c r="B84" t="s">
         <v>388</v>
       </c>
       <c r="C84" t="s">
@@ -9269,7 +9313,7 @@
       <c r="A85" t="s">
         <v>159</v>
       </c>
-      <c r="B85" s="8" t="s">
+      <c r="B85" t="s">
         <v>388</v>
       </c>
       <c r="C85" t="s">
@@ -9283,7 +9327,7 @@
       <c r="A86" t="s">
         <v>159</v>
       </c>
-      <c r="B86" s="8" t="s">
+      <c r="B86" t="s">
         <v>388</v>
       </c>
       <c r="C86" t="s">
@@ -9297,7 +9341,7 @@
       <c r="A87" t="s">
         <v>159</v>
       </c>
-      <c r="B87" s="8" t="s">
+      <c r="B87" t="s">
         <v>388</v>
       </c>
       <c r="C87" t="s">
@@ -9311,7 +9355,7 @@
       <c r="A88" t="s">
         <v>159</v>
       </c>
-      <c r="B88" s="8" t="s">
+      <c r="B88" t="s">
         <v>399</v>
       </c>
       <c r="C88" t="s">
@@ -9325,7 +9369,7 @@
       <c r="A89" t="s">
         <v>159</v>
       </c>
-      <c r="B89" s="8" t="s">
+      <c r="B89" t="s">
         <v>399</v>
       </c>
       <c r="C89" t="s">
@@ -9339,7 +9383,7 @@
       <c r="A90" t="s">
         <v>159</v>
       </c>
-      <c r="B90" s="8" t="s">
+      <c r="B90" t="s">
         <v>387</v>
       </c>
       <c r="C90" t="s">
@@ -9353,7 +9397,7 @@
       <c r="A91" t="s">
         <v>159</v>
       </c>
-      <c r="B91" s="8" t="s">
+      <c r="B91" t="s">
         <v>387</v>
       </c>
       <c r="C91" t="s">
@@ -9367,7 +9411,7 @@
       <c r="A92" t="s">
         <v>159</v>
       </c>
-      <c r="B92" s="8" t="s">
+      <c r="B92" t="s">
         <v>387</v>
       </c>
       <c r="C92" t="s">
@@ -9381,7 +9425,7 @@
       <c r="A93" t="s">
         <v>159</v>
       </c>
-      <c r="B93" s="8" t="s">
+      <c r="B93" t="s">
         <v>387</v>
       </c>
       <c r="C93" t="s">
@@ -9395,7 +9439,7 @@
       <c r="A94" t="s">
         <v>159</v>
       </c>
-      <c r="B94" s="8" t="s">
+      <c r="B94" t="s">
         <v>390</v>
       </c>
       <c r="C94" t="s">
@@ -9409,7 +9453,7 @@
       <c r="A95" t="s">
         <v>159</v>
       </c>
-      <c r="B95" s="8" t="s">
+      <c r="B95" t="s">
         <v>390</v>
       </c>
       <c r="C95" t="s">
@@ -9423,7 +9467,7 @@
       <c r="A96" t="s">
         <v>159</v>
       </c>
-      <c r="B96" s="8" t="s">
+      <c r="B96" t="s">
         <v>390</v>
       </c>
       <c r="C96" t="s">
@@ -9437,7 +9481,7 @@
       <c r="A97" t="s">
         <v>159</v>
       </c>
-      <c r="B97" s="8" t="s">
+      <c r="B97" t="s">
         <v>390</v>
       </c>
       <c r="C97" t="s">
@@ -9451,7 +9495,7 @@
       <c r="A98" t="s">
         <v>159</v>
       </c>
-      <c r="B98" s="8" t="s">
+      <c r="B98" t="s">
         <v>390</v>
       </c>
       <c r="C98" t="s">
@@ -10288,6 +10332,1417 @@
 </file>
 
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7FC8E18F-6C4D-4E79-95C6-12AA8E1945EB}">
+  <dimension ref="A1:F83"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="12.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="16.85546875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" t="s">
+        <v>547</v>
+      </c>
+      <c r="C1" t="s">
+        <v>548</v>
+      </c>
+      <c r="D1" t="s">
+        <v>549</v>
+      </c>
+      <c r="E1" t="s">
+        <v>550</v>
+      </c>
+      <c r="F1" t="s">
+        <v>576</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" s="9">
+        <v>0.15966</v>
+      </c>
+      <c r="C2" s="9">
+        <v>3.1980000000000001E-2</v>
+      </c>
+      <c r="E2" s="9">
+        <v>7.7979999999999994E-2</v>
+      </c>
+      <c r="F2">
+        <v>0.10276338514680482</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>192</v>
+      </c>
+      <c r="B3" s="9">
+        <v>1.298E-2</v>
+      </c>
+      <c r="C3" s="9">
+        <v>1.6500000000000001E-2</v>
+      </c>
+      <c r="D3">
+        <v>0.13413</v>
+      </c>
+      <c r="E3" s="9">
+        <v>4.5690000000000001E-2</v>
+      </c>
+      <c r="F3">
+        <v>5.7046979865771806E-2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>193</v>
+      </c>
+      <c r="B4" s="9">
+        <v>7.4329999999999993E-2</v>
+      </c>
+      <c r="C4" s="9">
+        <v>0.11271</v>
+      </c>
+      <c r="E4" s="9">
+        <v>4.3610000000000003E-2</v>
+      </c>
+      <c r="F4">
+        <v>6.6497622820919172E-2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>194</v>
+      </c>
+      <c r="B5" s="9">
+        <v>1.5270000000000001E-2</v>
+      </c>
+      <c r="C5" s="9">
+        <v>6.5979999999999997E-2</v>
+      </c>
+      <c r="D5">
+        <v>0.14641999999999999</v>
+      </c>
+      <c r="E5" s="9">
+        <v>1.64E-3</v>
+      </c>
+      <c r="F5">
+        <v>9.2728435867363235E-2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>49</v>
+      </c>
+      <c r="B6" s="9">
+        <v>8.4100000000000008E-3</v>
+      </c>
+      <c r="C6" s="9">
+        <v>4.3920000000000001E-2</v>
+      </c>
+      <c r="D6">
+        <v>0.18093000000000001</v>
+      </c>
+      <c r="E6" s="9">
+        <v>8.0999999999999996E-3</v>
+      </c>
+      <c r="F6">
+        <v>2.6170492762099724E-2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>7</v>
+      </c>
+      <c r="B7" s="9">
+        <v>2.017E-2</v>
+      </c>
+      <c r="C7" s="9">
+        <v>0.1893</v>
+      </c>
+      <c r="E7" s="9">
+        <v>1.3480000000000001E-2</v>
+      </c>
+      <c r="F7">
+        <v>2.3157235582423143E-2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>195</v>
+      </c>
+      <c r="B8" s="9">
+        <v>2.043E-2</v>
+      </c>
+      <c r="C8" s="9">
+        <v>0.14116000000000001</v>
+      </c>
+      <c r="D8">
+        <v>0.10986</v>
+      </c>
+      <c r="E8" s="9">
+        <v>2.2030000000000001E-2</v>
+      </c>
+      <c r="F8">
+        <v>7.4038997214484689E-2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>196</v>
+      </c>
+      <c r="B9" s="9">
+        <v>7.0899999999999999E-3</v>
+      </c>
+      <c r="C9" s="9">
+        <v>5.219E-2</v>
+      </c>
+      <c r="D9">
+        <v>0.27805000000000002</v>
+      </c>
+      <c r="E9" s="9">
+        <v>4.8320000000000002E-2</v>
+      </c>
+      <c r="F9">
+        <v>1.5974833115936466E-2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>8</v>
+      </c>
+      <c r="B10" s="9">
+        <v>5.64E-3</v>
+      </c>
+      <c r="C10" s="9">
+        <v>8.3089999999999997E-2</v>
+      </c>
+      <c r="E10" s="9"/>
+      <c r="F10">
+        <v>7.7241379310344829E-3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>9</v>
+      </c>
+      <c r="B11" s="9">
+        <v>7.2199999999999999E-3</v>
+      </c>
+      <c r="C11" s="9">
+        <v>6.9879999999999998E-2</v>
+      </c>
+      <c r="D11">
+        <v>0.13275000000000001</v>
+      </c>
+      <c r="E11" s="9">
+        <v>1.5509999999999999E-2</v>
+      </c>
+      <c r="F11">
+        <v>1.573346511819455E-2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>197</v>
+      </c>
+      <c r="B12" s="9">
+        <v>1.17E-3</v>
+      </c>
+      <c r="C12" s="9">
+        <v>1.404E-2</v>
+      </c>
+      <c r="E12" s="9">
+        <v>1.6000000000000001E-4</v>
+      </c>
+      <c r="F12">
+        <v>2.2321428571428579E-3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>10</v>
+      </c>
+      <c r="B13" s="9">
+        <v>9.8499999999999994E-3</v>
+      </c>
+      <c r="C13" s="9">
+        <v>9.2880000000000004E-2</v>
+      </c>
+      <c r="D13">
+        <v>3.823E-2</v>
+      </c>
+      <c r="E13" s="9">
+        <v>0.13804</v>
+      </c>
+      <c r="F13">
+        <v>1.6318583126617055E-2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>198</v>
+      </c>
+      <c r="B14" s="9">
+        <v>1.9720000000000001E-2</v>
+      </c>
+      <c r="C14" s="9">
+        <v>7.1029999999999996E-2</v>
+      </c>
+      <c r="E14" s="9">
+        <v>8.0769999999999995E-2</v>
+      </c>
+      <c r="F14">
+        <v>2.0745542949756893E-2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>50</v>
+      </c>
+      <c r="B15" s="9">
+        <v>1.4250000000000001E-2</v>
+      </c>
+      <c r="C15" s="9">
+        <v>5.5899999999999998E-2</v>
+      </c>
+      <c r="D15">
+        <v>2.7449999999999999E-2</v>
+      </c>
+      <c r="E15" s="9"/>
+      <c r="F15">
+        <v>1.6995523130492456E-2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>199</v>
+      </c>
+      <c r="B16" s="9">
+        <v>7.5100000000000002E-3</v>
+      </c>
+      <c r="C16" s="9">
+        <v>1.558E-2</v>
+      </c>
+      <c r="E16" s="9">
+        <v>1.9820000000000001E-2</v>
+      </c>
+      <c r="F16">
+        <v>8.3100428544810884E-3</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>200</v>
+      </c>
+      <c r="B17" s="9">
+        <v>3.397E-2</v>
+      </c>
+      <c r="C17" s="9">
+        <v>8.8230000000000003E-2</v>
+      </c>
+      <c r="D17">
+        <v>8.695E-2</v>
+      </c>
+      <c r="E17" s="9">
+        <v>0.23178000000000001</v>
+      </c>
+      <c r="F17">
+        <v>3.8650618417710392E-2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>201</v>
+      </c>
+      <c r="B18" s="9">
+        <v>6.8500000000000002E-3</v>
+      </c>
+      <c r="C18" s="9">
+        <v>4.1919999999999999E-2</v>
+      </c>
+      <c r="E18" s="9">
+        <v>8.0000000000000007E-5</v>
+      </c>
+      <c r="F18">
+        <v>1.1245353159851304E-2</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>202</v>
+      </c>
+      <c r="B19" s="9">
+        <v>5.8100000000000001E-3</v>
+      </c>
+      <c r="C19" s="9">
+        <v>9.0900000000000009E-3</v>
+      </c>
+      <c r="E19" s="9">
+        <v>3.3189999999999997E-2</v>
+      </c>
+      <c r="F19">
+        <v>6.1644865433769349E-3</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>51</v>
+      </c>
+      <c r="B20" s="9">
+        <v>7.9810000000000006E-2</v>
+      </c>
+      <c r="C20" s="9">
+        <v>4.82E-2</v>
+      </c>
+      <c r="E20" s="9"/>
+      <c r="F20">
+        <v>6.2890462307371928E-2</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>203</v>
+      </c>
+      <c r="B21" s="9">
+        <v>0.11771</v>
+      </c>
+      <c r="C21" s="9">
+        <v>7.6410000000000006E-2</v>
+      </c>
+      <c r="E21" s="9">
+        <v>3.492E-2</v>
+      </c>
+      <c r="F21">
+        <v>0.10450740001555169</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>204</v>
+      </c>
+      <c r="B22" s="9">
+        <v>6.923E-2</v>
+      </c>
+      <c r="C22" s="9">
+        <v>6.019E-2</v>
+      </c>
+      <c r="E22" s="9">
+        <v>0.17216000000000001</v>
+      </c>
+      <c r="F22">
+        <v>6.6161325860995351E-2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>205</v>
+      </c>
+      <c r="B23" s="9">
+        <v>0.12694</v>
+      </c>
+      <c r="C23" s="9">
+        <v>0.12697</v>
+      </c>
+      <c r="E23" s="9">
+        <v>0.19883000000000001</v>
+      </c>
+      <c r="F23">
+        <v>0.1229835212489159</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>206</v>
+      </c>
+      <c r="B24" s="9">
+        <v>0.23297999999999999</v>
+      </c>
+      <c r="C24" s="9">
+        <v>0.11595999999999999</v>
+      </c>
+      <c r="E24" s="9">
+        <v>1.4420000000000001E-2</v>
+      </c>
+      <c r="F24">
+        <v>0.21490225945671487</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>207</v>
+      </c>
+      <c r="B25" s="9">
+        <v>2.1090000000000001E-2</v>
+      </c>
+      <c r="C25" s="9">
+        <v>8.3360000000000004E-2</v>
+      </c>
+      <c r="E25" s="9"/>
+      <c r="F25">
+        <v>2.3949579831932771E-2</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>208</v>
+      </c>
+      <c r="B26" s="9">
+        <v>4.2320000000000003E-2</v>
+      </c>
+      <c r="C26" s="9">
+        <v>8.3760000000000001E-2</v>
+      </c>
+      <c r="E26" s="9">
+        <v>0.15517</v>
+      </c>
+      <c r="F26">
+        <v>4.7607126465556801E-2</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>11</v>
+      </c>
+      <c r="B27" s="9">
+        <v>5.5500000000000002E-3</v>
+      </c>
+      <c r="C27" s="9">
+        <v>1.6910000000000001E-2</v>
+      </c>
+      <c r="E27" s="9">
+        <v>1.523E-2</v>
+      </c>
+      <c r="F27">
+        <v>6.4581917063222293E-3</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>209</v>
+      </c>
+      <c r="B28" s="9">
+        <v>9.5240000000000005E-2</v>
+      </c>
+      <c r="C28" s="9">
+        <v>4.3180000000000003E-2</v>
+      </c>
+      <c r="E28" s="9">
+        <v>6.2399999999999997E-2</v>
+      </c>
+      <c r="F28">
+        <v>6.9099526066350697E-2</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>210</v>
+      </c>
+      <c r="B29" s="9">
+        <v>6.4490000000000006E-2</v>
+      </c>
+      <c r="C29" s="9">
+        <v>5.6989999999999999E-2</v>
+      </c>
+      <c r="E29" s="9">
+        <v>2.9199999999999999E-3</v>
+      </c>
+      <c r="F29">
+        <v>6.2753141551562988E-2</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>211</v>
+      </c>
+      <c r="B30" s="9">
+        <v>6.2480000000000001E-2</v>
+      </c>
+      <c r="C30" s="9">
+        <v>5.2650000000000002E-2</v>
+      </c>
+      <c r="E30" s="9">
+        <v>0.10173</v>
+      </c>
+      <c r="F30">
+        <v>5.8967227348314284E-2</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>212</v>
+      </c>
+      <c r="B31" s="9">
+        <v>0.16317999999999999</v>
+      </c>
+      <c r="C31" s="9">
+        <v>0.10635</v>
+      </c>
+      <c r="E31" s="9">
+        <v>0.75083999999999995</v>
+      </c>
+      <c r="F31">
+        <v>0.1614764161529221</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>213</v>
+      </c>
+      <c r="B32" s="9">
+        <v>1.291E-2</v>
+      </c>
+      <c r="C32" s="9">
+        <v>3.9730000000000001E-2</v>
+      </c>
+      <c r="E32" s="9"/>
+      <c r="F32">
+        <v>1.4303464616985003E-2</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>214</v>
+      </c>
+      <c r="B33" s="9">
+        <v>6.9269999999999998E-2</v>
+      </c>
+      <c r="C33" s="9">
+        <v>6.7239999999999994E-2</v>
+      </c>
+      <c r="E33" s="9">
+        <v>9.1370000000000007E-2</v>
+      </c>
+      <c r="F33">
+        <v>6.8503201707577371E-2</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>12</v>
+      </c>
+      <c r="B34" s="9">
+        <v>3.3360000000000001E-2</v>
+      </c>
+      <c r="C34" s="9">
+        <v>0.10623</v>
+      </c>
+      <c r="E34" s="9">
+        <v>0.31896000000000002</v>
+      </c>
+      <c r="F34">
+        <v>4.8022598870056499E-2</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>215</v>
+      </c>
+      <c r="B35" s="9">
+        <v>5.6899999999999997E-3</v>
+      </c>
+      <c r="C35" s="9">
+        <v>2.2699999999999999E-3</v>
+      </c>
+      <c r="E35" s="9"/>
+      <c r="F35">
+        <v>4.8262548262548262E-3</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>216</v>
+      </c>
+      <c r="B36" s="9">
+        <v>0.17901</v>
+      </c>
+      <c r="C36" s="9">
+        <v>8.0089999999999995E-2</v>
+      </c>
+      <c r="E36" s="9"/>
+      <c r="F36">
+        <v>0.14072847682119211</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>217</v>
+      </c>
+      <c r="B37" s="9">
+        <v>3.0300000000000001E-2</v>
+      </c>
+      <c r="C37" s="9">
+        <v>4.9299999999999997E-2</v>
+      </c>
+      <c r="E37" s="9">
+        <v>0.17380000000000001</v>
+      </c>
+      <c r="F37">
+        <v>3.2800161976108522E-2</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>218</v>
+      </c>
+      <c r="B38" s="9">
+        <v>0.12252</v>
+      </c>
+      <c r="C38" s="9">
+        <v>8.7489999999999998E-2</v>
+      </c>
+      <c r="E38" s="9">
+        <v>0.30692000000000003</v>
+      </c>
+      <c r="F38">
+        <v>0.11141604365792879</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>219</v>
+      </c>
+      <c r="B39" s="9">
+        <v>5.3670000000000002E-2</v>
+      </c>
+      <c r="C39" s="9">
+        <v>5.0479999999999997E-2</v>
+      </c>
+      <c r="E39" s="9"/>
+      <c r="F39">
+        <v>5.255023183925811E-2</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>220</v>
+      </c>
+      <c r="B40" s="9">
+        <v>0.1081</v>
+      </c>
+      <c r="C40" s="9">
+        <v>0.14080999999999999</v>
+      </c>
+      <c r="E40" s="9">
+        <v>0.44716</v>
+      </c>
+      <c r="F40">
+        <v>0.11179788563515382</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>221</v>
+      </c>
+      <c r="B41" s="9">
+        <v>2.5000000000000001E-2</v>
+      </c>
+      <c r="C41" s="9">
+        <v>5.1700000000000001E-3</v>
+      </c>
+      <c r="E41" s="9">
+        <v>1.3390000000000001E-2</v>
+      </c>
+      <c r="F41">
+        <v>2.3883789323589699E-2</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>222</v>
+      </c>
+      <c r="B42" s="9">
+        <v>4.1750000000000002E-2</v>
+      </c>
+      <c r="C42" s="9">
+        <v>0.13517000000000001</v>
+      </c>
+      <c r="E42" s="9">
+        <v>0.61514000000000002</v>
+      </c>
+      <c r="F42">
+        <v>5.4419650579484523E-2</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>223</v>
+      </c>
+      <c r="B43" s="9">
+        <v>3.14E-3</v>
+      </c>
+      <c r="C43" s="9">
+        <v>8.5800000000000008E-3</v>
+      </c>
+      <c r="E43" s="9"/>
+      <c r="F43">
+        <v>3.472222222222222E-3</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>13</v>
+      </c>
+      <c r="B44" s="9">
+        <v>7.1249999999999994E-2</v>
+      </c>
+      <c r="C44" s="9">
+        <v>8.3199999999999996E-2</v>
+      </c>
+      <c r="E44" s="9">
+        <v>0.15623000000000001</v>
+      </c>
+      <c r="F44">
+        <v>7.3144905107110858E-2</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>224</v>
+      </c>
+      <c r="B45" s="9">
+        <v>8.7600000000000004E-3</v>
+      </c>
+      <c r="C45" s="9">
+        <v>2.2200000000000002E-3</v>
+      </c>
+      <c r="E45" s="9"/>
+      <c r="F45">
+        <v>7.1138211382113826E-3</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>225</v>
+      </c>
+      <c r="B46" s="9">
+        <v>9.0310000000000001E-2</v>
+      </c>
+      <c r="C46" s="9">
+        <v>6.2300000000000001E-2</v>
+      </c>
+      <c r="E46" s="9">
+        <v>1.0580000000000001E-2</v>
+      </c>
+      <c r="F46">
+        <v>8.0877657148070423E-2</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>226</v>
+      </c>
+      <c r="B47" s="9">
+        <v>1.251E-2</v>
+      </c>
+      <c r="C47" s="9">
+        <v>3.0130000000000001E-2</v>
+      </c>
+      <c r="E47" s="9">
+        <v>2.6870000000000002E-2</v>
+      </c>
+      <c r="F47">
+        <v>1.458227032252867E-2</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>227</v>
+      </c>
+      <c r="B48" s="9">
+        <v>9.3670000000000003E-2</v>
+      </c>
+      <c r="C48" s="9">
+        <v>8.2030000000000006E-2</v>
+      </c>
+      <c r="E48" s="9">
+        <v>0.34797</v>
+      </c>
+      <c r="F48">
+        <v>8.9793252890452202E-2</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>228</v>
+      </c>
+      <c r="B49" s="9">
+        <v>0.13993</v>
+      </c>
+      <c r="C49" s="9">
+        <v>0.13708000000000001</v>
+      </c>
+      <c r="E49" s="9">
+        <v>0.30248000000000003</v>
+      </c>
+      <c r="F49">
+        <v>0.13964252652567116</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>229</v>
+      </c>
+      <c r="B50" s="9">
+        <v>9.9500000000000005E-2</v>
+      </c>
+      <c r="C50" s="9">
+        <v>0.10402</v>
+      </c>
+      <c r="E50" s="9">
+        <v>0.19621</v>
+      </c>
+      <c r="F50">
+        <v>9.9375744235557298E-2</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>52</v>
+      </c>
+      <c r="B51" s="9">
+        <v>1.4300000000000001E-3</v>
+      </c>
+      <c r="C51" s="9">
+        <v>2.6540000000000001E-2</v>
+      </c>
+      <c r="E51" s="9">
+        <v>2.15E-3</v>
+      </c>
+      <c r="F51">
+        <v>4.1106128550074741E-3</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>230</v>
+      </c>
+      <c r="B52" s="9">
+        <v>7.918E-2</v>
+      </c>
+      <c r="C52" s="9">
+        <v>4.9979999999999997E-2</v>
+      </c>
+      <c r="E52" s="9">
+        <v>0.45939000000000002</v>
+      </c>
+      <c r="F52">
+        <v>6.8943504628151936E-2</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>231</v>
+      </c>
+      <c r="B53" s="9">
+        <v>3.356E-2</v>
+      </c>
+      <c r="C53" s="9">
+        <v>6.9510000000000002E-2</v>
+      </c>
+      <c r="E53" s="9">
+        <v>0.74536000000000002</v>
+      </c>
+      <c r="F53">
+        <v>3.9046501918527203E-2</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>232</v>
+      </c>
+      <c r="B54" s="9">
+        <v>7.3340000000000002E-2</v>
+      </c>
+      <c r="C54" s="9">
+        <v>1.2840000000000001E-2</v>
+      </c>
+      <c r="E54" s="9">
+        <v>4.0499999999999998E-3</v>
+      </c>
+      <c r="F54">
+        <v>4.8306571312913237E-2</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>233</v>
+      </c>
+      <c r="B55" s="9">
+        <v>7.714E-2</v>
+      </c>
+      <c r="C55" s="9">
+        <v>7.5069999999999998E-2</v>
+      </c>
+      <c r="E55" s="9"/>
+      <c r="F55">
+        <v>6.7975984532410716E-2</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>234</v>
+      </c>
+      <c r="B56" s="9">
+        <v>1.9449999999999999E-2</v>
+      </c>
+      <c r="C56" s="9">
+        <v>3.2649999999999998E-2</v>
+      </c>
+      <c r="E56" s="9">
+        <v>3.6600000000000001E-2</v>
+      </c>
+      <c r="F56">
+        <v>2.0533642691415319E-2</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>235</v>
+      </c>
+      <c r="B57" s="9">
+        <v>9.7890000000000005E-2</v>
+      </c>
+      <c r="C57" s="9">
+        <v>9.2480000000000007E-2</v>
+      </c>
+      <c r="E57" s="9">
+        <v>1.9980000000000001E-2</v>
+      </c>
+      <c r="F57">
+        <v>9.2757660167130912E-2</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>236</v>
+      </c>
+      <c r="B58" s="9">
+        <v>9.3640000000000001E-2</v>
+      </c>
+      <c r="C58" s="9">
+        <v>0.10761</v>
+      </c>
+      <c r="E58" s="9">
+        <v>8.1780000000000005E-2</v>
+      </c>
+      <c r="F58">
+        <v>9.7482550388204817E-2</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>237</v>
+      </c>
+      <c r="B59" s="9">
+        <v>4.258E-2</v>
+      </c>
+      <c r="C59" s="9">
+        <v>9.5530000000000004E-2</v>
+      </c>
+      <c r="E59" s="9"/>
+      <c r="F59">
+        <v>5.5325034578146609E-2</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>238</v>
+      </c>
+      <c r="B60" s="9">
+        <v>5.4350000000000002E-2</v>
+      </c>
+      <c r="C60" s="9">
+        <v>9.1199999999999996E-3</v>
+      </c>
+      <c r="E60" s="9"/>
+      <c r="F60">
+        <v>5.153696720374816E-2</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>239</v>
+      </c>
+      <c r="B61" s="9">
+        <v>1.8010000000000002E-2</v>
+      </c>
+      <c r="C61" s="9">
+        <v>1.2710000000000001E-2</v>
+      </c>
+      <c r="E61" s="9">
+        <v>6.25E-2</v>
+      </c>
+      <c r="F61">
+        <v>1.4139930218526192E-2</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>14</v>
+      </c>
+      <c r="B62" s="9">
+        <v>5.1119999999999999E-2</v>
+      </c>
+      <c r="C62" s="9">
+        <v>9.5259999999999997E-2</v>
+      </c>
+      <c r="E62" s="9"/>
+      <c r="F62">
+        <v>5.505251720391164E-2</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>240</v>
+      </c>
+      <c r="B63" s="9">
+        <v>3.134E-2</v>
+      </c>
+      <c r="C63" s="9">
+        <v>5.1049999999999998E-2</v>
+      </c>
+      <c r="E63" s="9">
+        <v>0.16006000000000001</v>
+      </c>
+      <c r="F63">
+        <v>3.0634997576345135E-2</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>241</v>
+      </c>
+      <c r="B64" s="9">
+        <v>4.1349999999999998E-2</v>
+      </c>
+      <c r="C64" s="9">
+        <v>4.5629999999999997E-2</v>
+      </c>
+      <c r="E64" s="9">
+        <v>0.11323</v>
+      </c>
+      <c r="F64">
+        <v>4.0991420400381319E-2</v>
+      </c>
+    </row>
+    <row r="65" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>242</v>
+      </c>
+      <c r="B65" s="9">
+        <v>0.12227</v>
+      </c>
+      <c r="C65" s="9">
+        <v>8.2180000000000003E-2</v>
+      </c>
+      <c r="E65" s="9">
+        <v>9.3329999999999996E-2</v>
+      </c>
+      <c r="F65">
+        <v>0.11877523553162854</v>
+      </c>
+    </row>
+    <row r="66" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>243</v>
+      </c>
+      <c r="B66" s="9">
+        <v>7.8780000000000003E-2</v>
+      </c>
+      <c r="C66" s="9">
+        <v>2.572E-2</v>
+      </c>
+      <c r="E66" s="9">
+        <v>0.20397000000000001</v>
+      </c>
+      <c r="F66">
+        <v>7.4107142857142871E-2</v>
+      </c>
+    </row>
+    <row r="67" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>244</v>
+      </c>
+      <c r="B67" s="9">
+        <v>2.818E-2</v>
+      </c>
+      <c r="C67" s="9">
+        <v>1.6900000000000001E-3</v>
+      </c>
+      <c r="E67" s="9"/>
+      <c r="F67">
+        <v>1.4580801944106927E-2</v>
+      </c>
+    </row>
+    <row r="68" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>245</v>
+      </c>
+      <c r="B68" s="9">
+        <v>4.3729999999999998E-2</v>
+      </c>
+      <c r="C68" s="9">
+        <v>9.1579999999999995E-2</v>
+      </c>
+      <c r="E68" s="9"/>
+      <c r="F68">
+        <v>5.4958183990442055E-2</v>
+      </c>
+    </row>
+    <row r="69" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>246</v>
+      </c>
+      <c r="B69" s="9">
+        <v>3.5699999999999998E-3</v>
+      </c>
+      <c r="C69" s="9">
+        <v>1.9939999999999999E-2</v>
+      </c>
+      <c r="E69" s="9">
+        <v>7.535E-2</v>
+      </c>
+      <c r="F69">
+        <v>7.7773727062826594E-3</v>
+      </c>
+    </row>
+    <row r="70" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>15</v>
+      </c>
+      <c r="B70" s="9">
+        <v>6.6710000000000005E-2</v>
+      </c>
+      <c r="C70" s="9">
+        <v>7.7090000000000006E-2</v>
+      </c>
+      <c r="E70" s="9">
+        <v>5.5870000000000003E-2</v>
+      </c>
+      <c r="F70">
+        <v>6.7973239557423459E-2</v>
+      </c>
+    </row>
+    <row r="71" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
+        <v>247</v>
+      </c>
+      <c r="B71" s="9">
+        <v>9.6149999999999999E-2</v>
+      </c>
+      <c r="C71" s="9">
+        <v>6.4850000000000005E-2</v>
+      </c>
+      <c r="E71" s="9">
+        <v>2.1499999999999998E-2</v>
+      </c>
+      <c r="F71">
+        <v>8.4594909332889698E-2</v>
+      </c>
+    </row>
+    <row r="72" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
+        <v>248</v>
+      </c>
+      <c r="B72" s="9">
+        <v>4.3159999999999997E-2</v>
+      </c>
+      <c r="C72" s="9">
+        <v>2.5569999999999999E-2</v>
+      </c>
+      <c r="E72" s="9">
+        <v>3.8760000000000003E-2</v>
+      </c>
+      <c r="F72">
+        <v>3.9871488590493449E-2</v>
+      </c>
+    </row>
+    <row r="73" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
+        <v>249</v>
+      </c>
+      <c r="B73" s="9">
+        <v>3.8359999999999998E-2</v>
+      </c>
+      <c r="C73" s="9">
+        <v>4.5280000000000001E-2</v>
+      </c>
+      <c r="E73" s="9">
+        <v>0.25383</v>
+      </c>
+      <c r="F73">
+        <v>4.0262089657606769E-2</v>
+      </c>
+    </row>
+    <row r="74" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
+        <v>250</v>
+      </c>
+      <c r="B74" s="9">
+        <v>3.7620000000000001E-2</v>
+      </c>
+      <c r="C74" s="9">
+        <v>8.4949999999999998E-2</v>
+      </c>
+      <c r="E74" s="9">
+        <v>7.9460000000000003E-2</v>
+      </c>
+      <c r="F74">
+        <v>4.8370384325546363E-2</v>
+      </c>
+    </row>
+    <row r="75" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
+        <v>16</v>
+      </c>
+      <c r="B75" s="9">
+        <v>8.7309999999999999E-2</v>
+      </c>
+      <c r="C75" s="9">
+        <v>0.12786</v>
+      </c>
+      <c r="E75" s="9">
+        <v>0.44885000000000003</v>
+      </c>
+      <c r="F75">
+        <v>9.0312873319311454E-2</v>
+      </c>
+    </row>
+    <row r="76" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
+        <v>251</v>
+      </c>
+      <c r="B76" s="9">
+        <v>7.2100000000000003E-3</v>
+      </c>
+      <c r="C76" s="9">
+        <v>5.7400000000000003E-3</v>
+      </c>
+      <c r="E76" s="9"/>
+      <c r="F76">
+        <v>7.0600632244467868E-3</v>
+      </c>
+    </row>
+    <row r="77" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
+        <v>17</v>
+      </c>
+      <c r="B77" s="9">
+        <v>3.705E-2</v>
+      </c>
+      <c r="C77" s="9">
+        <v>5.5939999999999997E-2</v>
+      </c>
+      <c r="E77" s="9">
+        <v>0.28910000000000002</v>
+      </c>
+      <c r="F77">
+        <v>3.9216346769249434E-2</v>
+      </c>
+    </row>
+    <row r="78" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
+        <v>60</v>
+      </c>
+      <c r="B78" s="9">
+        <v>1.685E-2</v>
+      </c>
+      <c r="C78" s="9">
+        <v>4.1480000000000003E-2</v>
+      </c>
+      <c r="E78" s="9">
+        <v>8.6849999999999997E-2</v>
+      </c>
+      <c r="F78">
+        <v>1.8174780014350994E-2</v>
+      </c>
+    </row>
+    <row r="79" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
+        <v>18</v>
+      </c>
+      <c r="B79" s="9">
+        <v>9.4009999999999996E-2</v>
+      </c>
+      <c r="C79" s="9">
+        <v>5.0799999999999998E-2</v>
+      </c>
+      <c r="E79" s="9">
+        <v>0.16173999999999999</v>
+      </c>
+      <c r="F79">
+        <v>7.7806228785803608E-2</v>
+      </c>
+    </row>
+    <row r="80" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A80" t="s">
+        <v>59</v>
+      </c>
+      <c r="B80" s="9">
+        <v>2.4899999999999999E-2</v>
+      </c>
+      <c r="C80" s="9">
+        <v>7.2760000000000005E-2</v>
+      </c>
+      <c r="E80" s="9">
+        <v>0.25317000000000001</v>
+      </c>
+      <c r="F80">
+        <v>3.3090211132437625E-2</v>
+      </c>
+    </row>
+    <row r="81" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
+        <v>19</v>
+      </c>
+      <c r="B81" s="9">
+        <v>2.5409999999999999E-2</v>
+      </c>
+      <c r="C81" s="9">
+        <v>1.0370000000000001E-2</v>
+      </c>
+      <c r="E81" s="9"/>
+      <c r="F81">
+        <v>2.4477889014121863E-2</v>
+      </c>
+    </row>
+    <row r="82" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A82" t="s">
+        <v>252</v>
+      </c>
+      <c r="B82" s="9">
+        <v>1.3780000000000001E-2</v>
+      </c>
+      <c r="C82" s="9">
+        <v>7.775E-2</v>
+      </c>
+      <c r="E82" s="9">
+        <v>0.23533000000000001</v>
+      </c>
+      <c r="F82">
+        <v>1.6930446445679252E-2</v>
+      </c>
+    </row>
+    <row r="83" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B83" s="9"/>
+      <c r="C83" s="9"/>
+      <c r="D83" s="9"/>
+      <c r="E83" s="9"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{118A6323-FA6A-47F1-8FD7-71097682A301}">
   <dimension ref="A1:C183"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -12081,7 +13536,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{61D05816-00FF-458D-8921-8D01423DCE8A}">
   <dimension ref="A1:C61"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -12755,1183 +14210,6 @@
       </c>
       <c r="C61">
         <v>-2.1</v>
-      </c>
-    </row>
-  </sheetData>
-  <sheetProtection sheet="1" objects="1" scenarios="1"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0206C416-5E99-4BF3-A01A-B219B8D6BE2C}">
-  <dimension ref="A1:C106"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>362</v>
-      </c>
-      <c r="B1" t="s">
-        <v>363</v>
-      </c>
-      <c r="C1" t="s">
-        <v>345</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>307</v>
-      </c>
-      <c r="B2" t="s">
-        <v>364</v>
-      </c>
-      <c r="C2">
-        <v>1404</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>307</v>
-      </c>
-      <c r="B3" t="s">
-        <v>365</v>
-      </c>
-      <c r="C3">
-        <v>10.7</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>307</v>
-      </c>
-      <c r="B4" t="s">
-        <v>366</v>
-      </c>
-      <c r="C4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>307</v>
-      </c>
-      <c r="B5" t="s">
-        <v>367</v>
-      </c>
-      <c r="C5">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>307</v>
-      </c>
-      <c r="B6" t="s">
-        <v>368</v>
-      </c>
-      <c r="C6">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>308</v>
-      </c>
-      <c r="B7" t="s">
-        <v>364</v>
-      </c>
-      <c r="C7">
-        <v>1428</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>308</v>
-      </c>
-      <c r="B8" t="s">
-        <v>365</v>
-      </c>
-      <c r="C8">
-        <v>9.1999999999999993</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>308</v>
-      </c>
-      <c r="B9" t="s">
-        <v>366</v>
-      </c>
-      <c r="C9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>308</v>
-      </c>
-      <c r="B10" t="s">
-        <v>367</v>
-      </c>
-      <c r="C10">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>308</v>
-      </c>
-      <c r="B11" t="s">
-        <v>368</v>
-      </c>
-      <c r="C11">
-        <v>64.7</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>309</v>
-      </c>
-      <c r="B12" t="s">
-        <v>364</v>
-      </c>
-      <c r="C12">
-        <v>1473</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>309</v>
-      </c>
-      <c r="B13" t="s">
-        <v>365</v>
-      </c>
-      <c r="C13">
-        <v>8.4700000000000006</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>309</v>
-      </c>
-      <c r="B14" t="s">
-        <v>366</v>
-      </c>
-      <c r="C14">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>309</v>
-      </c>
-      <c r="B15" t="s">
-        <v>367</v>
-      </c>
-      <c r="C15">
-        <v>1.88</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>309</v>
-      </c>
-      <c r="B16" t="s">
-        <v>368</v>
-      </c>
-      <c r="C16">
-        <v>72.400000000000006</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>310</v>
-      </c>
-      <c r="B17" t="s">
-        <v>364</v>
-      </c>
-      <c r="C17">
-        <v>3700</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>310</v>
-      </c>
-      <c r="B18" t="s">
-        <v>365</v>
-      </c>
-      <c r="C18">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>310</v>
-      </c>
-      <c r="B19" t="s">
-        <v>366</v>
-      </c>
-      <c r="C19">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>310</v>
-      </c>
-      <c r="B20" t="s">
-        <v>367</v>
-      </c>
-      <c r="C20">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>310</v>
-      </c>
-      <c r="B21" t="s">
-        <v>368</v>
-      </c>
-      <c r="C21">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
-        <v>312</v>
-      </c>
-      <c r="B22" t="s">
-        <v>364</v>
-      </c>
-      <c r="C22">
-        <v>329</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
-        <v>312</v>
-      </c>
-      <c r="B23" t="s">
-        <v>365</v>
-      </c>
-      <c r="C23">
-        <v>1.74</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
-        <v>312</v>
-      </c>
-      <c r="B24" t="s">
-        <v>366</v>
-      </c>
-      <c r="C24">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
-        <v>312</v>
-      </c>
-      <c r="B25" t="s">
-        <v>367</v>
-      </c>
-      <c r="C25">
-        <v>0.1</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
-        <v>312</v>
-      </c>
-      <c r="B26" t="s">
-        <v>368</v>
-      </c>
-      <c r="C26">
-        <v>16.399999999999999</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
-        <v>313</v>
-      </c>
-      <c r="B27" t="s">
-        <v>364</v>
-      </c>
-      <c r="C27">
-        <v>1693</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
-        <v>313</v>
-      </c>
-      <c r="B28" t="s">
-        <v>365</v>
-      </c>
-      <c r="C28">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
-        <v>313</v>
-      </c>
-      <c r="B29" t="s">
-        <v>366</v>
-      </c>
-      <c r="C29">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
-        <v>313</v>
-      </c>
-      <c r="B30" t="s">
-        <v>367</v>
-      </c>
-      <c r="C30">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A31" t="s">
-        <v>313</v>
-      </c>
-      <c r="B31" t="s">
-        <v>368</v>
-      </c>
-      <c r="C31">
-        <v>99.6</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A32" t="s">
-        <v>324</v>
-      </c>
-      <c r="B32" t="s">
-        <v>364</v>
-      </c>
-      <c r="C32">
-        <v>850</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A33" t="s">
-        <v>324</v>
-      </c>
-      <c r="B33" t="s">
-        <v>365</v>
-      </c>
-      <c r="C33">
-        <v>18.5</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A34" t="s">
-        <v>324</v>
-      </c>
-      <c r="B34" t="s">
-        <v>366</v>
-      </c>
-      <c r="C34">
-        <v>18.5</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A35" t="s">
-        <v>324</v>
-      </c>
-      <c r="B35" t="s">
-        <v>367</v>
-      </c>
-      <c r="C35">
-        <v>14.2</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A36" t="s">
-        <v>324</v>
-      </c>
-      <c r="B36" t="s">
-        <v>368</v>
-      </c>
-      <c r="C36">
-        <v>0.17</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A37" t="s">
-        <v>314</v>
-      </c>
-      <c r="B37" t="s">
-        <v>364</v>
-      </c>
-      <c r="C37">
-        <v>575</v>
-      </c>
-    </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A38" t="s">
-        <v>314</v>
-      </c>
-      <c r="B38" t="s">
-        <v>365</v>
-      </c>
-      <c r="C38">
-        <v>12.3</v>
-      </c>
-    </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A39" t="s">
-        <v>314</v>
-      </c>
-      <c r="B39" t="s">
-        <v>366</v>
-      </c>
-      <c r="C39">
-        <v>12.3</v>
-      </c>
-    </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A40" t="s">
-        <v>314</v>
-      </c>
-      <c r="B40" t="s">
-        <v>367</v>
-      </c>
-      <c r="C40">
-        <v>9.73</v>
-      </c>
-    </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A41" t="s">
-        <v>314</v>
-      </c>
-      <c r="B41" t="s">
-        <v>368</v>
-      </c>
-      <c r="C41">
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A42" t="s">
-        <v>316</v>
-      </c>
-      <c r="B42" t="s">
-        <v>364</v>
-      </c>
-      <c r="C42">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A43" t="s">
-        <v>316</v>
-      </c>
-      <c r="B43" t="s">
-        <v>365</v>
-      </c>
-      <c r="C43">
-        <v>3.5</v>
-      </c>
-    </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A44" t="s">
-        <v>316</v>
-      </c>
-      <c r="B44" t="s">
-        <v>366</v>
-      </c>
-      <c r="C44">
-        <v>3.5</v>
-      </c>
-    </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A45" t="s">
-        <v>316</v>
-      </c>
-      <c r="B45" t="s">
-        <v>367</v>
-      </c>
-      <c r="C45">
-        <v>1.9</v>
-      </c>
-    </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A46" t="s">
-        <v>316</v>
-      </c>
-      <c r="B46" t="s">
-        <v>368</v>
-      </c>
-      <c r="C46">
-        <v>4.8</v>
-      </c>
-    </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A47" t="s">
-        <v>317</v>
-      </c>
-      <c r="B47" t="s">
-        <v>364</v>
-      </c>
-      <c r="C47">
-        <v>1377</v>
-      </c>
-    </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A48" t="s">
-        <v>317</v>
-      </c>
-      <c r="B48" t="s">
-        <v>365</v>
-      </c>
-      <c r="C48">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A49" t="s">
-        <v>317</v>
-      </c>
-      <c r="B49" t="s">
-        <v>366</v>
-      </c>
-      <c r="C49">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A50" t="s">
-        <v>317</v>
-      </c>
-      <c r="B50" t="s">
-        <v>367</v>
-      </c>
-      <c r="C50">
-        <v>27.3</v>
-      </c>
-    </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A51" t="s">
-        <v>317</v>
-      </c>
-      <c r="B51" t="s">
-        <v>368</v>
-      </c>
-      <c r="C51">
-        <v>1.7</v>
-      </c>
-    </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A52" t="s">
-        <v>318</v>
-      </c>
-      <c r="B52" t="s">
-        <v>364</v>
-      </c>
-      <c r="C52">
-        <v>3049</v>
-      </c>
-    </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A53" t="s">
-        <v>318</v>
-      </c>
-      <c r="B53" t="s">
-        <v>365</v>
-      </c>
-      <c r="C53">
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A54" t="s">
-        <v>318</v>
-      </c>
-      <c r="B54" t="s">
-        <v>366</v>
-      </c>
-      <c r="C54">
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A55" t="s">
-        <v>318</v>
-      </c>
-      <c r="B55" t="s">
-        <v>367</v>
-      </c>
-      <c r="C55">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A56" t="s">
-        <v>318</v>
-      </c>
-      <c r="B56" t="s">
-        <v>368</v>
-      </c>
-      <c r="C56">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A57" t="s">
-        <v>319</v>
-      </c>
-      <c r="B57" t="s">
-        <v>364</v>
-      </c>
-      <c r="C57">
-        <v>1319</v>
-      </c>
-    </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A58" t="s">
-        <v>319</v>
-      </c>
-      <c r="B58" t="s">
-        <v>365</v>
-      </c>
-      <c r="C58">
-        <v>2.4</v>
-      </c>
-    </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A59" t="s">
-        <v>319</v>
-      </c>
-      <c r="B59" t="s">
-        <v>366</v>
-      </c>
-      <c r="C59">
-        <v>2.4</v>
-      </c>
-    </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A60" t="s">
-        <v>319</v>
-      </c>
-      <c r="B60" t="s">
-        <v>367</v>
-      </c>
-      <c r="C60">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A61" t="s">
-        <v>319</v>
-      </c>
-      <c r="B61" t="s">
-        <v>368</v>
-      </c>
-      <c r="C61">
-        <v>3.3</v>
-      </c>
-    </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A62" t="s">
-        <v>320</v>
-      </c>
-      <c r="B62" t="s">
-        <v>364</v>
-      </c>
-      <c r="C62">
-        <v>1570</v>
-      </c>
-    </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A63" t="s">
-        <v>320</v>
-      </c>
-      <c r="B63" t="s">
-        <v>365</v>
-      </c>
-      <c r="C63">
-        <v>36.200000000000003</v>
-      </c>
-    </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A64" t="s">
-        <v>320</v>
-      </c>
-      <c r="B64" t="s">
-        <v>366</v>
-      </c>
-      <c r="C64">
-        <v>36.200000000000003</v>
-      </c>
-    </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A65" t="s">
-        <v>320</v>
-      </c>
-      <c r="B65" t="s">
-        <v>367</v>
-      </c>
-      <c r="C65">
-        <v>1.92</v>
-      </c>
-    </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A66" t="s">
-        <v>320</v>
-      </c>
-      <c r="B66" t="s">
-        <v>368</v>
-      </c>
-      <c r="C66">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A67" t="s">
-        <v>321</v>
-      </c>
-      <c r="B67" t="s">
-        <v>364</v>
-      </c>
-      <c r="C67">
-        <v>789</v>
-      </c>
-    </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A68" t="s">
-        <v>321</v>
-      </c>
-      <c r="B68" t="s">
-        <v>365</v>
-      </c>
-      <c r="C68">
-        <v>19.600000000000001</v>
-      </c>
-    </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A69" t="s">
-        <v>321</v>
-      </c>
-      <c r="B69" t="s">
-        <v>366</v>
-      </c>
-      <c r="C69">
-        <v>19.600000000000001</v>
-      </c>
-    </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A70" t="s">
-        <v>321</v>
-      </c>
-      <c r="B70" t="s">
-        <v>367</v>
-      </c>
-      <c r="C70">
-        <v>12.2</v>
-      </c>
-    </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A71" t="s">
-        <v>321</v>
-      </c>
-      <c r="B71" t="s">
-        <v>368</v>
-      </c>
-      <c r="C71">
-        <v>0.21</v>
-      </c>
-    </row>
-    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A72" t="s">
-        <v>322</v>
-      </c>
-      <c r="B72" t="s">
-        <v>364</v>
-      </c>
-      <c r="C72">
-        <v>1029</v>
-      </c>
-    </row>
-    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A73" t="s">
-        <v>322</v>
-      </c>
-      <c r="B73" t="s">
-        <v>365</v>
-      </c>
-      <c r="C73">
-        <v>16.2</v>
-      </c>
-    </row>
-    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A74" t="s">
-        <v>322</v>
-      </c>
-      <c r="B74" t="s">
-        <v>366</v>
-      </c>
-      <c r="C74">
-        <v>16.2</v>
-      </c>
-    </row>
-    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A75" t="s">
-        <v>322</v>
-      </c>
-      <c r="B75" t="s">
-        <v>367</v>
-      </c>
-      <c r="C75">
-        <v>20.3</v>
-      </c>
-    </row>
-    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A76" t="s">
-        <v>322</v>
-      </c>
-      <c r="B76" t="s">
-        <v>368</v>
-      </c>
-      <c r="C76">
-        <v>0.14000000000000001</v>
-      </c>
-    </row>
-    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A77" t="s">
-        <v>323</v>
-      </c>
-      <c r="B77" t="s">
-        <v>364</v>
-      </c>
-      <c r="C77">
-        <v>426</v>
-      </c>
-    </row>
-    <row r="78" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A78" t="s">
-        <v>323</v>
-      </c>
-      <c r="B78" t="s">
-        <v>365</v>
-      </c>
-      <c r="C78">
-        <v>11.5</v>
-      </c>
-    </row>
-    <row r="79" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A79" t="s">
-        <v>323</v>
-      </c>
-      <c r="B79" t="s">
-        <v>366</v>
-      </c>
-      <c r="C79">
-        <v>11.5</v>
-      </c>
-    </row>
-    <row r="80" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A80" t="s">
-        <v>323</v>
-      </c>
-      <c r="B80" t="s">
-        <v>367</v>
-      </c>
-      <c r="C80">
-        <v>6.2</v>
-      </c>
-    </row>
-    <row r="81" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A81" t="s">
-        <v>323</v>
-      </c>
-      <c r="B81" t="s">
-        <v>368</v>
-      </c>
-      <c r="C81">
-        <v>0.1</v>
-      </c>
-    </row>
-    <row r="82" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A82" t="s">
-        <v>325</v>
-      </c>
-      <c r="B82" t="s">
-        <v>364</v>
-      </c>
-      <c r="C82">
-        <v>548</v>
-      </c>
-    </row>
-    <row r="83" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A83" t="s">
-        <v>325</v>
-      </c>
-      <c r="B83" t="s">
-        <v>365</v>
-      </c>
-      <c r="C83">
-        <v>18.100000000000001</v>
-      </c>
-    </row>
-    <row r="84" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A84" t="s">
-        <v>325</v>
-      </c>
-      <c r="B84" t="s">
-        <v>366</v>
-      </c>
-      <c r="C84">
-        <v>18.100000000000001</v>
-      </c>
-    </row>
-    <row r="85" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A85" t="s">
-        <v>325</v>
-      </c>
-      <c r="B85" t="s">
-        <v>367</v>
-      </c>
-      <c r="C85">
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="86" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A86" t="s">
-        <v>325</v>
-      </c>
-      <c r="B86" t="s">
-        <v>368</v>
-      </c>
-      <c r="C86">
-        <v>0.99</v>
-      </c>
-    </row>
-    <row r="87" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A87" t="s">
-        <v>326</v>
-      </c>
-      <c r="B87" t="s">
-        <v>364</v>
-      </c>
-      <c r="C87">
-        <v>685</v>
-      </c>
-    </row>
-    <row r="88" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A88" t="s">
-        <v>326</v>
-      </c>
-      <c r="B88" t="s">
-        <v>365</v>
-      </c>
-      <c r="C88">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="89" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A89" t="s">
-        <v>326</v>
-      </c>
-      <c r="B89" t="s">
-        <v>366</v>
-      </c>
-      <c r="C89">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="90" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A90" t="s">
-        <v>326</v>
-      </c>
-      <c r="B90" t="s">
-        <v>367</v>
-      </c>
-      <c r="C90">
-        <v>10.5</v>
-      </c>
-    </row>
-    <row r="91" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A91" t="s">
-        <v>326</v>
-      </c>
-      <c r="B91" t="s">
-        <v>368</v>
-      </c>
-      <c r="C91">
-        <v>4.8499999999999996</v>
-      </c>
-    </row>
-    <row r="92" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A92" t="s">
-        <v>327</v>
-      </c>
-      <c r="B92" t="s">
-        <v>364</v>
-      </c>
-      <c r="C92">
-        <v>387</v>
-      </c>
-    </row>
-    <row r="93" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A93" t="s">
-        <v>327</v>
-      </c>
-      <c r="B93" t="s">
-        <v>365</v>
-      </c>
-      <c r="C93">
-        <v>1.7</v>
-      </c>
-    </row>
-    <row r="94" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A94" t="s">
-        <v>327</v>
-      </c>
-      <c r="B94" t="s">
-        <v>366</v>
-      </c>
-      <c r="C94">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="95" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A95" t="s">
-        <v>327</v>
-      </c>
-      <c r="B95" t="s">
-        <v>367</v>
-      </c>
-      <c r="C95">
-        <v>2.6</v>
-      </c>
-    </row>
-    <row r="96" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A96" t="s">
-        <v>327</v>
-      </c>
-      <c r="B96" t="s">
-        <v>368</v>
-      </c>
-      <c r="C96">
-        <v>14.3</v>
-      </c>
-    </row>
-    <row r="97" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A97" t="s">
-        <v>328</v>
-      </c>
-      <c r="B97" t="s">
-        <v>364</v>
-      </c>
-      <c r="C97">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="98" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A98" t="s">
-        <v>328</v>
-      </c>
-      <c r="B98" t="s">
-        <v>365</v>
-      </c>
-      <c r="C98">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="99" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A99" t="s">
-        <v>328</v>
-      </c>
-      <c r="B99" t="s">
-        <v>366</v>
-      </c>
-      <c r="C99">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="100" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A100" t="s">
-        <v>328</v>
-      </c>
-      <c r="B100" t="s">
-        <v>367</v>
-      </c>
-      <c r="C100">
-        <v>0.1</v>
-      </c>
-    </row>
-    <row r="101" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A101" t="s">
-        <v>328</v>
-      </c>
-      <c r="B101" t="s">
-        <v>368</v>
-      </c>
-      <c r="C101">
-        <v>4.1399999999999997</v>
-      </c>
-    </row>
-    <row r="102" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A102" t="s">
-        <v>329</v>
-      </c>
-      <c r="B102" t="s">
-        <v>364</v>
-      </c>
-      <c r="C102">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="103" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A103" t="s">
-        <v>329</v>
-      </c>
-      <c r="B103" t="s">
-        <v>365</v>
-      </c>
-      <c r="C103">
-        <v>0.7</v>
-      </c>
-    </row>
-    <row r="104" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A104" t="s">
-        <v>329</v>
-      </c>
-      <c r="B104" t="s">
-        <v>366</v>
-      </c>
-      <c r="C104">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="105" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A105" t="s">
-        <v>329</v>
-      </c>
-      <c r="B105" t="s">
-        <v>367</v>
-      </c>
-      <c r="C105">
-        <v>0.8</v>
-      </c>
-    </row>
-    <row r="106" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A106" t="s">
-        <v>329</v>
-      </c>
-      <c r="B106" t="s">
-        <v>368</v>
-      </c>
-      <c r="C106">
-        <v>9.1</v>
       </c>
     </row>
   </sheetData>
@@ -14869,6 +15147,1183 @@
 </file>
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0206C416-5E99-4BF3-A01A-B219B8D6BE2C}">
+  <dimension ref="A1:C106"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>362</v>
+      </c>
+      <c r="B1" t="s">
+        <v>363</v>
+      </c>
+      <c r="C1" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>307</v>
+      </c>
+      <c r="B2" t="s">
+        <v>364</v>
+      </c>
+      <c r="C2">
+        <v>1404</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>307</v>
+      </c>
+      <c r="B3" t="s">
+        <v>365</v>
+      </c>
+      <c r="C3">
+        <v>10.7</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>307</v>
+      </c>
+      <c r="B4" t="s">
+        <v>366</v>
+      </c>
+      <c r="C4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>307</v>
+      </c>
+      <c r="B5" t="s">
+        <v>367</v>
+      </c>
+      <c r="C5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>307</v>
+      </c>
+      <c r="B6" t="s">
+        <v>368</v>
+      </c>
+      <c r="C6">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>308</v>
+      </c>
+      <c r="B7" t="s">
+        <v>364</v>
+      </c>
+      <c r="C7">
+        <v>1428</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>308</v>
+      </c>
+      <c r="B8" t="s">
+        <v>365</v>
+      </c>
+      <c r="C8">
+        <v>9.1999999999999993</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>308</v>
+      </c>
+      <c r="B9" t="s">
+        <v>366</v>
+      </c>
+      <c r="C9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>308</v>
+      </c>
+      <c r="B10" t="s">
+        <v>367</v>
+      </c>
+      <c r="C10">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>308</v>
+      </c>
+      <c r="B11" t="s">
+        <v>368</v>
+      </c>
+      <c r="C11">
+        <v>64.7</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>309</v>
+      </c>
+      <c r="B12" t="s">
+        <v>364</v>
+      </c>
+      <c r="C12">
+        <v>1473</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>309</v>
+      </c>
+      <c r="B13" t="s">
+        <v>365</v>
+      </c>
+      <c r="C13">
+        <v>8.4700000000000006</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>309</v>
+      </c>
+      <c r="B14" t="s">
+        <v>366</v>
+      </c>
+      <c r="C14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>309</v>
+      </c>
+      <c r="B15" t="s">
+        <v>367</v>
+      </c>
+      <c r="C15">
+        <v>1.88</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>309</v>
+      </c>
+      <c r="B16" t="s">
+        <v>368</v>
+      </c>
+      <c r="C16">
+        <v>72.400000000000006</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>310</v>
+      </c>
+      <c r="B17" t="s">
+        <v>364</v>
+      </c>
+      <c r="C17">
+        <v>3700</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>310</v>
+      </c>
+      <c r="B18" t="s">
+        <v>365</v>
+      </c>
+      <c r="C18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>310</v>
+      </c>
+      <c r="B19" t="s">
+        <v>366</v>
+      </c>
+      <c r="C19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>310</v>
+      </c>
+      <c r="B20" t="s">
+        <v>367</v>
+      </c>
+      <c r="C20">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>310</v>
+      </c>
+      <c r="B21" t="s">
+        <v>368</v>
+      </c>
+      <c r="C21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>312</v>
+      </c>
+      <c r="B22" t="s">
+        <v>364</v>
+      </c>
+      <c r="C22">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>312</v>
+      </c>
+      <c r="B23" t="s">
+        <v>365</v>
+      </c>
+      <c r="C23">
+        <v>1.74</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>312</v>
+      </c>
+      <c r="B24" t="s">
+        <v>366</v>
+      </c>
+      <c r="C24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>312</v>
+      </c>
+      <c r="B25" t="s">
+        <v>367</v>
+      </c>
+      <c r="C25">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>312</v>
+      </c>
+      <c r="B26" t="s">
+        <v>368</v>
+      </c>
+      <c r="C26">
+        <v>16.399999999999999</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>313</v>
+      </c>
+      <c r="B27" t="s">
+        <v>364</v>
+      </c>
+      <c r="C27">
+        <v>1693</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>313</v>
+      </c>
+      <c r="B28" t="s">
+        <v>365</v>
+      </c>
+      <c r="C28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>313</v>
+      </c>
+      <c r="B29" t="s">
+        <v>366</v>
+      </c>
+      <c r="C29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>313</v>
+      </c>
+      <c r="B30" t="s">
+        <v>367</v>
+      </c>
+      <c r="C30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>313</v>
+      </c>
+      <c r="B31" t="s">
+        <v>368</v>
+      </c>
+      <c r="C31">
+        <v>99.6</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>324</v>
+      </c>
+      <c r="B32" t="s">
+        <v>364</v>
+      </c>
+      <c r="C32">
+        <v>850</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>324</v>
+      </c>
+      <c r="B33" t="s">
+        <v>365</v>
+      </c>
+      <c r="C33">
+        <v>18.5</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>324</v>
+      </c>
+      <c r="B34" t="s">
+        <v>366</v>
+      </c>
+      <c r="C34">
+        <v>18.5</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>324</v>
+      </c>
+      <c r="B35" t="s">
+        <v>367</v>
+      </c>
+      <c r="C35">
+        <v>14.2</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>324</v>
+      </c>
+      <c r="B36" t="s">
+        <v>368</v>
+      </c>
+      <c r="C36">
+        <v>0.17</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>314</v>
+      </c>
+      <c r="B37" t="s">
+        <v>364</v>
+      </c>
+      <c r="C37">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>314</v>
+      </c>
+      <c r="B38" t="s">
+        <v>365</v>
+      </c>
+      <c r="C38">
+        <v>12.3</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>314</v>
+      </c>
+      <c r="B39" t="s">
+        <v>366</v>
+      </c>
+      <c r="C39">
+        <v>12.3</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>314</v>
+      </c>
+      <c r="B40" t="s">
+        <v>367</v>
+      </c>
+      <c r="C40">
+        <v>9.73</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>314</v>
+      </c>
+      <c r="B41" t="s">
+        <v>368</v>
+      </c>
+      <c r="C41">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>316</v>
+      </c>
+      <c r="B42" t="s">
+        <v>364</v>
+      </c>
+      <c r="C42">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>316</v>
+      </c>
+      <c r="B43" t="s">
+        <v>365</v>
+      </c>
+      <c r="C43">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>316</v>
+      </c>
+      <c r="B44" t="s">
+        <v>366</v>
+      </c>
+      <c r="C44">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>316</v>
+      </c>
+      <c r="B45" t="s">
+        <v>367</v>
+      </c>
+      <c r="C45">
+        <v>1.9</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>316</v>
+      </c>
+      <c r="B46" t="s">
+        <v>368</v>
+      </c>
+      <c r="C46">
+        <v>4.8</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>317</v>
+      </c>
+      <c r="B47" t="s">
+        <v>364</v>
+      </c>
+      <c r="C47">
+        <v>1377</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>317</v>
+      </c>
+      <c r="B48" t="s">
+        <v>365</v>
+      </c>
+      <c r="C48">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>317</v>
+      </c>
+      <c r="B49" t="s">
+        <v>366</v>
+      </c>
+      <c r="C49">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>317</v>
+      </c>
+      <c r="B50" t="s">
+        <v>367</v>
+      </c>
+      <c r="C50">
+        <v>27.3</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>317</v>
+      </c>
+      <c r="B51" t="s">
+        <v>368</v>
+      </c>
+      <c r="C51">
+        <v>1.7</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>318</v>
+      </c>
+      <c r="B52" t="s">
+        <v>364</v>
+      </c>
+      <c r="C52">
+        <v>3049</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>318</v>
+      </c>
+      <c r="B53" t="s">
+        <v>365</v>
+      </c>
+      <c r="C53">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>318</v>
+      </c>
+      <c r="B54" t="s">
+        <v>366</v>
+      </c>
+      <c r="C54">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>318</v>
+      </c>
+      <c r="B55" t="s">
+        <v>367</v>
+      </c>
+      <c r="C55">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>318</v>
+      </c>
+      <c r="B56" t="s">
+        <v>368</v>
+      </c>
+      <c r="C56">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>319</v>
+      </c>
+      <c r="B57" t="s">
+        <v>364</v>
+      </c>
+      <c r="C57">
+        <v>1319</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>319</v>
+      </c>
+      <c r="B58" t="s">
+        <v>365</v>
+      </c>
+      <c r="C58">
+        <v>2.4</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>319</v>
+      </c>
+      <c r="B59" t="s">
+        <v>366</v>
+      </c>
+      <c r="C59">
+        <v>2.4</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>319</v>
+      </c>
+      <c r="B60" t="s">
+        <v>367</v>
+      </c>
+      <c r="C60">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>319</v>
+      </c>
+      <c r="B61" t="s">
+        <v>368</v>
+      </c>
+      <c r="C61">
+        <v>3.3</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>320</v>
+      </c>
+      <c r="B62" t="s">
+        <v>364</v>
+      </c>
+      <c r="C62">
+        <v>1570</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>320</v>
+      </c>
+      <c r="B63" t="s">
+        <v>365</v>
+      </c>
+      <c r="C63">
+        <v>36.200000000000003</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>320</v>
+      </c>
+      <c r="B64" t="s">
+        <v>366</v>
+      </c>
+      <c r="C64">
+        <v>36.200000000000003</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>320</v>
+      </c>
+      <c r="B65" t="s">
+        <v>367</v>
+      </c>
+      <c r="C65">
+        <v>1.92</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>320</v>
+      </c>
+      <c r="B66" t="s">
+        <v>368</v>
+      </c>
+      <c r="C66">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>321</v>
+      </c>
+      <c r="B67" t="s">
+        <v>364</v>
+      </c>
+      <c r="C67">
+        <v>789</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>321</v>
+      </c>
+      <c r="B68" t="s">
+        <v>365</v>
+      </c>
+      <c r="C68">
+        <v>19.600000000000001</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>321</v>
+      </c>
+      <c r="B69" t="s">
+        <v>366</v>
+      </c>
+      <c r="C69">
+        <v>19.600000000000001</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>321</v>
+      </c>
+      <c r="B70" t="s">
+        <v>367</v>
+      </c>
+      <c r="C70">
+        <v>12.2</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
+        <v>321</v>
+      </c>
+      <c r="B71" t="s">
+        <v>368</v>
+      </c>
+      <c r="C71">
+        <v>0.21</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
+        <v>322</v>
+      </c>
+      <c r="B72" t="s">
+        <v>364</v>
+      </c>
+      <c r="C72">
+        <v>1029</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
+        <v>322</v>
+      </c>
+      <c r="B73" t="s">
+        <v>365</v>
+      </c>
+      <c r="C73">
+        <v>16.2</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
+        <v>322</v>
+      </c>
+      <c r="B74" t="s">
+        <v>366</v>
+      </c>
+      <c r="C74">
+        <v>16.2</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
+        <v>322</v>
+      </c>
+      <c r="B75" t="s">
+        <v>367</v>
+      </c>
+      <c r="C75">
+        <v>20.3</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
+        <v>322</v>
+      </c>
+      <c r="B76" t="s">
+        <v>368</v>
+      </c>
+      <c r="C76">
+        <v>0.14000000000000001</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
+        <v>323</v>
+      </c>
+      <c r="B77" t="s">
+        <v>364</v>
+      </c>
+      <c r="C77">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
+        <v>323</v>
+      </c>
+      <c r="B78" t="s">
+        <v>365</v>
+      </c>
+      <c r="C78">
+        <v>11.5</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
+        <v>323</v>
+      </c>
+      <c r="B79" t="s">
+        <v>366</v>
+      </c>
+      <c r="C79">
+        <v>11.5</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A80" t="s">
+        <v>323</v>
+      </c>
+      <c r="B80" t="s">
+        <v>367</v>
+      </c>
+      <c r="C80">
+        <v>6.2</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
+        <v>323</v>
+      </c>
+      <c r="B81" t="s">
+        <v>368</v>
+      </c>
+      <c r="C81">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="82" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A82" t="s">
+        <v>325</v>
+      </c>
+      <c r="B82" t="s">
+        <v>364</v>
+      </c>
+      <c r="C82">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="83" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A83" t="s">
+        <v>325</v>
+      </c>
+      <c r="B83" t="s">
+        <v>365</v>
+      </c>
+      <c r="C83">
+        <v>18.100000000000001</v>
+      </c>
+    </row>
+    <row r="84" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A84" t="s">
+        <v>325</v>
+      </c>
+      <c r="B84" t="s">
+        <v>366</v>
+      </c>
+      <c r="C84">
+        <v>18.100000000000001</v>
+      </c>
+    </row>
+    <row r="85" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A85" t="s">
+        <v>325</v>
+      </c>
+      <c r="B85" t="s">
+        <v>367</v>
+      </c>
+      <c r="C85">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="86" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A86" t="s">
+        <v>325</v>
+      </c>
+      <c r="B86" t="s">
+        <v>368</v>
+      </c>
+      <c r="C86">
+        <v>0.99</v>
+      </c>
+    </row>
+    <row r="87" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A87" t="s">
+        <v>326</v>
+      </c>
+      <c r="B87" t="s">
+        <v>364</v>
+      </c>
+      <c r="C87">
+        <v>685</v>
+      </c>
+    </row>
+    <row r="88" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A88" t="s">
+        <v>326</v>
+      </c>
+      <c r="B88" t="s">
+        <v>365</v>
+      </c>
+      <c r="C88">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="89" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A89" t="s">
+        <v>326</v>
+      </c>
+      <c r="B89" t="s">
+        <v>366</v>
+      </c>
+      <c r="C89">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="90" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A90" t="s">
+        <v>326</v>
+      </c>
+      <c r="B90" t="s">
+        <v>367</v>
+      </c>
+      <c r="C90">
+        <v>10.5</v>
+      </c>
+    </row>
+    <row r="91" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A91" t="s">
+        <v>326</v>
+      </c>
+      <c r="B91" t="s">
+        <v>368</v>
+      </c>
+      <c r="C91">
+        <v>4.8499999999999996</v>
+      </c>
+    </row>
+    <row r="92" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A92" t="s">
+        <v>327</v>
+      </c>
+      <c r="B92" t="s">
+        <v>364</v>
+      </c>
+      <c r="C92">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="93" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A93" t="s">
+        <v>327</v>
+      </c>
+      <c r="B93" t="s">
+        <v>365</v>
+      </c>
+      <c r="C93">
+        <v>1.7</v>
+      </c>
+    </row>
+    <row r="94" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A94" t="s">
+        <v>327</v>
+      </c>
+      <c r="B94" t="s">
+        <v>366</v>
+      </c>
+      <c r="C94">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A95" t="s">
+        <v>327</v>
+      </c>
+      <c r="B95" t="s">
+        <v>367</v>
+      </c>
+      <c r="C95">
+        <v>2.6</v>
+      </c>
+    </row>
+    <row r="96" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A96" t="s">
+        <v>327</v>
+      </c>
+      <c r="B96" t="s">
+        <v>368</v>
+      </c>
+      <c r="C96">
+        <v>14.3</v>
+      </c>
+    </row>
+    <row r="97" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A97" t="s">
+        <v>328</v>
+      </c>
+      <c r="B97" t="s">
+        <v>364</v>
+      </c>
+      <c r="C97">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="98" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A98" t="s">
+        <v>328</v>
+      </c>
+      <c r="B98" t="s">
+        <v>365</v>
+      </c>
+      <c r="C98">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="99" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A99" t="s">
+        <v>328</v>
+      </c>
+      <c r="B99" t="s">
+        <v>366</v>
+      </c>
+      <c r="C99">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A100" t="s">
+        <v>328</v>
+      </c>
+      <c r="B100" t="s">
+        <v>367</v>
+      </c>
+      <c r="C100">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="101" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A101" t="s">
+        <v>328</v>
+      </c>
+      <c r="B101" t="s">
+        <v>368</v>
+      </c>
+      <c r="C101">
+        <v>4.1399999999999997</v>
+      </c>
+    </row>
+    <row r="102" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A102" t="s">
+        <v>329</v>
+      </c>
+      <c r="B102" t="s">
+        <v>364</v>
+      </c>
+      <c r="C102">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="103" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A103" t="s">
+        <v>329</v>
+      </c>
+      <c r="B103" t="s">
+        <v>365</v>
+      </c>
+      <c r="C103">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="104" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A104" t="s">
+        <v>329</v>
+      </c>
+      <c r="B104" t="s">
+        <v>366</v>
+      </c>
+      <c r="C104">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="105" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A105" t="s">
+        <v>329</v>
+      </c>
+      <c r="B105" t="s">
+        <v>367</v>
+      </c>
+      <c r="C105">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="106" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A106" t="s">
+        <v>329</v>
+      </c>
+      <c r="B106" t="s">
+        <v>368</v>
+      </c>
+      <c r="C106">
+        <v>9.1</v>
+      </c>
+    </row>
+  </sheetData>
+  <sheetProtection sheet="1" objects="1" scenarios="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{97461BA3-2572-48E1-B51A-549B5CBBC0F1}">
   <dimension ref="A1:B7"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -14935,7 +16390,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:D1343"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -33754,7 +35209,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FEAC8083-8073-4708-9AE8-A894D58A1ECD}">
   <dimension ref="A1:W312"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -38191,7 +39646,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D959A23A-6549-4BFB-8CFE-8BFCAC8B0CB4}">
   <dimension ref="A1:D2155"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -68377,7 +69832,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9AC8E327-ABF8-4EDA-AC3F-CA18C56BB80A}">
   <dimension ref="A1:B40"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -72310,27 +73765,22 @@
   <cols>
     <col min="1" max="1" width="6.140625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="10.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.42578125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="10.42578125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="10.85546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="8.42578125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="8.5703125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="9.5703125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="10.28515625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="11.85546875" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="9" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="10" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="10.42578125" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="8" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="8.140625" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="8.7109375" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="9.85546875" bestFit="1" customWidth="1"/>
-    <col min="22" max="23" width="9.7109375" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="8.7109375" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="10.28515625" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="9.85546875" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="9.5703125" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.5703125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.28515625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="9" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="10" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="8" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="8.7109375" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="8.7109375" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="10.28515625" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="9.5703125" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="9.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:28" x14ac:dyDescent="0.25">
@@ -72423,7 +73873,7 @@
       <c r="A2" t="s">
         <v>6</v>
       </c>
-      <c r="B2">
+      <c r="B2" s="8">
         <v>2.14</v>
       </c>
       <c r="C2">
@@ -79386,7 +80836,6 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection sheet="1" objects="1" scenarios="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
